--- a/src/main/resources/btc_usdt_dummy_year.xlsx
+++ b/src/main/resources/btc_usdt_dummy_year.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24527"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NoteBook\Desktop\Mine\Code\CAlg\src\main\resources\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E242AA5-7F64-45A4-A953-CD1BCB36515C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -1132,8 +1138,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1196,6 +1202,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1242,7 +1256,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1274,9 +1288,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1308,6 +1340,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1483,11 +1533,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F366"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1507,7 +1557,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1527,7 +1577,7 @@
         <v>21839.9</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1544,10 +1594,10 @@
         <v>42479.38</v>
       </c>
       <c r="F3">
-        <v>33233.87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>33233.870000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1567,7 +1617,7 @@
         <v>18479.93</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1587,7 +1637,7 @@
         <v>21834.86</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1598,7 +1648,7 @@
         <v>42367.06</v>
       </c>
       <c r="D6">
-        <v>41609.73</v>
+        <v>41609.730000000003</v>
       </c>
       <c r="E6">
         <v>42293.18</v>
@@ -1607,7 +1657,7 @@
         <v>31175.41</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1618,16 +1668,16 @@
         <v>42965.39</v>
       </c>
       <c r="D7">
-        <v>42081.28</v>
+        <v>42081.279999999999</v>
       </c>
       <c r="E7">
         <v>42490.84</v>
       </c>
       <c r="F7">
-        <v>17010.42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>17010.419999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1647,7 +1697,7 @@
         <v>21400</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1664,10 +1714,10 @@
         <v>42655.3</v>
       </c>
       <c r="F9">
-        <v>18412.51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>18412.509999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1687,18 +1737,18 @@
         <v>27596.9</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="B11">
-        <v>42797.28</v>
+        <v>42797.279999999999</v>
       </c>
       <c r="C11">
         <v>43481.97</v>
       </c>
       <c r="D11">
-        <v>42507.84</v>
+        <v>42507.839999999997</v>
       </c>
       <c r="E11">
         <v>43288.62</v>
@@ -1707,7 +1757,7 @@
         <v>25735.22</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1727,7 +1777,7 @@
         <v>32470.82</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -1747,7 +1797,7 @@
         <v>13416.13</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1767,7 +1817,7 @@
         <v>27818.5</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1787,7 +1837,7 @@
         <v>36318.89</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -1807,7 +1857,7 @@
         <v>27458.7</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1827,12 +1877,12 @@
         <v>27639.86</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>22</v>
       </c>
       <c r="B18">
-        <v>44017.44</v>
+        <v>44017.440000000002</v>
       </c>
       <c r="C18">
         <v>44385.36</v>
@@ -1847,7 +1897,7 @@
         <v>11537.22</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -1864,15 +1914,15 @@
         <v>43424.29</v>
       </c>
       <c r="F19">
-        <v>8974.709999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>8974.7099999999991</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>24</v>
       </c>
       <c r="B20">
-        <v>43613.76</v>
+        <v>43613.760000000002</v>
       </c>
       <c r="C20">
         <v>44050.27</v>
@@ -1884,10 +1934,10 @@
         <v>43384.72</v>
       </c>
       <c r="F20">
-        <v>38759.3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>38759.300000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1907,7 +1957,7 @@
         <v>21540.97</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -1924,10 +1974,10 @@
         <v>44189.83</v>
       </c>
       <c r="F22">
-        <v>33115.63</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>33115.629999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -1947,7 +1997,7 @@
         <v>23527.85</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -1967,7 +2017,7 @@
         <v>26408.58</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1987,7 +2037,7 @@
         <v>15242.94</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -2007,12 +2057,12 @@
         <v>27144.92</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>31</v>
       </c>
       <c r="B27">
-        <v>45061.28</v>
+        <v>45061.279999999999</v>
       </c>
       <c r="C27">
         <v>45628.95</v>
@@ -2027,7 +2077,7 @@
         <v>19244.2</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -2047,7 +2097,7 @@
         <v>25974.26</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -2061,13 +2111,13 @@
         <v>43850.11</v>
       </c>
       <c r="E29">
-        <v>44501.12</v>
+        <v>44501.120000000003</v>
       </c>
       <c r="F29">
         <v>33677.82</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -2084,10 +2134,10 @@
         <v>43635.97</v>
       </c>
       <c r="F30">
-        <v>24552.08</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>24552.080000000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -2104,10 +2154,10 @@
         <v>43064.66</v>
       </c>
       <c r="F31">
-        <v>32658.8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>32658.799999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -2127,7 +2177,7 @@
         <v>25026.3</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -2147,7 +2197,7 @@
         <v>16261.1</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -2167,7 +2217,7 @@
         <v>25018.37</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -2187,7 +2237,7 @@
         <v>2414.08</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -2207,7 +2257,7 @@
         <v>14684.72</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -2227,7 +2277,7 @@
         <v>31518.14</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -2247,7 +2297,7 @@
         <v>12259.94</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -2264,10 +2314,10 @@
         <v>43214.94</v>
       </c>
       <c r="F39">
-        <v>33535.27</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>33535.269999999997</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -2287,7 +2337,7 @@
         <v>12445.02</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -2307,12 +2357,12 @@
         <v>21554.84</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>46</v>
       </c>
       <c r="B42">
-        <v>42078.88</v>
+        <v>42078.879999999997</v>
       </c>
       <c r="C42">
         <v>42268.62</v>
@@ -2321,13 +2371,13 @@
         <v>41356.35</v>
       </c>
       <c r="E42">
-        <v>41565.44</v>
+        <v>41565.440000000002</v>
       </c>
       <c r="F42">
         <v>27244.28</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -2347,7 +2397,7 @@
         <v>29578.07</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>48</v>
       </c>
@@ -2364,10 +2414,10 @@
         <v>42351.24</v>
       </c>
       <c r="F44">
-        <v>32801.76</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>32801.760000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -2378,24 +2428,24 @@
         <v>42649.48</v>
       </c>
       <c r="D45">
-        <v>41655.8</v>
+        <v>41655.800000000003</v>
       </c>
       <c r="E45">
         <v>42041.97</v>
       </c>
       <c r="F45">
-        <v>36280.64</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <v>36280.639999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>50</v>
       </c>
       <c r="B46">
-        <v>41225.36</v>
+        <v>41225.360000000001</v>
       </c>
       <c r="C46">
-        <v>41733.05</v>
+        <v>41733.050000000003</v>
       </c>
       <c r="D46">
         <v>40959.07</v>
@@ -2407,12 +2457,12 @@
         <v>23364.01</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>51</v>
       </c>
       <c r="B47">
-        <v>41281.73</v>
+        <v>41281.730000000003</v>
       </c>
       <c r="C47">
         <v>41927.19</v>
@@ -2424,10 +2474,10 @@
         <v>41384.39</v>
       </c>
       <c r="F47">
-        <v>9178.780000000001</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>9178.7800000000007</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>52</v>
       </c>
@@ -2444,10 +2494,10 @@
         <v>40308.68</v>
       </c>
       <c r="F48">
-        <v>34954.09</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+        <v>34954.089999999997</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>53</v>
       </c>
@@ -2458,16 +2508,16 @@
         <v>40906.14</v>
       </c>
       <c r="D49">
-        <v>39907.76</v>
+        <v>39907.760000000002</v>
       </c>
       <c r="E49">
-        <v>40662.62</v>
+        <v>40662.620000000003</v>
       </c>
       <c r="F49">
         <v>16803.88</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>54</v>
       </c>
@@ -2478,7 +2528,7 @@
         <v>41313.58</v>
       </c>
       <c r="D50">
-        <v>40438.34</v>
+        <v>40438.339999999997</v>
       </c>
       <c r="E50">
         <v>40682.42</v>
@@ -2487,7 +2537,7 @@
         <v>21512.78</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>55</v>
       </c>
@@ -2495,7 +2545,7 @@
         <v>41000.74</v>
       </c>
       <c r="C51">
-        <v>41183.12</v>
+        <v>41183.120000000003</v>
       </c>
       <c r="D51">
         <v>40453.96</v>
@@ -2507,7 +2557,7 @@
         <v>22223.32</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>56</v>
       </c>
@@ -2518,36 +2568,36 @@
         <v>41276.19</v>
       </c>
       <c r="D52">
-        <v>40390.48</v>
+        <v>40390.480000000003</v>
       </c>
       <c r="E52">
-        <v>40574.27</v>
+        <v>40574.269999999997</v>
       </c>
       <c r="F52">
         <v>17247.72</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>57</v>
       </c>
       <c r="B53">
-        <v>40798.7</v>
+        <v>40798.699999999997</v>
       </c>
       <c r="C53">
-        <v>41032.95</v>
+        <v>41032.949999999997</v>
       </c>
       <c r="D53">
         <v>40380.26</v>
       </c>
       <c r="E53">
-        <v>40970.4</v>
+        <v>40970.400000000001</v>
       </c>
       <c r="F53">
         <v>32690.53</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>58</v>
       </c>
@@ -2555,10 +2605,10 @@
         <v>41190.17</v>
       </c>
       <c r="C54">
-        <v>41567.63</v>
+        <v>41567.629999999997</v>
       </c>
       <c r="D54">
-        <v>40580.77</v>
+        <v>40580.769999999997</v>
       </c>
       <c r="E54">
         <v>40903.94</v>
@@ -2567,7 +2617,7 @@
         <v>26783.46</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>59</v>
       </c>
@@ -2578,7 +2628,7 @@
         <v>41507.58</v>
       </c>
       <c r="D55">
-        <v>40804.08</v>
+        <v>40804.080000000002</v>
       </c>
       <c r="E55">
         <v>41244.06</v>
@@ -2587,38 +2637,38 @@
         <v>29953.02</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>60</v>
       </c>
       <c r="B56">
-        <v>41320.24</v>
+        <v>41320.239999999998</v>
       </c>
       <c r="C56">
-        <v>41725.98</v>
+        <v>41725.980000000003</v>
       </c>
       <c r="D56">
-        <v>40980.48</v>
+        <v>40980.480000000003</v>
       </c>
       <c r="E56">
-        <v>41702.95</v>
+        <v>41702.949999999997</v>
       </c>
       <c r="F56">
-        <v>19105.67</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
+        <v>19105.669999999998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>61</v>
       </c>
       <c r="B57">
-        <v>41689.48</v>
+        <v>41689.480000000003</v>
       </c>
       <c r="C57">
         <v>41800.21</v>
       </c>
       <c r="D57">
-        <v>41486.63</v>
+        <v>41486.629999999997</v>
       </c>
       <c r="E57">
         <v>41648.31</v>
@@ -2627,7 +2677,7 @@
         <v>25535.5</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>62</v>
       </c>
@@ -2635,7 +2685,7 @@
         <v>41446.58</v>
       </c>
       <c r="C58">
-        <v>41896.63</v>
+        <v>41896.629999999997</v>
       </c>
       <c r="D58">
         <v>40933.49</v>
@@ -2647,7 +2697,7 @@
         <v>22970.98</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>63</v>
       </c>
@@ -2667,7 +2717,7 @@
         <v>11966.81</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>64</v>
       </c>
@@ -2675,27 +2725,27 @@
         <v>41571.5</v>
       </c>
       <c r="C60">
-        <v>41768.88</v>
+        <v>41768.879999999997</v>
       </c>
       <c r="D60">
-        <v>41071.16</v>
+        <v>41071.160000000003</v>
       </c>
       <c r="E60">
-        <v>41743.27</v>
+        <v>41743.269999999997</v>
       </c>
       <c r="F60">
         <v>24711.62</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>65</v>
       </c>
       <c r="B61">
-        <v>41819.41</v>
+        <v>41819.410000000003</v>
       </c>
       <c r="C61">
-        <v>42305.92</v>
+        <v>42305.919999999998</v>
       </c>
       <c r="D61">
         <v>41248.19</v>
@@ -2707,7 +2757,7 @@
         <v>16788.34</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>66</v>
       </c>
@@ -2718,16 +2768,16 @@
         <v>41349.69</v>
       </c>
       <c r="D62">
-        <v>40804.41</v>
+        <v>40804.410000000003</v>
       </c>
       <c r="E62">
-        <v>41098.62</v>
+        <v>41098.620000000003</v>
       </c>
       <c r="F62">
         <v>32729.64</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>67</v>
       </c>
@@ -2735,19 +2785,19 @@
         <v>40861.54</v>
       </c>
       <c r="C63">
-        <v>40965.2</v>
+        <v>40965.199999999997</v>
       </c>
       <c r="D63">
-        <v>40184.13</v>
+        <v>40184.129999999997</v>
       </c>
       <c r="E63">
-        <v>40596.38</v>
+        <v>40596.379999999997</v>
       </c>
       <c r="F63">
         <v>32103.59</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>68</v>
       </c>
@@ -2761,24 +2811,24 @@
         <v>39393.94</v>
       </c>
       <c r="E64">
-        <v>39590.23</v>
+        <v>39590.230000000003</v>
       </c>
       <c r="F64">
         <v>21163.8</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>69</v>
       </c>
       <c r="B65">
-        <v>39427.44</v>
+        <v>39427.440000000002</v>
       </c>
       <c r="C65">
         <v>40308.42</v>
       </c>
       <c r="D65">
-        <v>38822.34</v>
+        <v>38822.339999999997</v>
       </c>
       <c r="E65">
         <v>39380.25</v>
@@ -2787,7 +2837,7 @@
         <v>23822.17</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>70</v>
       </c>
@@ -2807,15 +2857,15 @@
         <v>35338.47</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>71</v>
       </c>
       <c r="B67">
-        <v>39109.7</v>
+        <v>39109.699999999997</v>
       </c>
       <c r="C67">
-        <v>39493.55</v>
+        <v>39493.550000000003</v>
       </c>
       <c r="D67">
         <v>38453.94</v>
@@ -2827,18 +2877,18 @@
         <v>13543.89</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>72</v>
       </c>
       <c r="B68">
-        <v>39303.37</v>
+        <v>39303.370000000003</v>
       </c>
       <c r="C68">
         <v>39421.17</v>
       </c>
       <c r="D68">
-        <v>39233.09</v>
+        <v>39233.089999999997</v>
       </c>
       <c r="E68">
         <v>39329.93</v>
@@ -2847,12 +2897,12 @@
         <v>11514.18</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>73</v>
       </c>
       <c r="B69">
-        <v>39350.91</v>
+        <v>39350.910000000003</v>
       </c>
       <c r="C69">
         <v>39566.61</v>
@@ -2861,21 +2911,21 @@
         <v>38999.14</v>
       </c>
       <c r="E69">
-        <v>39317.23</v>
+        <v>39317.230000000003</v>
       </c>
       <c r="F69">
-        <v>25431.04</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
+        <v>25431.040000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>74</v>
       </c>
       <c r="B70">
-        <v>39033.91</v>
+        <v>39033.910000000003</v>
       </c>
       <c r="C70">
-        <v>39547.7</v>
+        <v>39547.699999999997</v>
       </c>
       <c r="D70">
         <v>38390.94</v>
@@ -2884,10 +2934,10 @@
         <v>38641.61</v>
       </c>
       <c r="F70">
-        <v>31963.36</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
+        <v>31963.360000000001</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>75</v>
       </c>
@@ -2907,27 +2957,27 @@
         <v>28264.85</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>76</v>
       </c>
       <c r="B72">
-        <v>38560.41</v>
+        <v>38560.410000000003</v>
       </c>
       <c r="C72">
-        <v>38890.02</v>
+        <v>38890.019999999997</v>
       </c>
       <c r="D72">
-        <v>38429.59</v>
+        <v>38429.589999999997</v>
       </c>
       <c r="E72">
-        <v>38874.91</v>
+        <v>38874.910000000003</v>
       </c>
       <c r="F72">
         <v>25333.74</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>77</v>
       </c>
@@ -2935,7 +2985,7 @@
         <v>38963.4</v>
       </c>
       <c r="C73">
-        <v>39614.59</v>
+        <v>39614.589999999997</v>
       </c>
       <c r="D73">
         <v>38575.53</v>
@@ -2947,7 +2997,7 @@
         <v>31275.16</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>78</v>
       </c>
@@ -2967,18 +3017,18 @@
         <v>22344.06</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>79</v>
       </c>
       <c r="B75">
-        <v>39023.36</v>
+        <v>39023.360000000001</v>
       </c>
       <c r="C75">
         <v>39561.32</v>
       </c>
       <c r="D75">
-        <v>38346.91</v>
+        <v>38346.910000000003</v>
       </c>
       <c r="E75">
         <v>39202.5</v>
@@ -2987,12 +3037,12 @@
         <v>30297.64</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>80</v>
       </c>
       <c r="B76">
-        <v>38950.16</v>
+        <v>38950.160000000003</v>
       </c>
       <c r="C76">
         <v>39603.06</v>
@@ -3007,7 +3057,7 @@
         <v>11093.54</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>81</v>
       </c>
@@ -3015,19 +3065,19 @@
         <v>39364.18</v>
       </c>
       <c r="C77">
-        <v>39934.38</v>
+        <v>39934.379999999997</v>
       </c>
       <c r="D77">
         <v>38712.74</v>
       </c>
       <c r="E77">
-        <v>38889.41</v>
+        <v>38889.410000000003</v>
       </c>
       <c r="F77">
         <v>24923.29</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>82</v>
       </c>
@@ -3035,10 +3085,10 @@
         <v>38851.08</v>
       </c>
       <c r="C78">
-        <v>39103.88</v>
+        <v>39103.879999999997</v>
       </c>
       <c r="D78">
-        <v>38480.8</v>
+        <v>38480.800000000003</v>
       </c>
       <c r="E78">
         <v>38726.97</v>
@@ -3047,15 +3097,15 @@
         <v>19945.18</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>83</v>
       </c>
       <c r="B79">
-        <v>38876.38</v>
+        <v>38876.379999999997</v>
       </c>
       <c r="C79">
-        <v>39119.77</v>
+        <v>39119.769999999997</v>
       </c>
       <c r="D79">
         <v>38479.83</v>
@@ -3067,7 +3117,7 @@
         <v>18663.41</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>84</v>
       </c>
@@ -3075,24 +3125,24 @@
         <v>38569.65</v>
       </c>
       <c r="C80">
-        <v>39126.84</v>
+        <v>39126.839999999997</v>
       </c>
       <c r="D80">
         <v>37621.89</v>
       </c>
       <c r="E80">
-        <v>38932.84</v>
+        <v>38932.839999999997</v>
       </c>
       <c r="F80">
         <v>27220.76</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>85</v>
       </c>
       <c r="B81">
-        <v>38942.05</v>
+        <v>38942.050000000003</v>
       </c>
       <c r="C81">
         <v>39234.89</v>
@@ -3101,13 +3151,13 @@
         <v>38204.53</v>
       </c>
       <c r="E81">
-        <v>38331.09</v>
+        <v>38331.089999999997</v>
       </c>
       <c r="F81">
         <v>19324.72</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>86</v>
       </c>
@@ -3127,18 +3177,18 @@
         <v>21716.97</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>87</v>
       </c>
       <c r="B83">
-        <v>37820.96</v>
+        <v>37820.959999999999</v>
       </c>
       <c r="C83">
         <v>37999.24</v>
       </c>
       <c r="D83">
-        <v>37287.2</v>
+        <v>37287.199999999997</v>
       </c>
       <c r="E83">
         <v>37291.58</v>
@@ -3147,18 +3197,18 @@
         <v>29403.88</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>88</v>
       </c>
       <c r="B84">
-        <v>36922.98</v>
+        <v>36922.980000000003</v>
       </c>
       <c r="C84">
         <v>37193.43</v>
       </c>
       <c r="D84">
-        <v>36709.34</v>
+        <v>36709.339999999997</v>
       </c>
       <c r="E84">
         <v>36735.65</v>
@@ -3167,7 +3217,7 @@
         <v>25310.69</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>89</v>
       </c>
@@ -3178,36 +3228,36 @@
         <v>38162.33</v>
       </c>
       <c r="D85">
-        <v>36705.92</v>
+        <v>36705.919999999998</v>
       </c>
       <c r="E85">
-        <v>38019.13</v>
+        <v>38019.129999999997</v>
       </c>
       <c r="F85">
-        <v>20752.6</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
+        <v>20752.599999999999</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>90</v>
       </c>
       <c r="B86">
-        <v>38251.13</v>
+        <v>38251.129999999997</v>
       </c>
       <c r="C86">
-        <v>38898.4</v>
+        <v>38898.400000000001</v>
       </c>
       <c r="D86">
         <v>37915.32</v>
       </c>
       <c r="E86">
-        <v>38204.4</v>
+        <v>38204.400000000001</v>
       </c>
       <c r="F86">
         <v>26555.51</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>91</v>
       </c>
@@ -3215,19 +3265,19 @@
         <v>37742.93</v>
       </c>
       <c r="C87">
-        <v>38002.02</v>
+        <v>38002.019999999997</v>
       </c>
       <c r="D87">
         <v>37344.43</v>
       </c>
       <c r="E87">
-        <v>37621.02</v>
+        <v>37621.019999999997</v>
       </c>
       <c r="F87">
         <v>28581.72</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>92</v>
       </c>
@@ -3235,67 +3285,67 @@
         <v>37156.76</v>
       </c>
       <c r="C88">
-        <v>37439.12</v>
+        <v>37439.120000000003</v>
       </c>
       <c r="D88">
         <v>36874.25</v>
       </c>
       <c r="E88">
-        <v>37293.37</v>
+        <v>37293.370000000003</v>
       </c>
       <c r="F88">
         <v>22281.81</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>93</v>
       </c>
       <c r="B89">
-        <v>36964.64</v>
+        <v>36964.639999999999</v>
       </c>
       <c r="C89">
         <v>37399.29</v>
       </c>
       <c r="D89">
-        <v>36120.3</v>
+        <v>36120.300000000003</v>
       </c>
       <c r="E89">
-        <v>36247.88</v>
+        <v>36247.879999999997</v>
       </c>
       <c r="F89">
-        <v>18563.33</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
+        <v>18563.330000000002</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>94</v>
       </c>
       <c r="B90">
-        <v>36399.04</v>
+        <v>36399.040000000001</v>
       </c>
       <c r="C90">
         <v>37201.26</v>
       </c>
       <c r="D90">
-        <v>35717.98</v>
+        <v>35717.980000000003</v>
       </c>
       <c r="E90">
-        <v>36019.16</v>
+        <v>36019.160000000003</v>
       </c>
       <c r="F90">
         <v>25382.95</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>95</v>
       </c>
       <c r="B91">
-        <v>35960.24</v>
+        <v>35960.239999999998</v>
       </c>
       <c r="C91">
-        <v>36462.45</v>
+        <v>36462.449999999997</v>
       </c>
       <c r="D91">
         <v>35616.03</v>
@@ -3304,10 +3354,10 @@
         <v>35693.96</v>
       </c>
       <c r="F91">
-        <v>33582.73</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
+        <v>33582.730000000003</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>96</v>
       </c>
@@ -3318,24 +3368,24 @@
         <v>36028.19</v>
       </c>
       <c r="D92">
-        <v>35144.16</v>
+        <v>35144.160000000003</v>
       </c>
       <c r="E92">
         <v>35301</v>
       </c>
       <c r="F92">
-        <v>17542.51</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
+        <v>17542.509999999998</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>97</v>
       </c>
       <c r="B93">
-        <v>35267.16</v>
+        <v>35267.160000000003</v>
       </c>
       <c r="C93">
-        <v>35972.27</v>
+        <v>35972.269999999997</v>
       </c>
       <c r="D93">
         <v>34806.71</v>
@@ -3344,15 +3394,15 @@
         <v>35417.79</v>
       </c>
       <c r="F93">
-        <v>29968.72</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
+        <v>29968.720000000001</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>98</v>
       </c>
       <c r="B94">
-        <v>36125.28</v>
+        <v>36125.279999999999</v>
       </c>
       <c r="C94">
         <v>36439.24</v>
@@ -3367,7 +3417,7 @@
         <v>28933.47</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>99</v>
       </c>
@@ -3381,13 +3431,13 @@
         <v>36077.68</v>
       </c>
       <c r="E95">
-        <v>36555.52</v>
+        <v>36555.519999999997</v>
       </c>
       <c r="F95">
-        <v>36088.64</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
+        <v>36088.639999999999</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>100</v>
       </c>
@@ -3407,18 +3457,18 @@
         <v>46453.81</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>101</v>
       </c>
       <c r="B97">
-        <v>36831.92</v>
+        <v>36831.919999999998</v>
       </c>
       <c r="C97">
         <v>37045.75</v>
       </c>
       <c r="D97">
-        <v>36250.13</v>
+        <v>36250.129999999997</v>
       </c>
       <c r="E97">
         <v>36868.97</v>
@@ -3427,7 +3477,7 @@
         <v>31077.08</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>102</v>
       </c>
@@ -3438,7 +3488,7 @@
         <v>36905.57</v>
       </c>
       <c r="D98">
-        <v>36327.34</v>
+        <v>36327.339999999997</v>
       </c>
       <c r="E98">
         <v>36539.03</v>
@@ -3447,7 +3497,7 @@
         <v>12190.82</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>103</v>
       </c>
@@ -3464,15 +3514,15 @@
         <v>36350.61</v>
       </c>
       <c r="F99">
-        <v>39817.95</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
+        <v>39817.949999999997</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>104</v>
       </c>
       <c r="B100">
-        <v>36129.05</v>
+        <v>36129.050000000003</v>
       </c>
       <c r="C100">
         <v>36536.22</v>
@@ -3487,7 +3537,7 @@
         <v>30969.41</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>105</v>
       </c>
@@ -3498,16 +3548,16 @@
         <v>37353.56</v>
       </c>
       <c r="D101">
-        <v>36415.91</v>
+        <v>36415.910000000003</v>
       </c>
       <c r="E101">
-        <v>37159.34</v>
+        <v>37159.339999999997</v>
       </c>
       <c r="F101">
-        <v>27480.24</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
+        <v>27480.240000000002</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>106</v>
       </c>
@@ -3518,7 +3568,7 @@
         <v>37345.58</v>
       </c>
       <c r="D102">
-        <v>36705.84</v>
+        <v>36705.839999999997</v>
       </c>
       <c r="E102">
         <v>36711.82</v>
@@ -3527,7 +3577,7 @@
         <v>26353.55</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>107</v>
       </c>
@@ -3538,7 +3588,7 @@
         <v>37505.67</v>
       </c>
       <c r="D103">
-        <v>36872.45</v>
+        <v>36872.449999999997</v>
       </c>
       <c r="E103">
         <v>36959.51</v>
@@ -3547,15 +3597,15 @@
         <v>32263.73</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>108</v>
       </c>
       <c r="B104">
-        <v>36606.8</v>
+        <v>36606.800000000003</v>
       </c>
       <c r="C104">
-        <v>37011.6</v>
+        <v>37011.599999999999</v>
       </c>
       <c r="D104">
         <v>36127.42</v>
@@ -3567,7 +3617,7 @@
         <v>19679.07</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>109</v>
       </c>
@@ -3578,24 +3628,24 @@
         <v>37260.49</v>
       </c>
       <c r="D105">
-        <v>36731.2</v>
+        <v>36731.199999999997</v>
       </c>
       <c r="E105">
         <v>36929.42</v>
       </c>
       <c r="F105">
-        <v>18416.92</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
+        <v>18416.919999999998</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>110</v>
       </c>
       <c r="B106">
-        <v>37397.41</v>
+        <v>37397.410000000003</v>
       </c>
       <c r="C106">
-        <v>37920.37</v>
+        <v>37920.370000000003</v>
       </c>
       <c r="D106">
         <v>36678.33</v>
@@ -3607,7 +3657,7 @@
         <v>20191.71</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>111</v>
       </c>
@@ -3618,7 +3668,7 @@
         <v>38239.51</v>
       </c>
       <c r="D107">
-        <v>37766.24</v>
+        <v>37766.239999999998</v>
       </c>
       <c r="E107">
         <v>38096.43</v>
@@ -3627,7 +3677,7 @@
         <v>14383.28</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>112</v>
       </c>
@@ -3641,13 +3691,13 @@
         <v>37671.93</v>
       </c>
       <c r="E108">
-        <v>37979.92</v>
+        <v>37979.919999999998</v>
       </c>
       <c r="F108">
         <v>22880.19</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>113</v>
       </c>
@@ -3661,13 +3711,13 @@
         <v>37454.58</v>
       </c>
       <c r="E109">
-        <v>37945.91</v>
+        <v>37945.910000000003</v>
       </c>
       <c r="F109">
         <v>42570.33</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>114</v>
       </c>
@@ -3684,10 +3734,10 @@
         <v>37867.79</v>
       </c>
       <c r="F110">
-        <v>18097.31</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
+        <v>18097.310000000001</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>115</v>
       </c>
@@ -3698,16 +3748,16 @@
         <v>39130.69</v>
       </c>
       <c r="D111">
-        <v>38044.12</v>
+        <v>38044.120000000003</v>
       </c>
       <c r="E111">
-        <v>38837.23</v>
+        <v>38837.230000000003</v>
       </c>
       <c r="F111">
         <v>19037.18</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>116</v>
       </c>
@@ -3715,24 +3765,24 @@
         <v>38572.22</v>
       </c>
       <c r="C112">
-        <v>39097.73</v>
+        <v>39097.730000000003</v>
       </c>
       <c r="D112">
         <v>38311.21</v>
       </c>
       <c r="E112">
-        <v>38670.98</v>
+        <v>38670.980000000003</v>
       </c>
       <c r="F112">
         <v>27264.69</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>117</v>
       </c>
       <c r="B113">
-        <v>38377.88</v>
+        <v>38377.879999999997</v>
       </c>
       <c r="C113">
         <v>38637.93</v>
@@ -3747,52 +3797,52 @@
         <v>29774.67</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>118</v>
       </c>
       <c r="B114">
-        <v>38142.98</v>
+        <v>38142.980000000003</v>
       </c>
       <c r="C114">
-        <v>38521.52</v>
+        <v>38521.519999999997</v>
       </c>
       <c r="D114">
-        <v>37833.38</v>
+        <v>37833.379999999997</v>
       </c>
       <c r="E114">
-        <v>37975.95</v>
+        <v>37975.949999999997</v>
       </c>
       <c r="F114">
         <v>27796.87</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>119</v>
       </c>
       <c r="B115">
-        <v>37975.7</v>
+        <v>37975.699999999997</v>
       </c>
       <c r="C115">
         <v>38063.57</v>
       </c>
       <c r="D115">
-        <v>37762.8</v>
+        <v>37762.800000000003</v>
       </c>
       <c r="E115">
-        <v>37795.52</v>
+        <v>37795.519999999997</v>
       </c>
       <c r="F115">
         <v>14751.53</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>120</v>
       </c>
       <c r="B116">
-        <v>38155.36</v>
+        <v>38155.360000000001</v>
       </c>
       <c r="C116">
         <v>38668.14</v>
@@ -3801,21 +3851,21 @@
         <v>37711.5</v>
       </c>
       <c r="E116">
-        <v>38365.41</v>
+        <v>38365.410000000003</v>
       </c>
       <c r="F116">
         <v>8735.48</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>121</v>
       </c>
       <c r="B117">
-        <v>38362.8</v>
+        <v>38362.800000000003</v>
       </c>
       <c r="C117">
-        <v>38735.02</v>
+        <v>38735.019999999997</v>
       </c>
       <c r="D117">
         <v>37924.03</v>
@@ -3827,32 +3877,32 @@
         <v>31459.8</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>122</v>
       </c>
       <c r="B118">
-        <v>38507.27</v>
+        <v>38507.269999999997</v>
       </c>
       <c r="C118">
-        <v>38749.16</v>
+        <v>38749.160000000003</v>
       </c>
       <c r="D118">
-        <v>37948.3</v>
+        <v>37948.300000000003</v>
       </c>
       <c r="E118">
         <v>38395.9</v>
       </c>
       <c r="F118">
-        <v>40580.91</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
+        <v>40580.910000000003</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>123</v>
       </c>
       <c r="B119">
-        <v>38338.16</v>
+        <v>38338.160000000003</v>
       </c>
       <c r="C119">
         <v>38908.1</v>
@@ -3861,13 +3911,13 @@
         <v>38290.46</v>
       </c>
       <c r="E119">
-        <v>38595.48</v>
+        <v>38595.480000000003</v>
       </c>
       <c r="F119">
-        <v>19354.92</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
+        <v>19354.919999999998</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>124</v>
       </c>
@@ -3875,19 +3925,19 @@
         <v>38775.47</v>
       </c>
       <c r="C120">
-        <v>38985.88</v>
+        <v>38985.879999999997</v>
       </c>
       <c r="D120">
-        <v>38365.91</v>
+        <v>38365.910000000003</v>
       </c>
       <c r="E120">
         <v>38819.53</v>
       </c>
       <c r="F120">
-        <v>34347.2</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
+        <v>34347.199999999997</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>125</v>
       </c>
@@ -3895,19 +3945,19 @@
         <v>38651.61</v>
       </c>
       <c r="C121">
-        <v>39197.45</v>
+        <v>39197.449999999997</v>
       </c>
       <c r="D121">
         <v>38281.43</v>
       </c>
       <c r="E121">
-        <v>38353.59</v>
+        <v>38353.589999999997</v>
       </c>
       <c r="F121">
         <v>28031.46</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>126</v>
       </c>
@@ -3915,19 +3965,19 @@
         <v>37724.15</v>
       </c>
       <c r="C122">
-        <v>38362.3</v>
+        <v>38362.300000000003</v>
       </c>
       <c r="D122">
-        <v>37189.38</v>
+        <v>37189.379999999997</v>
       </c>
       <c r="E122">
-        <v>37617.36</v>
+        <v>37617.360000000001</v>
       </c>
       <c r="F122">
         <v>26078.92</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>127</v>
       </c>
@@ -3941,13 +3991,13 @@
         <v>36796.83</v>
       </c>
       <c r="E123">
-        <v>37602.27</v>
+        <v>37602.269999999997</v>
       </c>
       <c r="F123">
         <v>16118.51</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>128</v>
       </c>
@@ -3958,7 +4008,7 @@
         <v>37702.82</v>
       </c>
       <c r="D124">
-        <v>36925.98</v>
+        <v>36925.980000000003</v>
       </c>
       <c r="E124">
         <v>37056.35</v>
@@ -3967,7 +4017,7 @@
         <v>22857.58</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>129</v>
       </c>
@@ -3981,13 +4031,13 @@
         <v>36920.51</v>
       </c>
       <c r="E125">
-        <v>36972.02</v>
+        <v>36972.019999999997</v>
       </c>
       <c r="F125">
         <v>25693.21</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>130</v>
       </c>
@@ -4007,7 +4057,7 @@
         <v>29697.26</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>131</v>
       </c>
@@ -4021,13 +4071,13 @@
         <v>36899.64</v>
       </c>
       <c r="E127">
-        <v>37190.8</v>
+        <v>37190.800000000003</v>
       </c>
       <c r="F127">
         <v>28183.51</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>132</v>
       </c>
@@ -4035,7 +4085,7 @@
         <v>37373.43</v>
       </c>
       <c r="C128">
-        <v>37630.37</v>
+        <v>37630.370000000003</v>
       </c>
       <c r="D128">
         <v>37041.5</v>
@@ -4047,12 +4097,12 @@
         <v>33184.43</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>133</v>
       </c>
       <c r="B129">
-        <v>36982.2</v>
+        <v>36982.199999999997</v>
       </c>
       <c r="C129">
         <v>37312.75</v>
@@ -4067,7 +4117,7 @@
         <v>26696.79</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>134</v>
       </c>
@@ -4078,7 +4128,7 @@
         <v>37713.51</v>
       </c>
       <c r="D130">
-        <v>36791.73</v>
+        <v>36791.730000000003</v>
       </c>
       <c r="E130">
         <v>37482.93</v>
@@ -4087,7 +4137,7 @@
         <v>28560.04</v>
       </c>
     </row>
-    <row r="131" spans="1:6">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>135</v>
       </c>
@@ -4101,21 +4151,21 @@
         <v>37258.71</v>
       </c>
       <c r="E131">
-        <v>37386.2</v>
+        <v>37386.199999999997</v>
       </c>
       <c r="F131">
-        <v>30030.24</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
+        <v>30030.240000000002</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>136</v>
       </c>
       <c r="B132">
-        <v>37841.12</v>
+        <v>37841.120000000003</v>
       </c>
       <c r="C132">
-        <v>38093.84</v>
+        <v>38093.839999999997</v>
       </c>
       <c r="D132">
         <v>37109.86</v>
@@ -4127,27 +4177,27 @@
         <v>21763.74</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>137</v>
       </c>
       <c r="B133">
-        <v>36825.2</v>
+        <v>36825.199999999997</v>
       </c>
       <c r="C133">
         <v>37156.85</v>
       </c>
       <c r="D133">
-        <v>36347.88</v>
+        <v>36347.879999999997</v>
       </c>
       <c r="E133">
-        <v>36406.12</v>
+        <v>36406.120000000003</v>
       </c>
       <c r="F133">
         <v>25246.82</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>138</v>
       </c>
@@ -4158,16 +4208,16 @@
         <v>36733.53</v>
       </c>
       <c r="D134">
-        <v>36130.38</v>
+        <v>36130.379999999997</v>
       </c>
       <c r="E134">
-        <v>36150.45</v>
+        <v>36150.449999999997</v>
       </c>
       <c r="F134">
         <v>28869.8</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>139</v>
       </c>
@@ -4175,19 +4225,19 @@
         <v>35944.44</v>
       </c>
       <c r="C135">
-        <v>36093.87</v>
+        <v>36093.870000000003</v>
       </c>
       <c r="D135">
         <v>35545.25</v>
       </c>
       <c r="E135">
-        <v>36060.38</v>
+        <v>36060.379999999997</v>
       </c>
       <c r="F135">
-        <v>32214.56</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
+        <v>32214.560000000001</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>140</v>
       </c>
@@ -4195,7 +4245,7 @@
         <v>36347.53</v>
       </c>
       <c r="C136">
-        <v>36814.66</v>
+        <v>36814.660000000003</v>
       </c>
       <c r="D136">
         <v>35691.97</v>
@@ -4207,7 +4257,7 @@
         <v>24031.26</v>
       </c>
     </row>
-    <row r="137" spans="1:6">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>141</v>
       </c>
@@ -4215,7 +4265,7 @@
         <v>35842.29</v>
       </c>
       <c r="C137">
-        <v>36339.34</v>
+        <v>36339.339999999997</v>
       </c>
       <c r="D137">
         <v>35791.83</v>
@@ -4227,12 +4277,12 @@
         <v>19140.7</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>142</v>
       </c>
       <c r="B138">
-        <v>36124.66</v>
+        <v>36124.660000000003</v>
       </c>
       <c r="C138">
         <v>36473.97</v>
@@ -4241,13 +4291,13 @@
         <v>35937.39</v>
       </c>
       <c r="E138">
-        <v>36095.92</v>
+        <v>36095.919999999998</v>
       </c>
       <c r="F138">
         <v>34495.9</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>143</v>
       </c>
@@ -4255,19 +4305,19 @@
         <v>35996.35</v>
       </c>
       <c r="C139">
-        <v>36479.62</v>
+        <v>36479.620000000003</v>
       </c>
       <c r="D139">
         <v>35667.67</v>
       </c>
       <c r="E139">
-        <v>35687.41</v>
+        <v>35687.410000000003</v>
       </c>
       <c r="F139">
         <v>42507.12</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>144</v>
       </c>
@@ -4278,16 +4328,16 @@
         <v>36213.72</v>
       </c>
       <c r="D140">
-        <v>35730.64</v>
+        <v>35730.639999999999</v>
       </c>
       <c r="E140">
-        <v>36021.09</v>
+        <v>36021.089999999997</v>
       </c>
       <c r="F140">
-        <v>35051.88</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
+        <v>35051.879999999997</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>145</v>
       </c>
@@ -4301,33 +4351,33 @@
         <v>35655.42</v>
       </c>
       <c r="E141">
-        <v>35802.63</v>
+        <v>35802.629999999997</v>
       </c>
       <c r="F141">
         <v>25586.35</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>146</v>
       </c>
       <c r="B142">
-        <v>35790.7</v>
+        <v>35790.699999999997</v>
       </c>
       <c r="C142">
-        <v>36163.38</v>
+        <v>36163.379999999997</v>
       </c>
       <c r="D142">
-        <v>35699.55</v>
+        <v>35699.550000000003</v>
       </c>
       <c r="E142">
-        <v>36001.87</v>
+        <v>36001.870000000003</v>
       </c>
       <c r="F142">
-        <v>17110.83</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
+        <v>17110.830000000002</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>147</v>
       </c>
@@ -4338,7 +4388,7 @@
         <v>36747.43</v>
       </c>
       <c r="D143">
-        <v>36142.98</v>
+        <v>36142.980000000003</v>
       </c>
       <c r="E143">
         <v>36184.5</v>
@@ -4347,7 +4397,7 @@
         <v>25332.5</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>148</v>
       </c>
@@ -4355,10 +4405,10 @@
         <v>35778.97</v>
       </c>
       <c r="C144">
-        <v>36222.24</v>
+        <v>36222.239999999998</v>
       </c>
       <c r="D144">
-        <v>34919.55</v>
+        <v>34919.550000000003</v>
       </c>
       <c r="E144">
         <v>35865.94</v>
@@ -4367,7 +4417,7 @@
         <v>16796.84</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>149</v>
       </c>
@@ -4375,7 +4425,7 @@
         <v>36031.32</v>
       </c>
       <c r="C145">
-        <v>36771.13</v>
+        <v>36771.129999999997</v>
       </c>
       <c r="D145">
         <v>35534.46</v>
@@ -4387,7 +4437,7 @@
         <v>16866.38</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>150</v>
       </c>
@@ -4401,13 +4451,13 @@
         <v>35819.29</v>
       </c>
       <c r="E146">
-        <v>36746.88</v>
+        <v>36746.879999999997</v>
       </c>
       <c r="F146">
         <v>24771.79</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>151</v>
       </c>
@@ -4418,7 +4468,7 @@
         <v>37395.57</v>
       </c>
       <c r="D147">
-        <v>36577.52</v>
+        <v>36577.519999999997</v>
       </c>
       <c r="E147">
         <v>36835</v>
@@ -4427,7 +4477,7 @@
         <v>23735.31</v>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>152</v>
       </c>
@@ -4438,16 +4488,16 @@
         <v>37228.25</v>
       </c>
       <c r="D148">
-        <v>36413.28</v>
+        <v>36413.279999999999</v>
       </c>
       <c r="E148">
-        <v>36417.05</v>
+        <v>36417.050000000003</v>
       </c>
       <c r="F148">
         <v>31231.85</v>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>153</v>
       </c>
@@ -4461,13 +4511,13 @@
         <v>36016.26</v>
       </c>
       <c r="E149">
-        <v>36794.66</v>
+        <v>36794.660000000003</v>
       </c>
       <c r="F149">
         <v>28401.5</v>
       </c>
     </row>
-    <row r="150" spans="1:6">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>154</v>
       </c>
@@ -4475,7 +4525,7 @@
         <v>36840.86</v>
       </c>
       <c r="C150">
-        <v>37296.56</v>
+        <v>37296.559999999998</v>
       </c>
       <c r="D150">
         <v>36519.06</v>
@@ -4487,12 +4537,12 @@
         <v>28934.91</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>155</v>
       </c>
       <c r="B151">
-        <v>36611.48</v>
+        <v>36611.480000000003</v>
       </c>
       <c r="C151">
         <v>37189.19</v>
@@ -4507,7 +4557,7 @@
         <v>32281.1</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>156</v>
       </c>
@@ -4515,7 +4565,7 @@
         <v>37271.17</v>
       </c>
       <c r="C152">
-        <v>37645.09</v>
+        <v>37645.089999999997</v>
       </c>
       <c r="D152">
         <v>36989.75</v>
@@ -4527,7 +4577,7 @@
         <v>32187.72</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>157</v>
       </c>
@@ -4547,7 +4597,7 @@
         <v>31965.5</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>158</v>
       </c>
@@ -4555,10 +4605,10 @@
         <v>36976.32</v>
       </c>
       <c r="C154">
-        <v>37153.95</v>
+        <v>37153.949999999997</v>
       </c>
       <c r="D154">
-        <v>36708.34</v>
+        <v>36708.339999999997</v>
       </c>
       <c r="E154">
         <v>37090.94</v>
@@ -4567,15 +4617,15 @@
         <v>21699.79</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>159</v>
       </c>
       <c r="B155">
-        <v>37065.8</v>
+        <v>37065.800000000003</v>
       </c>
       <c r="C155">
-        <v>37809.73</v>
+        <v>37809.730000000003</v>
       </c>
       <c r="D155">
         <v>36905.18</v>
@@ -4587,7 +4637,7 @@
         <v>23148.48</v>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>160</v>
       </c>
@@ -4601,38 +4651,38 @@
         <v>36762.86</v>
       </c>
       <c r="E156">
-        <v>36884.24</v>
+        <v>36884.239999999998</v>
       </c>
       <c r="F156">
         <v>31925.9</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>161</v>
       </c>
       <c r="B157">
-        <v>36723.66</v>
+        <v>36723.660000000003</v>
       </c>
       <c r="C157">
         <v>37145.29</v>
       </c>
       <c r="D157">
-        <v>36453.09</v>
+        <v>36453.089999999997</v>
       </c>
       <c r="E157">
-        <v>36753.59</v>
+        <v>36753.589999999997</v>
       </c>
       <c r="F157">
         <v>20756.71</v>
       </c>
     </row>
-    <row r="158" spans="1:6">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>162</v>
       </c>
       <c r="B158">
-        <v>37173.91</v>
+        <v>37173.910000000003</v>
       </c>
       <c r="C158">
         <v>37822.68</v>
@@ -4641,13 +4691,13 @@
         <v>36994.97</v>
       </c>
       <c r="E158">
-        <v>37215.73</v>
+        <v>37215.730000000003</v>
       </c>
       <c r="F158">
         <v>27134.57</v>
       </c>
     </row>
-    <row r="159" spans="1:6">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>163</v>
       </c>
@@ -4658,21 +4708,21 @@
         <v>37581.22</v>
       </c>
       <c r="D159">
-        <v>36653.16</v>
+        <v>36653.160000000003</v>
       </c>
       <c r="E159">
         <v>37208.5</v>
       </c>
       <c r="F159">
-        <v>30049.44</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
+        <v>30049.439999999999</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>164</v>
       </c>
       <c r="B160">
-        <v>37462.16</v>
+        <v>37462.160000000003</v>
       </c>
       <c r="C160">
         <v>37546.25</v>
@@ -4681,18 +4731,18 @@
         <v>37291.08</v>
       </c>
       <c r="E160">
-        <v>37473.55</v>
+        <v>37473.550000000003</v>
       </c>
       <c r="F160">
         <v>22944.89</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>165</v>
       </c>
       <c r="B161">
-        <v>37729.52</v>
+        <v>37729.519999999997</v>
       </c>
       <c r="C161">
         <v>38143.26</v>
@@ -4707,7 +4757,7 @@
         <v>21681.45</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>166</v>
       </c>
@@ -4715,7 +4765,7 @@
         <v>37897.11</v>
       </c>
       <c r="C162">
-        <v>38332.63</v>
+        <v>38332.629999999997</v>
       </c>
       <c r="D162">
         <v>37471.81</v>
@@ -4724,10 +4774,10 @@
         <v>38184.04</v>
       </c>
       <c r="F162">
-        <v>33248.34</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6">
+        <v>33248.339999999997</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>167</v>
       </c>
@@ -4741,21 +4791,21 @@
         <v>37560.78</v>
       </c>
       <c r="E163">
-        <v>37764.72</v>
+        <v>37764.720000000001</v>
       </c>
       <c r="F163">
         <v>31030.47</v>
       </c>
     </row>
-    <row r="164" spans="1:6">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>168</v>
       </c>
       <c r="B164">
-        <v>38395.23</v>
+        <v>38395.230000000003</v>
       </c>
       <c r="C164">
-        <v>38448.08</v>
+        <v>38448.080000000002</v>
       </c>
       <c r="D164">
         <v>37657.24</v>
@@ -4764,10 +4814,10 @@
         <v>38446.46</v>
       </c>
       <c r="F164">
-        <v>20682.81</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6">
+        <v>20682.810000000001</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>169</v>
       </c>
@@ -4787,7 +4837,7 @@
         <v>29262.1</v>
       </c>
     </row>
-    <row r="166" spans="1:6">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>170</v>
       </c>
@@ -4795,10 +4845,10 @@
         <v>38440.29</v>
       </c>
       <c r="C166">
-        <v>38827.12</v>
+        <v>38827.120000000003</v>
       </c>
       <c r="D166">
-        <v>38134.38</v>
+        <v>38134.379999999997</v>
       </c>
       <c r="E166">
         <v>38208.57</v>
@@ -4807,15 +4857,15 @@
         <v>28871.14</v>
       </c>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>171</v>
       </c>
       <c r="B167">
-        <v>38009.73</v>
+        <v>38009.730000000003</v>
       </c>
       <c r="C167">
-        <v>38284.98</v>
+        <v>38284.980000000003</v>
       </c>
       <c r="D167">
         <v>37478.07</v>
@@ -4827,12 +4877,12 @@
         <v>12691.34</v>
       </c>
     </row>
-    <row r="168" spans="1:6">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>172</v>
       </c>
       <c r="B168">
-        <v>37826.48</v>
+        <v>37826.480000000003</v>
       </c>
       <c r="C168">
         <v>38327.57</v>
@@ -4847,7 +4897,7 @@
         <v>26439.52</v>
       </c>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>173</v>
       </c>
@@ -4855,7 +4905,7 @@
         <v>37950.33</v>
       </c>
       <c r="C169">
-        <v>38170.88</v>
+        <v>38170.879999999997</v>
       </c>
       <c r="D169">
         <v>37563.24</v>
@@ -4867,7 +4917,7 @@
         <v>13660.85</v>
       </c>
     </row>
-    <row r="170" spans="1:6">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>174</v>
       </c>
@@ -4884,10 +4934,10 @@
         <v>38421.61</v>
       </c>
       <c r="F170">
-        <v>9191.309999999999</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6">
+        <v>9191.31</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>175</v>
       </c>
@@ -4901,13 +4951,13 @@
         <v>37959.18</v>
       </c>
       <c r="E171">
-        <v>38697.04</v>
+        <v>38697.040000000001</v>
       </c>
       <c r="F171">
         <v>34390.17</v>
       </c>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>176</v>
       </c>
@@ -4915,7 +4965,7 @@
         <v>38828.5</v>
       </c>
       <c r="C172">
-        <v>39093.38</v>
+        <v>39093.379999999997</v>
       </c>
       <c r="D172">
         <v>38727.49</v>
@@ -4924,15 +4974,15 @@
         <v>38789.46</v>
       </c>
       <c r="F172">
-        <v>41425.84</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6">
+        <v>41425.839999999997</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>177</v>
       </c>
       <c r="B173">
-        <v>39140.23</v>
+        <v>39140.230000000003</v>
       </c>
       <c r="C173">
         <v>39535.42</v>
@@ -4941,18 +4991,18 @@
         <v>38800.46</v>
       </c>
       <c r="E173">
-        <v>39462.52</v>
+        <v>39462.519999999997</v>
       </c>
       <c r="F173">
         <v>17444.93</v>
       </c>
     </row>
-    <row r="174" spans="1:6">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>178</v>
       </c>
       <c r="B174">
-        <v>39649.41</v>
+        <v>39649.410000000003</v>
       </c>
       <c r="C174">
         <v>39832.06</v>
@@ -4961,13 +5011,13 @@
         <v>39071.94</v>
       </c>
       <c r="E174">
-        <v>39311.6</v>
+        <v>39311.599999999999</v>
       </c>
       <c r="F174">
         <v>14176.43</v>
       </c>
     </row>
-    <row r="175" spans="1:6">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>179</v>
       </c>
@@ -4975,10 +5025,10 @@
         <v>39464.47</v>
       </c>
       <c r="C175">
-        <v>39792.2</v>
+        <v>39792.199999999997</v>
       </c>
       <c r="D175">
-        <v>38863.28</v>
+        <v>38863.279999999999</v>
       </c>
       <c r="E175">
         <v>39782.65</v>
@@ -4987,7 +5037,7 @@
         <v>27565.46</v>
       </c>
     </row>
-    <row r="176" spans="1:6">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>180</v>
       </c>
@@ -5007,15 +5057,15 @@
         <v>14185.1</v>
       </c>
     </row>
-    <row r="177" spans="1:6">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>181</v>
       </c>
       <c r="B177">
-        <v>40062.12</v>
+        <v>40062.120000000003</v>
       </c>
       <c r="C177">
-        <v>40392.87</v>
+        <v>40392.870000000003</v>
       </c>
       <c r="D177">
         <v>39353.65</v>
@@ -5024,10 +5074,10 @@
         <v>40320.54</v>
       </c>
       <c r="F177">
-        <v>24597.04</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6">
+        <v>24597.040000000001</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>182</v>
       </c>
@@ -5035,10 +5085,10 @@
         <v>40462.89</v>
       </c>
       <c r="C178">
-        <v>40981.66</v>
+        <v>40981.660000000003</v>
       </c>
       <c r="D178">
-        <v>40092.24</v>
+        <v>40092.239999999998</v>
       </c>
       <c r="E178">
         <v>40286.49</v>
@@ -5047,7 +5097,7 @@
         <v>25051.16</v>
       </c>
     </row>
-    <row r="179" spans="1:6">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>183</v>
       </c>
@@ -5058,7 +5108,7 @@
         <v>40334.11</v>
       </c>
       <c r="D179">
-        <v>40036.2</v>
+        <v>40036.199999999997</v>
       </c>
       <c r="E179">
         <v>40176.01</v>
@@ -5067,7 +5117,7 @@
         <v>27992.39</v>
       </c>
     </row>
-    <row r="180" spans="1:6">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>184</v>
       </c>
@@ -5087,7 +5137,7 @@
         <v>17173.36</v>
       </c>
     </row>
-    <row r="181" spans="1:6">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>185</v>
       </c>
@@ -5101,13 +5151,13 @@
         <v>41057.79</v>
       </c>
       <c r="E181">
-        <v>41335.76</v>
+        <v>41335.760000000002</v>
       </c>
       <c r="F181">
         <v>26651.25</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>186</v>
       </c>
@@ -5118,21 +5168,21 @@
         <v>41856.47</v>
       </c>
       <c r="D182">
-        <v>41013.02</v>
+        <v>41013.019999999997</v>
       </c>
       <c r="E182">
         <v>41664.49</v>
       </c>
       <c r="F182">
-        <v>24286.64</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6">
+        <v>24286.639999999999</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>187</v>
       </c>
       <c r="B183">
-        <v>41317.02</v>
+        <v>41317.019999999997</v>
       </c>
       <c r="C183">
         <v>41696.67</v>
@@ -5147,7 +5197,7 @@
         <v>32721.21</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>188</v>
       </c>
@@ -5161,13 +5211,13 @@
         <v>40700.14</v>
       </c>
       <c r="E184">
-        <v>40741.09</v>
+        <v>40741.089999999997</v>
       </c>
       <c r="F184">
-        <v>20199.69</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6">
+        <v>20199.689999999999</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>189</v>
       </c>
@@ -5178,7 +5228,7 @@
         <v>41007.71</v>
       </c>
       <c r="D185">
-        <v>40550.62</v>
+        <v>40550.620000000003</v>
       </c>
       <c r="E185">
         <v>40921.57</v>
@@ -5187,15 +5237,15 @@
         <v>12851.98</v>
       </c>
     </row>
-    <row r="186" spans="1:6">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>190</v>
       </c>
       <c r="B186">
-        <v>40867.95</v>
+        <v>40867.949999999997</v>
       </c>
       <c r="C186">
-        <v>41187.05</v>
+        <v>41187.050000000003</v>
       </c>
       <c r="D186">
         <v>40399.68</v>
@@ -5207,27 +5257,27 @@
         <v>30368.03</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>191</v>
       </c>
       <c r="B187">
-        <v>40322.62</v>
+        <v>40322.620000000003</v>
       </c>
       <c r="C187">
         <v>40866.35</v>
       </c>
       <c r="D187">
-        <v>40280.91</v>
+        <v>40280.910000000003</v>
       </c>
       <c r="E187">
         <v>40345.67</v>
       </c>
       <c r="F187">
-        <v>37089.91</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6">
+        <v>37089.910000000003</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>192</v>
       </c>
@@ -5247,7 +5297,7 @@
         <v>26558.32</v>
       </c>
     </row>
-    <row r="189" spans="1:6">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>193</v>
       </c>
@@ -5255,7 +5305,7 @@
         <v>40058.99</v>
       </c>
       <c r="C189">
-        <v>40495.44</v>
+        <v>40495.440000000002</v>
       </c>
       <c r="D189">
         <v>39494.51</v>
@@ -5267,7 +5317,7 @@
         <v>27256.86</v>
       </c>
     </row>
-    <row r="190" spans="1:6">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>194</v>
       </c>
@@ -5275,19 +5325,19 @@
         <v>40223.75</v>
       </c>
       <c r="C190">
-        <v>40664.63</v>
+        <v>40664.629999999997</v>
       </c>
       <c r="D190">
-        <v>39837.23</v>
+        <v>39837.230000000003</v>
       </c>
       <c r="E190">
-        <v>39969.36</v>
+        <v>39969.360000000001</v>
       </c>
       <c r="F190">
         <v>35669.51</v>
       </c>
     </row>
-    <row r="191" spans="1:6">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>195</v>
       </c>
@@ -5295,10 +5345,10 @@
         <v>40291.56</v>
       </c>
       <c r="C191">
-        <v>40545.16</v>
+        <v>40545.160000000003</v>
       </c>
       <c r="D191">
-        <v>39564.96</v>
+        <v>39564.959999999999</v>
       </c>
       <c r="E191">
         <v>40468.53</v>
@@ -5307,27 +5357,27 @@
         <v>12940.58</v>
       </c>
     </row>
-    <row r="192" spans="1:6">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>196</v>
       </c>
       <c r="B192">
-        <v>40676.96</v>
+        <v>40676.959999999999</v>
       </c>
       <c r="C192">
-        <v>40710.2</v>
+        <v>40710.199999999997</v>
       </c>
       <c r="D192">
-        <v>40433.7</v>
+        <v>40433.699999999997</v>
       </c>
       <c r="E192">
-        <v>40547.13</v>
+        <v>40547.129999999997</v>
       </c>
       <c r="F192">
         <v>29427.38</v>
       </c>
     </row>
-    <row r="193" spans="1:6">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>197</v>
       </c>
@@ -5335,10 +5385,10 @@
         <v>40480.68</v>
       </c>
       <c r="C193">
-        <v>40976.48</v>
+        <v>40976.480000000003</v>
       </c>
       <c r="D193">
-        <v>40002.8</v>
+        <v>40002.800000000003</v>
       </c>
       <c r="E193">
         <v>40408.35</v>
@@ -5347,7 +5397,7 @@
         <v>22045.48</v>
       </c>
     </row>
-    <row r="194" spans="1:6">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>198</v>
       </c>
@@ -5361,18 +5411,18 @@
         <v>40131.9</v>
       </c>
       <c r="E194">
-        <v>40575.88</v>
+        <v>40575.879999999997</v>
       </c>
       <c r="F194">
         <v>28741.38</v>
       </c>
     </row>
-    <row r="195" spans="1:6">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>199</v>
       </c>
       <c r="B195">
-        <v>40072.52</v>
+        <v>40072.519999999997</v>
       </c>
       <c r="C195">
         <v>40519.47</v>
@@ -5381,24 +5431,24 @@
         <v>39922.46</v>
       </c>
       <c r="E195">
-        <v>40027.63</v>
+        <v>40027.629999999997</v>
       </c>
       <c r="F195">
         <v>15773.57</v>
       </c>
     </row>
-    <row r="196" spans="1:6">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>200</v>
       </c>
       <c r="B196">
-        <v>40236.24</v>
+        <v>40236.239999999998</v>
       </c>
       <c r="C196">
         <v>40599.24</v>
       </c>
       <c r="D196">
-        <v>39963.76</v>
+        <v>39963.760000000002</v>
       </c>
       <c r="E196">
         <v>40315.08</v>
@@ -5407,7 +5457,7 @@
         <v>24900.11</v>
       </c>
     </row>
-    <row r="197" spans="1:6">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>201</v>
       </c>
@@ -5421,13 +5471,13 @@
         <v>39622.9</v>
       </c>
       <c r="E197">
-        <v>39905.41</v>
+        <v>39905.410000000003</v>
       </c>
       <c r="F197">
         <v>29363.41</v>
       </c>
     </row>
-    <row r="198" spans="1:6">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>202</v>
       </c>
@@ -5435,7 +5485,7 @@
         <v>39751.85</v>
       </c>
       <c r="C198">
-        <v>40250.88</v>
+        <v>40250.879999999997</v>
       </c>
       <c r="D198">
         <v>39702.21</v>
@@ -5447,7 +5497,7 @@
         <v>25335.87</v>
       </c>
     </row>
-    <row r="199" spans="1:6">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>203</v>
       </c>
@@ -5461,13 +5511,13 @@
         <v>39449.29</v>
       </c>
       <c r="E199">
-        <v>40143.59</v>
+        <v>40143.589999999997</v>
       </c>
       <c r="F199">
         <v>25967.68</v>
       </c>
     </row>
-    <row r="200" spans="1:6">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>204</v>
       </c>
@@ -5475,10 +5525,10 @@
         <v>40323.9</v>
       </c>
       <c r="C200">
-        <v>41022.77</v>
+        <v>41022.769999999997</v>
       </c>
       <c r="D200">
-        <v>39890.12</v>
+        <v>39890.120000000003</v>
       </c>
       <c r="E200">
         <v>39962.17</v>
@@ -5487,7 +5537,7 @@
         <v>28930.63</v>
       </c>
     </row>
-    <row r="201" spans="1:6">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>205</v>
       </c>
@@ -5495,7 +5545,7 @@
         <v>40652.28</v>
       </c>
       <c r="C201">
-        <v>40858.2</v>
+        <v>40858.199999999997</v>
       </c>
       <c r="D201">
         <v>40591.82</v>
@@ -5507,12 +5557,12 @@
         <v>22224.3</v>
       </c>
     </row>
-    <row r="202" spans="1:6">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>206</v>
       </c>
       <c r="B202">
-        <v>40502.95</v>
+        <v>40502.949999999997</v>
       </c>
       <c r="C202">
         <v>41159.17</v>
@@ -5521,13 +5571,13 @@
         <v>40109.58</v>
       </c>
       <c r="E202">
-        <v>40444.84</v>
+        <v>40444.839999999997</v>
       </c>
       <c r="F202">
         <v>24915.93</v>
       </c>
     </row>
-    <row r="203" spans="1:6">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>207</v>
       </c>
@@ -5538,7 +5588,7 @@
         <v>41251.46</v>
       </c>
       <c r="D203">
-        <v>40382.02</v>
+        <v>40382.019999999997</v>
       </c>
       <c r="E203">
         <v>40746.22</v>
@@ -5547,7 +5597,7 @@
         <v>16107.39</v>
       </c>
     </row>
-    <row r="204" spans="1:6">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>208</v>
       </c>
@@ -5567,7 +5617,7 @@
         <v>21287.9</v>
       </c>
     </row>
-    <row r="205" spans="1:6">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>209</v>
       </c>
@@ -5587,27 +5637,27 @@
         <v>11358.37</v>
       </c>
     </row>
-    <row r="206" spans="1:6">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>210</v>
       </c>
       <c r="B206">
-        <v>40725.16</v>
+        <v>40725.160000000003</v>
       </c>
       <c r="C206">
         <v>41331.74</v>
       </c>
       <c r="D206">
-        <v>40028.72</v>
+        <v>40028.720000000001</v>
       </c>
       <c r="E206">
-        <v>40778.2</v>
+        <v>40778.199999999997</v>
       </c>
       <c r="F206">
         <v>24312.1</v>
       </c>
     </row>
-    <row r="207" spans="1:6">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>211</v>
       </c>
@@ -5627,12 +5677,12 @@
         <v>24662.49</v>
       </c>
     </row>
-    <row r="208" spans="1:6">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>212</v>
       </c>
       <c r="B208">
-        <v>41807.23</v>
+        <v>41807.230000000003</v>
       </c>
       <c r="C208">
         <v>42059.22</v>
@@ -5641,21 +5691,21 @@
         <v>41225.78</v>
       </c>
       <c r="E208">
-        <v>41761.28</v>
+        <v>41761.279999999999</v>
       </c>
       <c r="F208">
         <v>23956.55</v>
       </c>
     </row>
-    <row r="209" spans="1:6">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>213</v>
       </c>
       <c r="B209">
-        <v>41191.63</v>
+        <v>41191.629999999997</v>
       </c>
       <c r="C209">
-        <v>41831.92</v>
+        <v>41831.919999999998</v>
       </c>
       <c r="D209">
         <v>40864.86</v>
@@ -5664,10 +5714,10 @@
         <v>41170.07</v>
       </c>
       <c r="F209">
-        <v>18662.69</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6">
+        <v>18662.689999999999</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>214</v>
       </c>
@@ -5681,13 +5731,13 @@
         <v>40546.01</v>
       </c>
       <c r="E210">
-        <v>41151.48</v>
+        <v>41151.480000000003</v>
       </c>
       <c r="F210">
         <v>21278.79</v>
       </c>
     </row>
-    <row r="211" spans="1:6">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>215</v>
       </c>
@@ -5698,21 +5748,21 @@
         <v>41329.58</v>
       </c>
       <c r="D211">
-        <v>41042.8</v>
+        <v>41042.800000000003</v>
       </c>
       <c r="E211">
-        <v>41293.12</v>
+        <v>41293.120000000003</v>
       </c>
       <c r="F211">
         <v>14523.5</v>
       </c>
     </row>
-    <row r="212" spans="1:6">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
         <v>216</v>
       </c>
       <c r="B212">
-        <v>41078.91</v>
+        <v>41078.910000000003</v>
       </c>
       <c r="C212">
         <v>41492.9</v>
@@ -5727,7 +5777,7 @@
         <v>20074.43</v>
       </c>
     </row>
-    <row r="213" spans="1:6">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
         <v>217</v>
       </c>
@@ -5744,15 +5794,15 @@
         <v>41498.74</v>
       </c>
       <c r="F213">
-        <v>57536.8</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6">
+        <v>57536.800000000003</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
         <v>218</v>
       </c>
       <c r="B214">
-        <v>41573.28</v>
+        <v>41573.279999999999</v>
       </c>
       <c r="C214">
         <v>41780.82</v>
@@ -5761,13 +5811,13 @@
         <v>40967.78</v>
       </c>
       <c r="E214">
-        <v>41505.37</v>
+        <v>41505.370000000003</v>
       </c>
       <c r="F214">
         <v>27260.3</v>
       </c>
     </row>
-    <row r="215" spans="1:6">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
         <v>219</v>
       </c>
@@ -5781,13 +5831,13 @@
         <v>41143.64</v>
       </c>
       <c r="E215">
-        <v>41695.12</v>
+        <v>41695.120000000003</v>
       </c>
       <c r="F215">
-        <v>19972.51</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6">
+        <v>19972.509999999998</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
         <v>220</v>
       </c>
@@ -5804,21 +5854,21 @@
         <v>41799.33</v>
       </c>
       <c r="F216">
-        <v>34072.62</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6">
+        <v>34072.620000000003</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
         <v>221</v>
       </c>
       <c r="B217">
-        <v>41822.72</v>
+        <v>41822.720000000001</v>
       </c>
       <c r="C217">
         <v>42194.32</v>
       </c>
       <c r="D217">
-        <v>41347.76</v>
+        <v>41347.760000000002</v>
       </c>
       <c r="E217">
         <v>41781.42</v>
@@ -5827,7 +5877,7 @@
         <v>30854.97</v>
       </c>
     </row>
-    <row r="218" spans="1:6">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
         <v>222</v>
       </c>
@@ -5847,7 +5897,7 @@
         <v>25639.64</v>
       </c>
     </row>
-    <row r="219" spans="1:6">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>223</v>
       </c>
@@ -5867,7 +5917,7 @@
         <v>23925.77</v>
       </c>
     </row>
-    <row r="220" spans="1:6">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>224</v>
       </c>
@@ -5887,7 +5937,7 @@
         <v>21820.42</v>
       </c>
     </row>
-    <row r="221" spans="1:6">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
         <v>225</v>
       </c>
@@ -5898,7 +5948,7 @@
         <v>42661.61</v>
       </c>
       <c r="D221">
-        <v>42318.88</v>
+        <v>42318.879999999997</v>
       </c>
       <c r="E221">
         <v>42323.23</v>
@@ -5907,12 +5957,12 @@
         <v>16933.78</v>
       </c>
     </row>
-    <row r="222" spans="1:6">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
         <v>226</v>
       </c>
       <c r="B222">
-        <v>41604.59</v>
+        <v>41604.589999999997</v>
       </c>
       <c r="C222">
         <v>41763.9</v>
@@ -5921,13 +5971,13 @@
         <v>41336.65</v>
       </c>
       <c r="E222">
-        <v>41349.73</v>
+        <v>41349.730000000003</v>
       </c>
       <c r="F222">
         <v>22039</v>
       </c>
     </row>
-    <row r="223" spans="1:6">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
         <v>227</v>
       </c>
@@ -5944,10 +5994,10 @@
         <v>42170.97</v>
       </c>
       <c r="F223">
-        <v>37157.88</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6">
+        <v>37157.879999999997</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
         <v>228</v>
       </c>
@@ -5967,7 +6017,7 @@
         <v>14741.85</v>
       </c>
     </row>
-    <row r="225" spans="1:6">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
         <v>229</v>
       </c>
@@ -5987,12 +6037,12 @@
         <v>24463.86</v>
       </c>
     </row>
-    <row r="226" spans="1:6">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
         <v>230</v>
       </c>
       <c r="B226">
-        <v>41758.45</v>
+        <v>41758.449999999997</v>
       </c>
       <c r="C226">
         <v>42105.24</v>
@@ -6007,18 +6057,18 @@
         <v>27935.58</v>
       </c>
     </row>
-    <row r="227" spans="1:6">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
         <v>231</v>
       </c>
       <c r="B227">
-        <v>41608.05</v>
+        <v>41608.050000000003</v>
       </c>
       <c r="C227">
-        <v>41744.02</v>
+        <v>41744.019999999997</v>
       </c>
       <c r="D227">
-        <v>40955.34</v>
+        <v>40955.339999999997</v>
       </c>
       <c r="E227">
         <v>40985.32</v>
@@ -6027,7 +6077,7 @@
         <v>25520.81</v>
       </c>
     </row>
-    <row r="228" spans="1:6">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
         <v>232</v>
       </c>
@@ -6038,7 +6088,7 @@
         <v>41556.94</v>
       </c>
       <c r="D228">
-        <v>40865.84</v>
+        <v>40865.839999999997</v>
       </c>
       <c r="E228">
         <v>40973.54</v>
@@ -6047,12 +6097,12 @@
         <v>17824.5</v>
       </c>
     </row>
-    <row r="229" spans="1:6">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
         <v>233</v>
       </c>
       <c r="B229">
-        <v>41011.59</v>
+        <v>41011.589999999997</v>
       </c>
       <c r="C229">
         <v>41226.26</v>
@@ -6061,18 +6111,18 @@
         <v>40798.07</v>
       </c>
       <c r="E229">
-        <v>41065.38</v>
+        <v>41065.379999999997</v>
       </c>
       <c r="F229">
         <v>7305.98</v>
       </c>
     </row>
-    <row r="230" spans="1:6">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>234</v>
       </c>
       <c r="B230">
-        <v>41397.36</v>
+        <v>41397.360000000001</v>
       </c>
       <c r="C230">
         <v>42056.38</v>
@@ -6081,53 +6131,53 @@
         <v>40898.43</v>
       </c>
       <c r="E230">
-        <v>41173.98</v>
+        <v>41173.980000000003</v>
       </c>
       <c r="F230">
         <v>28675.78</v>
       </c>
     </row>
-    <row r="231" spans="1:6">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
         <v>235</v>
       </c>
       <c r="B231">
-        <v>40956.09</v>
+        <v>40956.089999999997</v>
       </c>
       <c r="C231">
         <v>41125.97</v>
       </c>
       <c r="D231">
-        <v>40361.12</v>
+        <v>40361.120000000003</v>
       </c>
       <c r="E231">
-        <v>40421.98</v>
+        <v>40421.980000000003</v>
       </c>
       <c r="F231">
         <v>11859.56</v>
       </c>
     </row>
-    <row r="232" spans="1:6">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
         <v>236</v>
       </c>
       <c r="B232">
-        <v>40421.76</v>
+        <v>40421.760000000002</v>
       </c>
       <c r="C232">
-        <v>41014.88</v>
+        <v>41014.879999999997</v>
       </c>
       <c r="D232">
-        <v>40279.28</v>
+        <v>40279.279999999999</v>
       </c>
       <c r="E232">
-        <v>40305.8</v>
+        <v>40305.800000000003</v>
       </c>
       <c r="F232">
         <v>29341.13</v>
       </c>
     </row>
-    <row r="233" spans="1:6">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
         <v>237</v>
       </c>
@@ -6138,7 +6188,7 @@
         <v>41328.57</v>
       </c>
       <c r="D233">
-        <v>40253.38</v>
+        <v>40253.379999999997</v>
       </c>
       <c r="E233">
         <v>40950.14</v>
@@ -6147,7 +6197,7 @@
         <v>24336.06</v>
       </c>
     </row>
-    <row r="234" spans="1:6">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
         <v>238</v>
       </c>
@@ -6158,7 +6208,7 @@
         <v>41518.97</v>
       </c>
       <c r="D234">
-        <v>41047.88</v>
+        <v>41047.879999999997</v>
       </c>
       <c r="E234">
         <v>41148.44</v>
@@ -6167,7 +6217,7 @@
         <v>21952.21</v>
       </c>
     </row>
-    <row r="235" spans="1:6">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
         <v>239</v>
       </c>
@@ -6178,16 +6228,16 @@
         <v>41596.82</v>
       </c>
       <c r="D235">
-        <v>40533.12</v>
+        <v>40533.120000000003</v>
       </c>
       <c r="E235">
-        <v>40538.48</v>
+        <v>40538.480000000003</v>
       </c>
       <c r="F235">
         <v>30390.21</v>
       </c>
     </row>
-    <row r="236" spans="1:6">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
         <v>240</v>
       </c>
@@ -6195,19 +6245,19 @@
         <v>40702.28</v>
       </c>
       <c r="C236">
-        <v>40886.8</v>
+        <v>40886.800000000003</v>
       </c>
       <c r="D236">
-        <v>40127.13</v>
+        <v>40127.129999999997</v>
       </c>
       <c r="E236">
-        <v>40598.45</v>
+        <v>40598.449999999997</v>
       </c>
       <c r="F236">
         <v>36493.58</v>
       </c>
     </row>
-    <row r="237" spans="1:6">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
         <v>241</v>
       </c>
@@ -6227,15 +6277,15 @@
         <v>27943.62</v>
       </c>
     </row>
-    <row r="238" spans="1:6">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
         <v>242</v>
       </c>
       <c r="B238">
-        <v>40426.77</v>
+        <v>40426.769999999997</v>
       </c>
       <c r="C238">
-        <v>40878.37</v>
+        <v>40878.370000000003</v>
       </c>
       <c r="D238">
         <v>39702.01</v>
@@ -6247,7 +6297,7 @@
         <v>33202.44</v>
       </c>
     </row>
-    <row r="239" spans="1:6">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
         <v>243</v>
       </c>
@@ -6258,16 +6308,16 @@
         <v>40827.83</v>
       </c>
       <c r="D239">
-        <v>39541.41</v>
+        <v>39541.410000000003</v>
       </c>
       <c r="E239">
         <v>40419.06</v>
       </c>
       <c r="F239">
-        <v>30874.08</v>
-      </c>
-    </row>
-    <row r="240" spans="1:6">
+        <v>30874.080000000002</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
         <v>244</v>
       </c>
@@ -6275,24 +6325,24 @@
         <v>40608.86</v>
       </c>
       <c r="C240">
-        <v>41119.23</v>
+        <v>41119.230000000003</v>
       </c>
       <c r="D240">
         <v>40031</v>
       </c>
       <c r="E240">
-        <v>40393.62</v>
+        <v>40393.620000000003</v>
       </c>
       <c r="F240">
-        <v>18435.08</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6">
+        <v>18435.080000000002</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
         <v>245</v>
       </c>
       <c r="B241">
-        <v>40554.52</v>
+        <v>40554.519999999997</v>
       </c>
       <c r="C241">
         <v>40930.76</v>
@@ -6301,18 +6351,18 @@
         <v>40258.28</v>
       </c>
       <c r="E241">
-        <v>40750.41</v>
+        <v>40750.410000000003</v>
       </c>
       <c r="F241">
         <v>17896.78</v>
       </c>
     </row>
-    <row r="242" spans="1:6">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
         <v>246</v>
       </c>
       <c r="B242">
-        <v>40460.4</v>
+        <v>40460.400000000001</v>
       </c>
       <c r="C242">
         <v>40825.74</v>
@@ -6327,7 +6377,7 @@
         <v>19638.47</v>
       </c>
     </row>
-    <row r="243" spans="1:6">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
         <v>247</v>
       </c>
@@ -6338,7 +6388,7 @@
         <v>40955.17</v>
       </c>
       <c r="D243">
-        <v>40216.84</v>
+        <v>40216.839999999997</v>
       </c>
       <c r="E243">
         <v>40261.72</v>
@@ -6347,7 +6397,7 @@
         <v>15058.28</v>
       </c>
     </row>
-    <row r="244" spans="1:6">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
         <v>248</v>
       </c>
@@ -6367,7 +6417,7 @@
         <v>15030.54</v>
       </c>
     </row>
-    <row r="245" spans="1:6">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
         <v>249</v>
       </c>
@@ -6375,19 +6425,19 @@
         <v>39549.39</v>
       </c>
       <c r="C245">
-        <v>39783.13</v>
+        <v>39783.129999999997</v>
       </c>
       <c r="D245">
         <v>39185.82</v>
       </c>
       <c r="E245">
-        <v>39320.3</v>
+        <v>39320.300000000003</v>
       </c>
       <c r="F245">
         <v>22813.03</v>
       </c>
     </row>
-    <row r="246" spans="1:6">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
         <v>250</v>
       </c>
@@ -6401,13 +6451,13 @@
         <v>38893.19</v>
       </c>
       <c r="E246">
-        <v>39253.36</v>
+        <v>39253.360000000001</v>
       </c>
       <c r="F246">
         <v>14584.97</v>
       </c>
     </row>
-    <row r="247" spans="1:6">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
         <v>251</v>
       </c>
@@ -6415,30 +6465,30 @@
         <v>39411.03</v>
       </c>
       <c r="C247">
-        <v>40255.09</v>
+        <v>40255.089999999997</v>
       </c>
       <c r="D247">
-        <v>38949.3</v>
+        <v>38949.300000000003</v>
       </c>
       <c r="E247">
         <v>39101.18</v>
       </c>
       <c r="F247">
-        <v>41579.45</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6">
+        <v>41579.449999999997</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
         <v>252</v>
       </c>
       <c r="B248">
-        <v>38664.45</v>
+        <v>38664.449999999997</v>
       </c>
       <c r="C248">
         <v>39350.67</v>
       </c>
       <c r="D248">
-        <v>38298.4</v>
+        <v>38298.400000000001</v>
       </c>
       <c r="E248">
         <v>38359.9</v>
@@ -6447,27 +6497,27 @@
         <v>30614.51</v>
       </c>
     </row>
-    <row r="249" spans="1:6">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
         <v>253</v>
       </c>
       <c r="B249">
-        <v>38138.63</v>
+        <v>38138.629999999997</v>
       </c>
       <c r="C249">
-        <v>38661.05</v>
+        <v>38661.050000000003</v>
       </c>
       <c r="D249">
         <v>37587.58</v>
       </c>
       <c r="E249">
-        <v>38529.09</v>
+        <v>38529.089999999997</v>
       </c>
       <c r="F249">
         <v>31245.72</v>
       </c>
     </row>
-    <row r="250" spans="1:6">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
         <v>254</v>
       </c>
@@ -6478,16 +6528,16 @@
         <v>38814.21</v>
       </c>
       <c r="D250">
-        <v>38093.62</v>
+        <v>38093.620000000003</v>
       </c>
       <c r="E250">
         <v>38696.25</v>
       </c>
       <c r="F250">
-        <v>24131.04</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6">
+        <v>24131.040000000001</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
         <v>255</v>
       </c>
@@ -6495,10 +6545,10 @@
         <v>39203.03</v>
       </c>
       <c r="C251">
-        <v>39765.66</v>
+        <v>39765.660000000003</v>
       </c>
       <c r="D251">
-        <v>38986.7</v>
+        <v>38986.699999999997</v>
       </c>
       <c r="E251">
         <v>39328.49</v>
@@ -6507,35 +6557,35 @@
         <v>21201.3</v>
       </c>
     </row>
-    <row r="252" spans="1:6">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
         <v>256</v>
       </c>
       <c r="B252">
-        <v>39131.7</v>
+        <v>39131.699999999997</v>
       </c>
       <c r="C252">
-        <v>39638.59</v>
+        <v>39638.589999999997</v>
       </c>
       <c r="D252">
-        <v>38806.55</v>
+        <v>38806.550000000003</v>
       </c>
       <c r="E252">
-        <v>39508.8</v>
+        <v>39508.800000000003</v>
       </c>
       <c r="F252">
-        <v>34232.73</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6">
+        <v>34232.730000000003</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
         <v>257</v>
       </c>
       <c r="B253">
-        <v>39581.23</v>
+        <v>39581.230000000003</v>
       </c>
       <c r="C253">
-        <v>39774.16</v>
+        <v>39774.160000000003</v>
       </c>
       <c r="D253">
         <v>39131.75</v>
@@ -6547,12 +6597,12 @@
         <v>15932.92</v>
       </c>
     </row>
-    <row r="254" spans="1:6">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
         <v>258</v>
       </c>
       <c r="B254">
-        <v>39435.91</v>
+        <v>39435.910000000003</v>
       </c>
       <c r="C254">
         <v>40046.97</v>
@@ -6561,13 +6611,13 @@
         <v>39044.01</v>
       </c>
       <c r="E254">
-        <v>39995.48</v>
+        <v>39995.480000000003</v>
       </c>
       <c r="F254">
         <v>18023.88</v>
       </c>
     </row>
-    <row r="255" spans="1:6">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
         <v>259</v>
       </c>
@@ -6578,7 +6628,7 @@
         <v>40513.4</v>
       </c>
       <c r="D255">
-        <v>40090.27</v>
+        <v>40090.269999999997</v>
       </c>
       <c r="E255">
         <v>40127.07</v>
@@ -6587,7 +6637,7 @@
         <v>19325.89</v>
       </c>
     </row>
-    <row r="256" spans="1:6">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
         <v>260</v>
       </c>
@@ -6598,21 +6648,21 @@
         <v>40445.08</v>
       </c>
       <c r="D256">
-        <v>39263.98</v>
+        <v>39263.980000000003</v>
       </c>
       <c r="E256">
-        <v>39318.08</v>
+        <v>39318.080000000002</v>
       </c>
       <c r="F256">
         <v>13997.6</v>
       </c>
     </row>
-    <row r="257" spans="1:6">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
         <v>261</v>
       </c>
       <c r="B257">
-        <v>39199.59</v>
+        <v>39199.589999999997</v>
       </c>
       <c r="C257">
         <v>39679.93</v>
@@ -6627,15 +6677,15 @@
         <v>34353.15</v>
       </c>
     </row>
-    <row r="258" spans="1:6">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
         <v>262</v>
       </c>
       <c r="B258">
-        <v>38601.13</v>
+        <v>38601.129999999997</v>
       </c>
       <c r="C258">
-        <v>38885.87</v>
+        <v>38885.870000000003</v>
       </c>
       <c r="D258">
         <v>38407.5</v>
@@ -6647,12 +6697,12 @@
         <v>22703.65</v>
       </c>
     </row>
-    <row r="259" spans="1:6">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
         <v>263</v>
       </c>
       <c r="B259">
-        <v>38227.44</v>
+        <v>38227.440000000002</v>
       </c>
       <c r="C259">
         <v>38535.08</v>
@@ -6667,7 +6717,7 @@
         <v>32772.89</v>
       </c>
     </row>
-    <row r="260" spans="1:6">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
         <v>264</v>
       </c>
@@ -6687,12 +6737,12 @@
         <v>21013.89</v>
       </c>
     </row>
-    <row r="261" spans="1:6">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
         <v>265</v>
       </c>
       <c r="B261">
-        <v>38548.63</v>
+        <v>38548.629999999997</v>
       </c>
       <c r="C261">
         <v>38865.06</v>
@@ -6701,13 +6751,13 @@
         <v>38035.24</v>
       </c>
       <c r="E261">
-        <v>38166.64</v>
+        <v>38166.639999999999</v>
       </c>
       <c r="F261">
         <v>17832.82</v>
       </c>
     </row>
-    <row r="262" spans="1:6">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
         <v>266</v>
       </c>
@@ -6715,19 +6765,19 @@
         <v>37672.43</v>
       </c>
       <c r="C262">
-        <v>37821.37</v>
+        <v>37821.370000000003</v>
       </c>
       <c r="D262">
         <v>37314.54</v>
       </c>
       <c r="E262">
-        <v>37443.13</v>
+        <v>37443.129999999997</v>
       </c>
       <c r="F262">
         <v>26936.31</v>
       </c>
     </row>
-    <row r="263" spans="1:6">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
         <v>267</v>
       </c>
@@ -6738,16 +6788,16 @@
         <v>38088.94</v>
       </c>
       <c r="D263">
-        <v>37223.84</v>
+        <v>37223.839999999997</v>
       </c>
       <c r="E263">
         <v>37389.49</v>
       </c>
       <c r="F263">
-        <v>17731.1</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6">
+        <v>17731.099999999999</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
         <v>268</v>
       </c>
@@ -6767,12 +6817,12 @@
         <v>32548.85</v>
       </c>
     </row>
-    <row r="265" spans="1:6">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
         <v>269</v>
       </c>
       <c r="B265">
-        <v>37916.48</v>
+        <v>37916.480000000003</v>
       </c>
       <c r="C265">
         <v>38517.43</v>
@@ -6781,13 +6831,13 @@
         <v>37560.44</v>
       </c>
       <c r="E265">
-        <v>37990.96</v>
+        <v>37990.959999999999</v>
       </c>
       <c r="F265">
-        <v>37142.24</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6">
+        <v>37142.239999999998</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
         <v>270</v>
       </c>
@@ -6798,24 +6848,24 @@
         <v>37893.42</v>
       </c>
       <c r="D266">
-        <v>37263.98</v>
+        <v>37263.980000000003</v>
       </c>
       <c r="E266">
-        <v>37508.45</v>
+        <v>37508.449999999997</v>
       </c>
       <c r="F266">
-        <v>16491.56</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6">
+        <v>16491.560000000001</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
         <v>271</v>
       </c>
       <c r="B267">
-        <v>37267.59</v>
+        <v>37267.589999999997</v>
       </c>
       <c r="C267">
-        <v>37738.34</v>
+        <v>37738.339999999997</v>
       </c>
       <c r="D267">
         <v>37052.79</v>
@@ -6827,27 +6877,27 @@
         <v>23652.05</v>
       </c>
     </row>
-    <row r="268" spans="1:6">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
         <v>272</v>
       </c>
       <c r="B268">
-        <v>37285.45</v>
+        <v>37285.449999999997</v>
       </c>
       <c r="C268">
-        <v>37380.87</v>
+        <v>37380.870000000003</v>
       </c>
       <c r="D268">
-        <v>36526.12</v>
+        <v>36526.120000000003</v>
       </c>
       <c r="E268">
-        <v>36639.04</v>
+        <v>36639.040000000001</v>
       </c>
       <c r="F268">
         <v>23016.45</v>
       </c>
     </row>
-    <row r="269" spans="1:6">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
         <v>273</v>
       </c>
@@ -6867,27 +6917,27 @@
         <v>19259.21</v>
       </c>
     </row>
-    <row r="270" spans="1:6">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
         <v>274</v>
       </c>
       <c r="B270">
-        <v>35893.13</v>
+        <v>35893.129999999997</v>
       </c>
       <c r="C270">
         <v>36361.03</v>
       </c>
       <c r="D270">
-        <v>35621.7</v>
+        <v>35621.699999999997</v>
       </c>
       <c r="E270">
-        <v>35845.27</v>
+        <v>35845.269999999997</v>
       </c>
       <c r="F270">
         <v>28986.9</v>
       </c>
     </row>
-    <row r="271" spans="1:6">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
         <v>275</v>
       </c>
@@ -6898,7 +6948,7 @@
         <v>36546.54</v>
       </c>
       <c r="D271">
-        <v>35252.95</v>
+        <v>35252.949999999997</v>
       </c>
       <c r="E271">
         <v>36526.14</v>
@@ -6907,7 +6957,7 @@
         <v>31232.11</v>
       </c>
     </row>
-    <row r="272" spans="1:6">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
         <v>276</v>
       </c>
@@ -6915,7 +6965,7 @@
         <v>37040.03</v>
       </c>
       <c r="C272">
-        <v>37394.37</v>
+        <v>37394.370000000003</v>
       </c>
       <c r="D272">
         <v>36995.67</v>
@@ -6927,18 +6977,18 @@
         <v>25075.33</v>
       </c>
     </row>
-    <row r="273" spans="1:6">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
         <v>277</v>
       </c>
       <c r="B273">
-        <v>37579.73</v>
+        <v>37579.730000000003</v>
       </c>
       <c r="C273">
-        <v>38441.92</v>
+        <v>38441.919999999998</v>
       </c>
       <c r="D273">
-        <v>36944.48</v>
+        <v>36944.480000000003</v>
       </c>
       <c r="E273">
         <v>38013.96</v>
@@ -6947,7 +6997,7 @@
         <v>36243.74</v>
       </c>
     </row>
-    <row r="274" spans="1:6">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
         <v>278</v>
       </c>
@@ -6961,13 +7011,13 @@
         <v>37832.44</v>
       </c>
       <c r="E274">
-        <v>38425.59</v>
+        <v>38425.589999999997</v>
       </c>
       <c r="F274">
         <v>30036.7</v>
       </c>
     </row>
-    <row r="275" spans="1:6">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
         <v>279</v>
       </c>
@@ -6975,44 +7025,44 @@
         <v>38395.21</v>
       </c>
       <c r="C275">
-        <v>38764.77</v>
+        <v>38764.769999999997</v>
       </c>
       <c r="D275">
-        <v>37988.91</v>
+        <v>37988.910000000003</v>
       </c>
       <c r="E275">
-        <v>38662.13</v>
+        <v>38662.129999999997</v>
       </c>
       <c r="F275">
         <v>17914.71</v>
       </c>
     </row>
-    <row r="276" spans="1:6">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
         <v>280</v>
       </c>
       <c r="B276">
-        <v>38740.84</v>
+        <v>38740.839999999997</v>
       </c>
       <c r="C276">
-        <v>38962.37</v>
+        <v>38962.370000000003</v>
       </c>
       <c r="D276">
         <v>38484.19</v>
       </c>
       <c r="E276">
-        <v>38822.12</v>
+        <v>38822.120000000003</v>
       </c>
       <c r="F276">
-        <v>18795.92</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6">
+        <v>18795.919999999998</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
         <v>281</v>
       </c>
       <c r="B277">
-        <v>38240.64</v>
+        <v>38240.639999999999</v>
       </c>
       <c r="C277">
         <v>38561.33</v>
@@ -7021,24 +7071,24 @@
         <v>37795.21</v>
       </c>
       <c r="E277">
-        <v>38352.27</v>
+        <v>38352.269999999997</v>
       </c>
       <c r="F277">
         <v>29328.01</v>
       </c>
     </row>
-    <row r="278" spans="1:6">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
         <v>282</v>
       </c>
       <c r="B278">
-        <v>38408.63</v>
+        <v>38408.629999999997</v>
       </c>
       <c r="C278">
         <v>38741.71</v>
       </c>
       <c r="D278">
-        <v>37949.3</v>
+        <v>37949.300000000003</v>
       </c>
       <c r="E278">
         <v>38619.06</v>
@@ -7047,7 +7097,7 @@
         <v>20985.45</v>
       </c>
     </row>
-    <row r="279" spans="1:6">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
         <v>283</v>
       </c>
@@ -7061,21 +7111,21 @@
         <v>37674.82</v>
       </c>
       <c r="E279">
-        <v>38074.59</v>
+        <v>38074.589999999997</v>
       </c>
       <c r="F279">
-        <v>31836.08</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6">
+        <v>31836.080000000002</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
         <v>284</v>
       </c>
       <c r="B280">
-        <v>38604.91</v>
+        <v>38604.910000000003</v>
       </c>
       <c r="C280">
-        <v>38976.3</v>
+        <v>38976.300000000003</v>
       </c>
       <c r="D280">
         <v>38274.04</v>
@@ -7084,10 +7134,10 @@
         <v>38622.61</v>
       </c>
       <c r="F280">
-        <v>19486.74</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6">
+        <v>19486.740000000002</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
         <v>285</v>
       </c>
@@ -7095,30 +7145,30 @@
         <v>38571.65</v>
       </c>
       <c r="C281">
-        <v>39132.02</v>
+        <v>39132.019999999997</v>
       </c>
       <c r="D281">
         <v>38010.92</v>
       </c>
       <c r="E281">
-        <v>38977.05</v>
+        <v>38977.050000000003</v>
       </c>
       <c r="F281">
         <v>7096.72</v>
       </c>
     </row>
-    <row r="282" spans="1:6">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
         <v>286</v>
       </c>
       <c r="B282">
-        <v>39004.73</v>
+        <v>39004.730000000003</v>
       </c>
       <c r="C282">
         <v>39545.83</v>
       </c>
       <c r="D282">
-        <v>38311.27</v>
+        <v>38311.269999999997</v>
       </c>
       <c r="E282">
         <v>39260.61</v>
@@ -7127,7 +7177,7 @@
         <v>25028.65</v>
       </c>
     </row>
-    <row r="283" spans="1:6">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
         <v>287</v>
       </c>
@@ -7135,39 +7185,39 @@
         <v>38871.15</v>
       </c>
       <c r="C283">
-        <v>39317.44</v>
+        <v>39317.440000000002</v>
       </c>
       <c r="D283">
         <v>38358.44</v>
       </c>
       <c r="E283">
-        <v>39306.64</v>
+        <v>39306.639999999999</v>
       </c>
       <c r="F283">
         <v>14146.42</v>
       </c>
     </row>
-    <row r="284" spans="1:6">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
         <v>288</v>
       </c>
       <c r="B284">
-        <v>39376.37</v>
+        <v>39376.370000000003</v>
       </c>
       <c r="C284">
         <v>39511.93</v>
       </c>
       <c r="D284">
-        <v>38841.02</v>
+        <v>38841.019999999997</v>
       </c>
       <c r="E284">
-        <v>39317.34</v>
+        <v>39317.339999999997</v>
       </c>
       <c r="F284">
         <v>22078.99</v>
       </c>
     </row>
-    <row r="285" spans="1:6">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
         <v>289</v>
       </c>
@@ -7187,7 +7237,7 @@
         <v>13094.36</v>
       </c>
     </row>
-    <row r="286" spans="1:6">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
         <v>290</v>
       </c>
@@ -7195,24 +7245,24 @@
         <v>39770.18</v>
       </c>
       <c r="C286">
-        <v>40055.27</v>
+        <v>40055.269999999997</v>
       </c>
       <c r="D286">
         <v>39385.11</v>
       </c>
       <c r="E286">
-        <v>39756.64</v>
+        <v>39756.639999999999</v>
       </c>
       <c r="F286">
         <v>26826.87</v>
       </c>
     </row>
-    <row r="287" spans="1:6">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A287" t="s">
         <v>291</v>
       </c>
       <c r="B287">
-        <v>39220.56</v>
+        <v>39220.559999999998</v>
       </c>
       <c r="C287">
         <v>39508.93</v>
@@ -7227,7 +7277,7 @@
         <v>24623.58</v>
       </c>
     </row>
-    <row r="288" spans="1:6">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
         <v>292</v>
       </c>
@@ -7241,13 +7291,13 @@
         <v>38478.51</v>
       </c>
       <c r="E288">
-        <v>38725.55</v>
+        <v>38725.550000000003</v>
       </c>
       <c r="F288">
         <v>21225.32</v>
       </c>
     </row>
-    <row r="289" spans="1:6">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
         <v>293</v>
       </c>
@@ -7264,10 +7314,10 @@
         <v>39038.15</v>
       </c>
       <c r="F289">
-        <v>38419.23</v>
-      </c>
-    </row>
-    <row r="290" spans="1:6">
+        <v>38419.230000000003</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
         <v>294</v>
       </c>
@@ -7284,10 +7334,10 @@
         <v>39029.72</v>
       </c>
       <c r="F290">
-        <v>19302.81</v>
-      </c>
-    </row>
-    <row r="291" spans="1:6">
+        <v>19302.810000000001</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
         <v>295</v>
       </c>
@@ -7298,7 +7348,7 @@
         <v>39736</v>
       </c>
       <c r="D291">
-        <v>38819.59</v>
+        <v>38819.589999999997</v>
       </c>
       <c r="E291">
         <v>39582.74</v>
@@ -7307,7 +7357,7 @@
         <v>32951.01</v>
       </c>
     </row>
-    <row r="292" spans="1:6">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A292" t="s">
         <v>296</v>
       </c>
@@ -7321,13 +7371,13 @@
         <v>39038.21</v>
       </c>
       <c r="E292">
-        <v>39357.04</v>
+        <v>39357.040000000001</v>
       </c>
       <c r="F292">
         <v>24648.26</v>
       </c>
     </row>
-    <row r="293" spans="1:6">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
         <v>297</v>
       </c>
@@ -7338,7 +7388,7 @@
         <v>39610.68</v>
       </c>
       <c r="D293">
-        <v>39023.59</v>
+        <v>39023.589999999997</v>
       </c>
       <c r="E293">
         <v>39228.75</v>
@@ -7347,7 +7397,7 @@
         <v>14505.53</v>
       </c>
     </row>
-    <row r="294" spans="1:6">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
         <v>298</v>
       </c>
@@ -7364,18 +7414,18 @@
         <v>39375.93</v>
       </c>
       <c r="F294">
-        <v>24302.72</v>
-      </c>
-    </row>
-    <row r="295" spans="1:6">
+        <v>24302.720000000001</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
         <v>299</v>
       </c>
       <c r="B295">
-        <v>39388.12</v>
+        <v>39388.120000000003</v>
       </c>
       <c r="C295">
-        <v>39902.09</v>
+        <v>39902.089999999997</v>
       </c>
       <c r="D295">
         <v>38924.36</v>
@@ -7387,12 +7437,12 @@
         <v>10816.47</v>
       </c>
     </row>
-    <row r="296" spans="1:6">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
         <v>300</v>
       </c>
       <c r="B296">
-        <v>39224.48</v>
+        <v>39224.480000000003</v>
       </c>
       <c r="C296">
         <v>39711.31</v>
@@ -7401,13 +7451,13 @@
         <v>39031.31</v>
       </c>
       <c r="E296">
-        <v>39576.52</v>
+        <v>39576.519999999997</v>
       </c>
       <c r="F296">
-        <v>37616.63</v>
-      </c>
-    </row>
-    <row r="297" spans="1:6">
+        <v>37616.629999999997</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
         <v>301</v>
       </c>
@@ -7415,30 +7465,30 @@
         <v>39219.78</v>
       </c>
       <c r="C297">
-        <v>39661.91</v>
+        <v>39661.910000000003</v>
       </c>
       <c r="D297">
-        <v>38453.8</v>
+        <v>38453.800000000003</v>
       </c>
       <c r="E297">
-        <v>39207.02</v>
+        <v>39207.019999999997</v>
       </c>
       <c r="F297">
         <v>24221.09</v>
       </c>
     </row>
-    <row r="298" spans="1:6">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
         <v>302</v>
       </c>
       <c r="B298">
-        <v>39085.13</v>
+        <v>39085.129999999997</v>
       </c>
       <c r="C298">
         <v>39762.21</v>
       </c>
       <c r="D298">
-        <v>38852.13</v>
+        <v>38852.129999999997</v>
       </c>
       <c r="E298">
         <v>39072.9</v>
@@ -7447,7 +7497,7 @@
         <v>23792.87</v>
       </c>
     </row>
-    <row r="299" spans="1:6">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
         <v>303</v>
       </c>
@@ -7455,10 +7505,10 @@
         <v>38976.57</v>
       </c>
       <c r="C299">
-        <v>39149.8</v>
+        <v>39149.800000000003</v>
       </c>
       <c r="D299">
-        <v>38609.48</v>
+        <v>38609.480000000003</v>
       </c>
       <c r="E299">
         <v>38900.18</v>
@@ -7467,7 +7517,7 @@
         <v>30062.04</v>
       </c>
     </row>
-    <row r="300" spans="1:6">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A300" t="s">
         <v>304</v>
       </c>
@@ -7475,7 +7525,7 @@
         <v>39242.68</v>
       </c>
       <c r="C300">
-        <v>39627.09</v>
+        <v>39627.089999999997</v>
       </c>
       <c r="D300">
         <v>38950.94</v>
@@ -7487,7 +7537,7 @@
         <v>42222.04</v>
       </c>
     </row>
-    <row r="301" spans="1:6">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A301" t="s">
         <v>305</v>
       </c>
@@ -7498,7 +7548,7 @@
         <v>39787.78</v>
       </c>
       <c r="D301">
-        <v>38916.3</v>
+        <v>38916.300000000003</v>
       </c>
       <c r="E301">
         <v>39137.51</v>
@@ -7507,27 +7557,27 @@
         <v>31025.42</v>
       </c>
     </row>
-    <row r="302" spans="1:6">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A302" t="s">
         <v>306</v>
       </c>
       <c r="B302">
-        <v>39195.3</v>
+        <v>39195.300000000003</v>
       </c>
       <c r="C302">
-        <v>39775.45</v>
+        <v>39775.449999999997</v>
       </c>
       <c r="D302">
-        <v>38750.63</v>
+        <v>38750.629999999997</v>
       </c>
       <c r="E302">
         <v>39358.79</v>
       </c>
       <c r="F302">
-        <v>34123.63</v>
-      </c>
-    </row>
-    <row r="303" spans="1:6">
+        <v>34123.629999999997</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A303" t="s">
         <v>307</v>
       </c>
@@ -7544,10 +7594,10 @@
         <v>39451.21</v>
       </c>
       <c r="F303">
-        <v>20387.81</v>
-      </c>
-    </row>
-    <row r="304" spans="1:6">
+        <v>20387.810000000001</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
         <v>308</v>
       </c>
@@ -7567,18 +7617,18 @@
         <v>19186.11</v>
       </c>
     </row>
-    <row r="305" spans="1:6">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
         <v>309</v>
       </c>
       <c r="B305">
-        <v>39698.27</v>
+        <v>39698.269999999997</v>
       </c>
       <c r="C305">
-        <v>40136.88</v>
+        <v>40136.879999999997</v>
       </c>
       <c r="D305">
-        <v>39250.56</v>
+        <v>39250.559999999998</v>
       </c>
       <c r="E305">
         <v>39334.75</v>
@@ -7587,18 +7637,18 @@
         <v>13669.83</v>
       </c>
     </row>
-    <row r="306" spans="1:6">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A306" t="s">
         <v>310</v>
       </c>
       <c r="B306">
-        <v>38939.63</v>
+        <v>38939.629999999997</v>
       </c>
       <c r="C306">
-        <v>39392.52</v>
+        <v>39392.519999999997</v>
       </c>
       <c r="D306">
-        <v>38686.55</v>
+        <v>38686.550000000003</v>
       </c>
       <c r="E306">
         <v>38890.06</v>
@@ -7607,7 +7657,7 @@
         <v>21033.18</v>
       </c>
     </row>
-    <row r="307" spans="1:6">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
         <v>311</v>
       </c>
@@ -7615,19 +7665,19 @@
         <v>38726.81</v>
       </c>
       <c r="C307">
-        <v>39346.45</v>
+        <v>39346.449999999997</v>
       </c>
       <c r="D307">
         <v>38011.35</v>
       </c>
       <c r="E307">
-        <v>38642.2</v>
+        <v>38642.199999999997</v>
       </c>
       <c r="F307">
         <v>21468.75</v>
       </c>
     </row>
-    <row r="308" spans="1:6">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A308" t="s">
         <v>312</v>
       </c>
@@ -7647,7 +7697,7 @@
         <v>20989.39</v>
       </c>
     </row>
-    <row r="309" spans="1:6">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A309" t="s">
         <v>313</v>
       </c>
@@ -7655,10 +7705,10 @@
         <v>37669.69</v>
       </c>
       <c r="C309">
-        <v>37947.44</v>
+        <v>37947.440000000002</v>
       </c>
       <c r="D309">
-        <v>37215.76</v>
+        <v>37215.760000000002</v>
       </c>
       <c r="E309">
         <v>37733.47</v>
@@ -7667,7 +7717,7 @@
         <v>31477.06</v>
       </c>
     </row>
-    <row r="310" spans="1:6">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A310" t="s">
         <v>314</v>
       </c>
@@ -7675,7 +7725,7 @@
         <v>37455.54</v>
       </c>
       <c r="C310">
-        <v>37548.24</v>
+        <v>37548.239999999998</v>
       </c>
       <c r="D310">
         <v>37282.04</v>
@@ -7687,7 +7737,7 @@
         <v>29922.89</v>
       </c>
     </row>
-    <row r="311" spans="1:6">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A311" t="s">
         <v>315</v>
       </c>
@@ -7695,24 +7745,24 @@
         <v>37645.07</v>
       </c>
       <c r="C311">
-        <v>38003.37</v>
+        <v>38003.370000000003</v>
       </c>
       <c r="D311">
         <v>37515.42</v>
       </c>
       <c r="E311">
-        <v>37826.55</v>
+        <v>37826.550000000003</v>
       </c>
       <c r="F311">
         <v>14598.25</v>
       </c>
     </row>
-    <row r="312" spans="1:6">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A312" t="s">
         <v>316</v>
       </c>
       <c r="B312">
-        <v>37507.45</v>
+        <v>37507.449999999997</v>
       </c>
       <c r="C312">
         <v>37997.96</v>
@@ -7721,13 +7771,13 @@
         <v>36926.68</v>
       </c>
       <c r="E312">
-        <v>37038.41</v>
+        <v>37038.410000000003</v>
       </c>
       <c r="F312">
         <v>43852.76</v>
       </c>
     </row>
-    <row r="313" spans="1:6">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
         <v>317</v>
       </c>
@@ -7738,7 +7788,7 @@
         <v>37004.54</v>
       </c>
       <c r="D313">
-        <v>36130.48</v>
+        <v>36130.480000000003</v>
       </c>
       <c r="E313">
         <v>36279.96</v>
@@ -7747,18 +7797,18 @@
         <v>21403.96</v>
       </c>
     </row>
-    <row r="314" spans="1:6">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A314" t="s">
         <v>318</v>
       </c>
       <c r="B314">
-        <v>36052.24</v>
+        <v>36052.239999999998</v>
       </c>
       <c r="C314">
         <v>36425.78</v>
       </c>
       <c r="D314">
-        <v>35561.16</v>
+        <v>35561.160000000003</v>
       </c>
       <c r="E314">
         <v>36225.93</v>
@@ -7767,7 +7817,7 @@
         <v>5736.9</v>
       </c>
     </row>
-    <row r="315" spans="1:6">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A315" t="s">
         <v>319</v>
       </c>
@@ -7778,16 +7828,16 @@
         <v>36599.21</v>
       </c>
       <c r="D315">
-        <v>35598.95</v>
+        <v>35598.949999999997</v>
       </c>
       <c r="E315">
-        <v>36558.84</v>
+        <v>36558.839999999997</v>
       </c>
       <c r="F315">
         <v>23482.23</v>
       </c>
     </row>
-    <row r="316" spans="1:6">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
         <v>320</v>
       </c>
@@ -7798,16 +7848,16 @@
         <v>36359.54</v>
       </c>
       <c r="D316">
-        <v>35296.05</v>
+        <v>35296.050000000003</v>
       </c>
       <c r="E316">
-        <v>36033.55</v>
+        <v>36033.550000000003</v>
       </c>
       <c r="F316">
         <v>17878.93</v>
       </c>
     </row>
-    <row r="317" spans="1:6">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A317" t="s">
         <v>321</v>
       </c>
@@ -7821,13 +7871,13 @@
         <v>36061.71</v>
       </c>
       <c r="E317">
-        <v>36432.73</v>
+        <v>36432.730000000003</v>
       </c>
       <c r="F317">
         <v>27649.27</v>
       </c>
     </row>
-    <row r="318" spans="1:6">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A318" t="s">
         <v>322</v>
       </c>
@@ -7841,24 +7891,24 @@
         <v>35843.61</v>
       </c>
       <c r="E318">
-        <v>36279.98</v>
+        <v>36279.980000000003</v>
       </c>
       <c r="F318">
         <v>16465</v>
       </c>
     </row>
-    <row r="319" spans="1:6">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A319" t="s">
         <v>323</v>
       </c>
       <c r="B319">
-        <v>36076.63</v>
+        <v>36076.629999999997</v>
       </c>
       <c r="C319">
-        <v>36311.7</v>
+        <v>36311.699999999997</v>
       </c>
       <c r="D319">
-        <v>35985.04</v>
+        <v>35985.040000000001</v>
       </c>
       <c r="E319">
         <v>36139.54</v>
@@ -7867,7 +7917,7 @@
         <v>20274.41</v>
       </c>
     </row>
-    <row r="320" spans="1:6">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A320" t="s">
         <v>324</v>
       </c>
@@ -7875,7 +7925,7 @@
         <v>35859.81</v>
       </c>
       <c r="C320">
-        <v>36016.62</v>
+        <v>36016.620000000003</v>
       </c>
       <c r="D320">
         <v>35767.43</v>
@@ -7887,7 +7937,7 @@
         <v>23441.13</v>
       </c>
     </row>
-    <row r="321" spans="1:6">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
         <v>325</v>
       </c>
@@ -7898,27 +7948,27 @@
         <v>35446</v>
       </c>
       <c r="D321">
-        <v>35155.95</v>
+        <v>35155.949999999997</v>
       </c>
       <c r="E321">
-        <v>35188.27</v>
+        <v>35188.269999999997</v>
       </c>
       <c r="F321">
         <v>24593.26</v>
       </c>
     </row>
-    <row r="322" spans="1:6">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
         <v>326</v>
       </c>
       <c r="B322">
-        <v>35102.48</v>
+        <v>35102.480000000003</v>
       </c>
       <c r="C322">
-        <v>35663.34</v>
+        <v>35663.339999999997</v>
       </c>
       <c r="D322">
-        <v>34761.37</v>
+        <v>34761.370000000003</v>
       </c>
       <c r="E322">
         <v>35486.39</v>
@@ -7927,7 +7977,7 @@
         <v>27472.78</v>
       </c>
     </row>
-    <row r="323" spans="1:6">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A323" t="s">
         <v>327</v>
       </c>
@@ -7935,19 +7985,19 @@
         <v>35222.69</v>
       </c>
       <c r="C323">
-        <v>35781.23</v>
+        <v>35781.230000000003</v>
       </c>
       <c r="D323">
         <v>35216.82</v>
       </c>
       <c r="E323">
-        <v>35335.38</v>
+        <v>35335.379999999997</v>
       </c>
       <c r="F323">
-        <v>31394.56</v>
-      </c>
-    </row>
-    <row r="324" spans="1:6">
+        <v>31394.560000000001</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A324" t="s">
         <v>328</v>
       </c>
@@ -7967,12 +8017,12 @@
         <v>31838.67</v>
       </c>
     </row>
-    <row r="325" spans="1:6">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
         <v>329</v>
       </c>
       <c r="B325">
-        <v>35511.37</v>
+        <v>35511.370000000003</v>
       </c>
       <c r="C325">
         <v>35650.21</v>
@@ -7987,12 +8037,12 @@
         <v>26253.08</v>
       </c>
     </row>
-    <row r="326" spans="1:6">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A326" t="s">
         <v>330</v>
       </c>
       <c r="B326">
-        <v>35611.88</v>
+        <v>35611.879999999997</v>
       </c>
       <c r="C326">
         <v>36069.96</v>
@@ -8001,13 +8051,13 @@
         <v>35070.75</v>
       </c>
       <c r="E326">
-        <v>35181.05</v>
+        <v>35181.050000000003</v>
       </c>
       <c r="F326">
-        <v>18195.08</v>
-      </c>
-    </row>
-    <row r="327" spans="1:6">
+        <v>18195.080000000002</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A327" t="s">
         <v>331</v>
       </c>
@@ -8015,24 +8065,24 @@
         <v>35587.11</v>
       </c>
       <c r="C327">
-        <v>35677.91</v>
+        <v>35677.910000000003</v>
       </c>
       <c r="D327">
         <v>35184.35</v>
       </c>
       <c r="E327">
-        <v>35431.38</v>
+        <v>35431.379999999997</v>
       </c>
       <c r="F327">
-        <v>36591.34</v>
-      </c>
-    </row>
-    <row r="328" spans="1:6">
+        <v>36591.339999999997</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A328" t="s">
         <v>332</v>
       </c>
       <c r="B328">
-        <v>35263.77</v>
+        <v>35263.769999999997</v>
       </c>
       <c r="C328">
         <v>35555.65</v>
@@ -8047,12 +8097,12 @@
         <v>14427.52</v>
       </c>
     </row>
-    <row r="329" spans="1:6">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
         <v>333</v>
       </c>
       <c r="B329">
-        <v>35725.87</v>
+        <v>35725.870000000003</v>
       </c>
       <c r="C329">
         <v>35793.43</v>
@@ -8061,13 +8111,13 @@
         <v>35452.31</v>
       </c>
       <c r="E329">
-        <v>35738.77</v>
+        <v>35738.769999999997</v>
       </c>
       <c r="F329">
         <v>23792.78</v>
       </c>
     </row>
-    <row r="330" spans="1:6">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A330" t="s">
         <v>334</v>
       </c>
@@ -8075,10 +8125,10 @@
         <v>35980.65</v>
       </c>
       <c r="C330">
-        <v>36718.3</v>
+        <v>36718.300000000003</v>
       </c>
       <c r="D330">
-        <v>35650.38</v>
+        <v>35650.379999999997</v>
       </c>
       <c r="E330">
         <v>35992.44</v>
@@ -8087,7 +8137,7 @@
         <v>6181.75</v>
       </c>
     </row>
-    <row r="331" spans="1:6">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
         <v>335</v>
       </c>
@@ -8101,18 +8151,18 @@
         <v>35292.83</v>
       </c>
       <c r="E331">
-        <v>35947.48</v>
+        <v>35947.480000000003</v>
       </c>
       <c r="F331">
         <v>1423.8</v>
       </c>
     </row>
-    <row r="332" spans="1:6">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A332" t="s">
         <v>336</v>
       </c>
       <c r="B332">
-        <v>35936.72</v>
+        <v>35936.720000000001</v>
       </c>
       <c r="C332">
         <v>36082.82</v>
@@ -8121,13 +8171,13 @@
         <v>35434.57</v>
       </c>
       <c r="E332">
-        <v>35671.09</v>
+        <v>35671.089999999997</v>
       </c>
       <c r="F332">
         <v>24348.57</v>
       </c>
     </row>
-    <row r="333" spans="1:6">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A333" t="s">
         <v>337</v>
       </c>
@@ -8135,7 +8185,7 @@
         <v>35385.14</v>
       </c>
       <c r="C333">
-        <v>35565.87</v>
+        <v>35565.870000000003</v>
       </c>
       <c r="D333">
         <v>34793.06</v>
@@ -8144,10 +8194,10 @@
         <v>35315.06</v>
       </c>
       <c r="F333">
-        <v>17747.81</v>
-      </c>
-    </row>
-    <row r="334" spans="1:6">
+        <v>17747.810000000001</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
         <v>338</v>
       </c>
@@ -8167,7 +8217,7 @@
         <v>2111.85</v>
       </c>
     </row>
-    <row r="335" spans="1:6">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A335" t="s">
         <v>339</v>
       </c>
@@ -8175,7 +8225,7 @@
         <v>34655.08</v>
       </c>
       <c r="C335">
-        <v>34851.59</v>
+        <v>34851.589999999997</v>
       </c>
       <c r="D335">
         <v>33881.21</v>
@@ -8187,12 +8237,12 @@
         <v>21478</v>
       </c>
     </row>
-    <row r="336" spans="1:6">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A336" t="s">
         <v>340</v>
       </c>
       <c r="B336">
-        <v>34136.91</v>
+        <v>34136.910000000003</v>
       </c>
       <c r="C336">
         <v>34359.46</v>
@@ -8201,13 +8251,13 @@
         <v>33706.04</v>
       </c>
       <c r="E336">
-        <v>33992.66</v>
+        <v>33992.660000000003</v>
       </c>
       <c r="F336">
         <v>23470.63</v>
       </c>
     </row>
-    <row r="337" spans="1:6">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
         <v>341</v>
       </c>
@@ -8215,19 +8265,19 @@
         <v>33498.07</v>
       </c>
       <c r="C337">
-        <v>33651.6</v>
+        <v>33651.599999999999</v>
       </c>
       <c r="D337">
         <v>33199.58</v>
       </c>
       <c r="E337">
-        <v>33554.62</v>
+        <v>33554.620000000003</v>
       </c>
       <c r="F337">
-        <v>20804.08</v>
-      </c>
-    </row>
-    <row r="338" spans="1:6">
+        <v>20804.080000000002</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A338" t="s">
         <v>342</v>
       </c>
@@ -8235,19 +8285,19 @@
         <v>33608.76</v>
       </c>
       <c r="C338">
-        <v>33943.84</v>
+        <v>33943.839999999997</v>
       </c>
       <c r="D338">
         <v>33086.61</v>
       </c>
       <c r="E338">
-        <v>33723.98</v>
+        <v>33723.980000000003</v>
       </c>
       <c r="F338">
         <v>14110.82</v>
       </c>
     </row>
-    <row r="339" spans="1:6">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
         <v>343</v>
       </c>
@@ -8255,10 +8305,10 @@
         <v>33717.56</v>
       </c>
       <c r="C339">
-        <v>34070.96</v>
+        <v>34070.959999999999</v>
       </c>
       <c r="D339">
-        <v>33348.41</v>
+        <v>33348.410000000003</v>
       </c>
       <c r="E339">
         <v>33831.93</v>
@@ -8267,7 +8317,7 @@
         <v>32733.03</v>
       </c>
     </row>
-    <row r="340" spans="1:6">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
         <v>344</v>
       </c>
@@ -8281,13 +8331,13 @@
         <v>32974.76</v>
       </c>
       <c r="E340">
-        <v>33475.48</v>
+        <v>33475.480000000003</v>
       </c>
       <c r="F340">
         <v>17450.66</v>
       </c>
     </row>
-    <row r="341" spans="1:6">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A341" t="s">
         <v>345</v>
       </c>
@@ -8295,24 +8345,24 @@
         <v>33432.79</v>
       </c>
       <c r="C341">
-        <v>33897.98</v>
+        <v>33897.980000000003</v>
       </c>
       <c r="D341">
         <v>33264.1</v>
       </c>
       <c r="E341">
-        <v>33310.63</v>
+        <v>33310.629999999997</v>
       </c>
       <c r="F341">
         <v>29848.11</v>
       </c>
     </row>
-    <row r="342" spans="1:6">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A342" t="s">
         <v>346</v>
       </c>
       <c r="B342">
-        <v>33165.34</v>
+        <v>33165.339999999997</v>
       </c>
       <c r="C342">
         <v>33482.17</v>
@@ -8324,10 +8374,10 @@
         <v>32863.79</v>
       </c>
       <c r="F342">
-        <v>27179.2</v>
-      </c>
-    </row>
-    <row r="343" spans="1:6">
+        <v>27179.200000000001</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
         <v>347</v>
       </c>
@@ -8335,7 +8385,7 @@
         <v>32668.82</v>
       </c>
       <c r="C343">
-        <v>32849.92</v>
+        <v>32849.919999999998</v>
       </c>
       <c r="D343">
         <v>32321.99</v>
@@ -8347,12 +8397,12 @@
         <v>20224.61</v>
       </c>
     </row>
-    <row r="344" spans="1:6">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A344" t="s">
         <v>348</v>
       </c>
       <c r="B344">
-        <v>33093.02</v>
+        <v>33093.019999999997</v>
       </c>
       <c r="C344">
         <v>33424.01</v>
@@ -8367,12 +8417,12 @@
         <v>31870.53</v>
       </c>
     </row>
-    <row r="345" spans="1:6">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
         <v>349</v>
       </c>
       <c r="B345">
-        <v>32405.92</v>
+        <v>32405.919999999998</v>
       </c>
       <c r="C345">
         <v>32682.31</v>
@@ -8387,7 +8437,7 @@
         <v>16380.2</v>
       </c>
     </row>
-    <row r="346" spans="1:6">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A346" t="s">
         <v>350</v>
       </c>
@@ -8407,12 +8457,12 @@
         <v>22522.44</v>
       </c>
     </row>
-    <row r="347" spans="1:6">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A347" t="s">
         <v>351</v>
       </c>
       <c r="B347">
-        <v>32430.8</v>
+        <v>32430.799999999999</v>
       </c>
       <c r="C347">
         <v>32935.33</v>
@@ -8421,13 +8471,13 @@
         <v>32015.84</v>
       </c>
       <c r="E347">
-        <v>32832.95</v>
+        <v>32832.949999999997</v>
       </c>
       <c r="F347">
         <v>22798.52</v>
       </c>
     </row>
-    <row r="348" spans="1:6">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A348" t="s">
         <v>352</v>
       </c>
@@ -8441,13 +8491,13 @@
         <v>31955.14</v>
       </c>
       <c r="E348">
-        <v>32753.6</v>
+        <v>32753.599999999999</v>
       </c>
       <c r="F348">
         <v>24003.85</v>
       </c>
     </row>
-    <row r="349" spans="1:6">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
         <v>353</v>
       </c>
@@ -8467,7 +8517,7 @@
         <v>39119.78</v>
       </c>
     </row>
-    <row r="350" spans="1:6">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A350" t="s">
         <v>354</v>
       </c>
@@ -8487,7 +8537,7 @@
         <v>34634.01</v>
       </c>
     </row>
-    <row r="351" spans="1:6">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A351" t="s">
         <v>355</v>
       </c>
@@ -8507,7 +8557,7 @@
         <v>3221.54</v>
       </c>
     </row>
-    <row r="352" spans="1:6">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
         <v>356</v>
       </c>
@@ -8527,7 +8577,7 @@
         <v>32649.81</v>
       </c>
     </row>
-    <row r="353" spans="1:6">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
         <v>357</v>
       </c>
@@ -8547,7 +8597,7 @@
         <v>35957.89</v>
       </c>
     </row>
-    <row r="354" spans="1:6">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A354" t="s">
         <v>358</v>
       </c>
@@ -8567,7 +8617,7 @@
         <v>34456.68</v>
       </c>
     </row>
-    <row r="355" spans="1:6">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A355" t="s">
         <v>359</v>
       </c>
@@ -8581,13 +8631,13 @@
         <v>31140.9</v>
       </c>
       <c r="E355">
-        <v>31155.6</v>
+        <v>31155.599999999999</v>
       </c>
       <c r="F355">
         <v>14399.39</v>
       </c>
     </row>
-    <row r="356" spans="1:6">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A356" t="s">
         <v>360</v>
       </c>
@@ -8601,13 +8651,13 @@
         <v>30596.06</v>
       </c>
       <c r="E356">
-        <v>31224.88</v>
+        <v>31224.880000000001</v>
       </c>
       <c r="F356">
         <v>24714.28</v>
       </c>
     </row>
-    <row r="357" spans="1:6">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A357" t="s">
         <v>361</v>
       </c>
@@ -8627,7 +8677,7 @@
         <v>26756.57</v>
       </c>
     </row>
-    <row r="358" spans="1:6">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
         <v>362</v>
       </c>
@@ -8647,7 +8697,7 @@
         <v>30645.14</v>
       </c>
     </row>
-    <row r="359" spans="1:6">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A359" t="s">
         <v>363</v>
       </c>
@@ -8667,7 +8717,7 @@
         <v>37126.71</v>
       </c>
     </row>
-    <row r="360" spans="1:6">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A360" t="s">
         <v>364</v>
       </c>
@@ -8687,7 +8737,7 @@
         <v>19926.97</v>
       </c>
     </row>
-    <row r="361" spans="1:6">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
         <v>365</v>
       </c>
@@ -8707,7 +8757,7 @@
         <v>25226.53</v>
       </c>
     </row>
-    <row r="362" spans="1:6">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A362" t="s">
         <v>366</v>
       </c>
@@ -8724,10 +8774,10 @@
         <v>29570.35</v>
       </c>
       <c r="F362">
-        <v>9619.280000000001</v>
-      </c>
-    </row>
-    <row r="363" spans="1:6">
+        <v>9619.2800000000007</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A363" t="s">
         <v>367</v>
       </c>
@@ -8747,7 +8797,7 @@
         <v>36418.86</v>
       </c>
     </row>
-    <row r="364" spans="1:6">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A364" t="s">
         <v>368</v>
       </c>
@@ -8767,7 +8817,7 @@
         <v>17203.88</v>
       </c>
     </row>
-    <row r="365" spans="1:6">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A365" t="s">
         <v>369</v>
       </c>
@@ -8787,7 +8837,7 @@
         <v>17061.73</v>
       </c>
     </row>
-    <row r="366" spans="1:6">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A366" t="s">
         <v>370</v>
       </c>

--- a/src/main/resources/btc_usdt_dummy_year.xlsx
+++ b/src/main/resources/btc_usdt_dummy_year.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24527"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NoteBook\Desktop\Mine\Code\CAlg\src\main\resources\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E242AA5-7F64-45A4-A953-CD1BCB36515C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1138,8 +1132,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1202,14 +1196,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1256,7 +1242,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1288,27 +1274,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1340,24 +1308,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1533,11 +1483,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F366"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1557,7 +1507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1577,7 +1527,7 @@
         <v>21839.9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1594,10 +1544,10 @@
         <v>42479.38</v>
       </c>
       <c r="F3">
-        <v>33233.870000000003</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+        <v>33233.87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1617,7 +1567,7 @@
         <v>18479.93</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1637,7 +1587,7 @@
         <v>21834.86</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1648,7 +1598,7 @@
         <v>42367.06</v>
       </c>
       <c r="D6">
-        <v>41609.730000000003</v>
+        <v>41609.73</v>
       </c>
       <c r="E6">
         <v>42293.18</v>
@@ -1657,7 +1607,7 @@
         <v>31175.41</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1668,16 +1618,16 @@
         <v>42965.39</v>
       </c>
       <c r="D7">
-        <v>42081.279999999999</v>
+        <v>42081.28</v>
       </c>
       <c r="E7">
         <v>42490.84</v>
       </c>
       <c r="F7">
-        <v>17010.419999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+        <v>17010.42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1697,7 +1647,7 @@
         <v>21400</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1714,10 +1664,10 @@
         <v>42655.3</v>
       </c>
       <c r="F9">
-        <v>18412.509999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+        <v>18412.51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1737,18 +1687,18 @@
         <v>27596.9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="B11">
-        <v>42797.279999999999</v>
+        <v>42797.28</v>
       </c>
       <c r="C11">
         <v>43481.97</v>
       </c>
       <c r="D11">
-        <v>42507.839999999997</v>
+        <v>42507.84</v>
       </c>
       <c r="E11">
         <v>43288.62</v>
@@ -1757,7 +1707,7 @@
         <v>25735.22</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1777,7 +1727,7 @@
         <v>32470.82</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -1797,7 +1747,7 @@
         <v>13416.13</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1817,7 +1767,7 @@
         <v>27818.5</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1837,7 +1787,7 @@
         <v>36318.89</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -1857,7 +1807,7 @@
         <v>27458.7</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1877,12 +1827,12 @@
         <v>27639.86</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>22</v>
       </c>
       <c r="B18">
-        <v>44017.440000000002</v>
+        <v>44017.44</v>
       </c>
       <c r="C18">
         <v>44385.36</v>
@@ -1897,7 +1847,7 @@
         <v>11537.22</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -1914,15 +1864,15 @@
         <v>43424.29</v>
       </c>
       <c r="F19">
-        <v>8974.7099999999991</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+        <v>8974.709999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>24</v>
       </c>
       <c r="B20">
-        <v>43613.760000000002</v>
+        <v>43613.76</v>
       </c>
       <c r="C20">
         <v>44050.27</v>
@@ -1934,10 +1884,10 @@
         <v>43384.72</v>
       </c>
       <c r="F20">
-        <v>38759.300000000003</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+        <v>38759.3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1957,7 +1907,7 @@
         <v>21540.97</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -1974,10 +1924,10 @@
         <v>44189.83</v>
       </c>
       <c r="F22">
-        <v>33115.629999999997</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+        <v>33115.63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -1997,7 +1947,7 @@
         <v>23527.85</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -2017,7 +1967,7 @@
         <v>26408.58</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -2037,7 +1987,7 @@
         <v>15242.94</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -2057,12 +2007,12 @@
         <v>27144.92</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>31</v>
       </c>
       <c r="B27">
-        <v>45061.279999999999</v>
+        <v>45061.28</v>
       </c>
       <c r="C27">
         <v>45628.95</v>
@@ -2077,7 +2027,7 @@
         <v>19244.2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -2097,7 +2047,7 @@
         <v>25974.26</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -2111,13 +2061,13 @@
         <v>43850.11</v>
       </c>
       <c r="E29">
-        <v>44501.120000000003</v>
+        <v>44501.12</v>
       </c>
       <c r="F29">
         <v>33677.82</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -2134,10 +2084,10 @@
         <v>43635.97</v>
       </c>
       <c r="F30">
-        <v>24552.080000000002</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+        <v>24552.08</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -2154,10 +2104,10 @@
         <v>43064.66</v>
       </c>
       <c r="F31">
-        <v>32658.799999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+        <v>32658.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -2177,7 +2127,7 @@
         <v>25026.3</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -2197,7 +2147,7 @@
         <v>16261.1</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -2217,7 +2167,7 @@
         <v>25018.37</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -2237,7 +2187,7 @@
         <v>2414.08</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -2257,7 +2207,7 @@
         <v>14684.72</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -2277,7 +2227,7 @@
         <v>31518.14</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -2297,7 +2247,7 @@
         <v>12259.94</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -2314,10 +2264,10 @@
         <v>43214.94</v>
       </c>
       <c r="F39">
-        <v>33535.269999999997</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
+        <v>33535.27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -2337,7 +2287,7 @@
         <v>12445.02</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -2357,12 +2307,12 @@
         <v>21554.84</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>46</v>
       </c>
       <c r="B42">
-        <v>42078.879999999997</v>
+        <v>42078.88</v>
       </c>
       <c r="C42">
         <v>42268.62</v>
@@ -2371,13 +2321,13 @@
         <v>41356.35</v>
       </c>
       <c r="E42">
-        <v>41565.440000000002</v>
+        <v>41565.44</v>
       </c>
       <c r="F42">
         <v>27244.28</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -2397,7 +2347,7 @@
         <v>29578.07</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>48</v>
       </c>
@@ -2414,10 +2364,10 @@
         <v>42351.24</v>
       </c>
       <c r="F44">
-        <v>32801.760000000002</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
+        <v>32801.76</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -2428,24 +2378,24 @@
         <v>42649.48</v>
       </c>
       <c r="D45">
-        <v>41655.800000000003</v>
+        <v>41655.8</v>
       </c>
       <c r="E45">
         <v>42041.97</v>
       </c>
       <c r="F45">
-        <v>36280.639999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
+        <v>36280.64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>50</v>
       </c>
       <c r="B46">
-        <v>41225.360000000001</v>
+        <v>41225.36</v>
       </c>
       <c r="C46">
-        <v>41733.050000000003</v>
+        <v>41733.05</v>
       </c>
       <c r="D46">
         <v>40959.07</v>
@@ -2457,12 +2407,12 @@
         <v>23364.01</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>51</v>
       </c>
       <c r="B47">
-        <v>41281.730000000003</v>
+        <v>41281.73</v>
       </c>
       <c r="C47">
         <v>41927.19</v>
@@ -2474,10 +2424,10 @@
         <v>41384.39</v>
       </c>
       <c r="F47">
-        <v>9178.7800000000007</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
+        <v>9178.780000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>52</v>
       </c>
@@ -2494,10 +2444,10 @@
         <v>40308.68</v>
       </c>
       <c r="F48">
-        <v>34954.089999999997</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
+        <v>34954.09</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>53</v>
       </c>
@@ -2508,16 +2458,16 @@
         <v>40906.14</v>
       </c>
       <c r="D49">
-        <v>39907.760000000002</v>
+        <v>39907.76</v>
       </c>
       <c r="E49">
-        <v>40662.620000000003</v>
+        <v>40662.62</v>
       </c>
       <c r="F49">
         <v>16803.88</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>54</v>
       </c>
@@ -2528,7 +2478,7 @@
         <v>41313.58</v>
       </c>
       <c r="D50">
-        <v>40438.339999999997</v>
+        <v>40438.34</v>
       </c>
       <c r="E50">
         <v>40682.42</v>
@@ -2537,7 +2487,7 @@
         <v>21512.78</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>55</v>
       </c>
@@ -2545,7 +2495,7 @@
         <v>41000.74</v>
       </c>
       <c r="C51">
-        <v>41183.120000000003</v>
+        <v>41183.12</v>
       </c>
       <c r="D51">
         <v>40453.96</v>
@@ -2557,7 +2507,7 @@
         <v>22223.32</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>56</v>
       </c>
@@ -2568,36 +2518,36 @@
         <v>41276.19</v>
       </c>
       <c r="D52">
-        <v>40390.480000000003</v>
+        <v>40390.48</v>
       </c>
       <c r="E52">
-        <v>40574.269999999997</v>
+        <v>40574.27</v>
       </c>
       <c r="F52">
         <v>17247.72</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>57</v>
       </c>
       <c r="B53">
-        <v>40798.699999999997</v>
+        <v>40798.7</v>
       </c>
       <c r="C53">
-        <v>41032.949999999997</v>
+        <v>41032.95</v>
       </c>
       <c r="D53">
         <v>40380.26</v>
       </c>
       <c r="E53">
-        <v>40970.400000000001</v>
+        <v>40970.4</v>
       </c>
       <c r="F53">
         <v>32690.53</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>58</v>
       </c>
@@ -2605,10 +2555,10 @@
         <v>41190.17</v>
       </c>
       <c r="C54">
-        <v>41567.629999999997</v>
+        <v>41567.63</v>
       </c>
       <c r="D54">
-        <v>40580.769999999997</v>
+        <v>40580.77</v>
       </c>
       <c r="E54">
         <v>40903.94</v>
@@ -2617,7 +2567,7 @@
         <v>26783.46</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>59</v>
       </c>
@@ -2628,7 +2578,7 @@
         <v>41507.58</v>
       </c>
       <c r="D55">
-        <v>40804.080000000002</v>
+        <v>40804.08</v>
       </c>
       <c r="E55">
         <v>41244.06</v>
@@ -2637,38 +2587,38 @@
         <v>29953.02</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>60</v>
       </c>
       <c r="B56">
-        <v>41320.239999999998</v>
+        <v>41320.24</v>
       </c>
       <c r="C56">
-        <v>41725.980000000003</v>
+        <v>41725.98</v>
       </c>
       <c r="D56">
-        <v>40980.480000000003</v>
+        <v>40980.48</v>
       </c>
       <c r="E56">
-        <v>41702.949999999997</v>
+        <v>41702.95</v>
       </c>
       <c r="F56">
-        <v>19105.669999999998</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
+        <v>19105.67</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>61</v>
       </c>
       <c r="B57">
-        <v>41689.480000000003</v>
+        <v>41689.48</v>
       </c>
       <c r="C57">
         <v>41800.21</v>
       </c>
       <c r="D57">
-        <v>41486.629999999997</v>
+        <v>41486.63</v>
       </c>
       <c r="E57">
         <v>41648.31</v>
@@ -2677,7 +2627,7 @@
         <v>25535.5</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>62</v>
       </c>
@@ -2685,7 +2635,7 @@
         <v>41446.58</v>
       </c>
       <c r="C58">
-        <v>41896.629999999997</v>
+        <v>41896.63</v>
       </c>
       <c r="D58">
         <v>40933.49</v>
@@ -2697,7 +2647,7 @@
         <v>22970.98</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>63</v>
       </c>
@@ -2717,7 +2667,7 @@
         <v>11966.81</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>64</v>
       </c>
@@ -2725,27 +2675,27 @@
         <v>41571.5</v>
       </c>
       <c r="C60">
-        <v>41768.879999999997</v>
+        <v>41768.88</v>
       </c>
       <c r="D60">
-        <v>41071.160000000003</v>
+        <v>41071.16</v>
       </c>
       <c r="E60">
-        <v>41743.269999999997</v>
+        <v>41743.27</v>
       </c>
       <c r="F60">
         <v>24711.62</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>65</v>
       </c>
       <c r="B61">
-        <v>41819.410000000003</v>
+        <v>41819.41</v>
       </c>
       <c r="C61">
-        <v>42305.919999999998</v>
+        <v>42305.92</v>
       </c>
       <c r="D61">
         <v>41248.19</v>
@@ -2757,7 +2707,7 @@
         <v>16788.34</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>66</v>
       </c>
@@ -2768,16 +2718,16 @@
         <v>41349.69</v>
       </c>
       <c r="D62">
-        <v>40804.410000000003</v>
+        <v>40804.41</v>
       </c>
       <c r="E62">
-        <v>41098.620000000003</v>
+        <v>41098.62</v>
       </c>
       <c r="F62">
         <v>32729.64</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>67</v>
       </c>
@@ -2785,19 +2735,19 @@
         <v>40861.54</v>
       </c>
       <c r="C63">
-        <v>40965.199999999997</v>
+        <v>40965.2</v>
       </c>
       <c r="D63">
-        <v>40184.129999999997</v>
+        <v>40184.13</v>
       </c>
       <c r="E63">
-        <v>40596.379999999997</v>
+        <v>40596.38</v>
       </c>
       <c r="F63">
         <v>32103.59</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>68</v>
       </c>
@@ -2811,24 +2761,24 @@
         <v>39393.94</v>
       </c>
       <c r="E64">
-        <v>39590.230000000003</v>
+        <v>39590.23</v>
       </c>
       <c r="F64">
         <v>21163.8</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>69</v>
       </c>
       <c r="B65">
-        <v>39427.440000000002</v>
+        <v>39427.44</v>
       </c>
       <c r="C65">
         <v>40308.42</v>
       </c>
       <c r="D65">
-        <v>38822.339999999997</v>
+        <v>38822.34</v>
       </c>
       <c r="E65">
         <v>39380.25</v>
@@ -2837,7 +2787,7 @@
         <v>23822.17</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>70</v>
       </c>
@@ -2857,15 +2807,15 @@
         <v>35338.47</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>71</v>
       </c>
       <c r="B67">
-        <v>39109.699999999997</v>
+        <v>39109.7</v>
       </c>
       <c r="C67">
-        <v>39493.550000000003</v>
+        <v>39493.55</v>
       </c>
       <c r="D67">
         <v>38453.94</v>
@@ -2877,18 +2827,18 @@
         <v>13543.89</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>72</v>
       </c>
       <c r="B68">
-        <v>39303.370000000003</v>
+        <v>39303.37</v>
       </c>
       <c r="C68">
         <v>39421.17</v>
       </c>
       <c r="D68">
-        <v>39233.089999999997</v>
+        <v>39233.09</v>
       </c>
       <c r="E68">
         <v>39329.93</v>
@@ -2897,12 +2847,12 @@
         <v>11514.18</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>73</v>
       </c>
       <c r="B69">
-        <v>39350.910000000003</v>
+        <v>39350.91</v>
       </c>
       <c r="C69">
         <v>39566.61</v>
@@ -2911,21 +2861,21 @@
         <v>38999.14</v>
       </c>
       <c r="E69">
-        <v>39317.230000000003</v>
+        <v>39317.23</v>
       </c>
       <c r="F69">
-        <v>25431.040000000001</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
+        <v>25431.04</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>74</v>
       </c>
       <c r="B70">
-        <v>39033.910000000003</v>
+        <v>39033.91</v>
       </c>
       <c r="C70">
-        <v>39547.699999999997</v>
+        <v>39547.7</v>
       </c>
       <c r="D70">
         <v>38390.94</v>
@@ -2934,10 +2884,10 @@
         <v>38641.61</v>
       </c>
       <c r="F70">
-        <v>31963.360000000001</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
+        <v>31963.36</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
         <v>75</v>
       </c>
@@ -2957,27 +2907,27 @@
         <v>28264.85</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
         <v>76</v>
       </c>
       <c r="B72">
-        <v>38560.410000000003</v>
+        <v>38560.41</v>
       </c>
       <c r="C72">
-        <v>38890.019999999997</v>
+        <v>38890.02</v>
       </c>
       <c r="D72">
-        <v>38429.589999999997</v>
+        <v>38429.59</v>
       </c>
       <c r="E72">
-        <v>38874.910000000003</v>
+        <v>38874.91</v>
       </c>
       <c r="F72">
         <v>25333.74</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
         <v>77</v>
       </c>
@@ -2985,7 +2935,7 @@
         <v>38963.4</v>
       </c>
       <c r="C73">
-        <v>39614.589999999997</v>
+        <v>39614.59</v>
       </c>
       <c r="D73">
         <v>38575.53</v>
@@ -2997,7 +2947,7 @@
         <v>31275.16</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>78</v>
       </c>
@@ -3017,18 +2967,18 @@
         <v>22344.06</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>79</v>
       </c>
       <c r="B75">
-        <v>39023.360000000001</v>
+        <v>39023.36</v>
       </c>
       <c r="C75">
         <v>39561.32</v>
       </c>
       <c r="D75">
-        <v>38346.910000000003</v>
+        <v>38346.91</v>
       </c>
       <c r="E75">
         <v>39202.5</v>
@@ -3037,12 +2987,12 @@
         <v>30297.64</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>80</v>
       </c>
       <c r="B76">
-        <v>38950.160000000003</v>
+        <v>38950.16</v>
       </c>
       <c r="C76">
         <v>39603.06</v>
@@ -3057,7 +3007,7 @@
         <v>11093.54</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>81</v>
       </c>
@@ -3065,19 +3015,19 @@
         <v>39364.18</v>
       </c>
       <c r="C77">
-        <v>39934.379999999997</v>
+        <v>39934.38</v>
       </c>
       <c r="D77">
         <v>38712.74</v>
       </c>
       <c r="E77">
-        <v>38889.410000000003</v>
+        <v>38889.41</v>
       </c>
       <c r="F77">
         <v>24923.29</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
         <v>82</v>
       </c>
@@ -3085,10 +3035,10 @@
         <v>38851.08</v>
       </c>
       <c r="C78">
-        <v>39103.879999999997</v>
+        <v>39103.88</v>
       </c>
       <c r="D78">
-        <v>38480.800000000003</v>
+        <v>38480.8</v>
       </c>
       <c r="E78">
         <v>38726.97</v>
@@ -3097,15 +3047,15 @@
         <v>19945.18</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
         <v>83</v>
       </c>
       <c r="B79">
-        <v>38876.379999999997</v>
+        <v>38876.38</v>
       </c>
       <c r="C79">
-        <v>39119.769999999997</v>
+        <v>39119.77</v>
       </c>
       <c r="D79">
         <v>38479.83</v>
@@ -3117,7 +3067,7 @@
         <v>18663.41</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
         <v>84</v>
       </c>
@@ -3125,24 +3075,24 @@
         <v>38569.65</v>
       </c>
       <c r="C80">
-        <v>39126.839999999997</v>
+        <v>39126.84</v>
       </c>
       <c r="D80">
         <v>37621.89</v>
       </c>
       <c r="E80">
-        <v>38932.839999999997</v>
+        <v>38932.84</v>
       </c>
       <c r="F80">
         <v>27220.76</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>85</v>
       </c>
       <c r="B81">
-        <v>38942.050000000003</v>
+        <v>38942.05</v>
       </c>
       <c r="C81">
         <v>39234.89</v>
@@ -3151,13 +3101,13 @@
         <v>38204.53</v>
       </c>
       <c r="E81">
-        <v>38331.089999999997</v>
+        <v>38331.09</v>
       </c>
       <c r="F81">
         <v>19324.72</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>86</v>
       </c>
@@ -3177,18 +3127,18 @@
         <v>21716.97</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>87</v>
       </c>
       <c r="B83">
-        <v>37820.959999999999</v>
+        <v>37820.96</v>
       </c>
       <c r="C83">
         <v>37999.24</v>
       </c>
       <c r="D83">
-        <v>37287.199999999997</v>
+        <v>37287.2</v>
       </c>
       <c r="E83">
         <v>37291.58</v>
@@ -3197,18 +3147,18 @@
         <v>29403.88</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>88</v>
       </c>
       <c r="B84">
-        <v>36922.980000000003</v>
+        <v>36922.98</v>
       </c>
       <c r="C84">
         <v>37193.43</v>
       </c>
       <c r="D84">
-        <v>36709.339999999997</v>
+        <v>36709.34</v>
       </c>
       <c r="E84">
         <v>36735.65</v>
@@ -3217,7 +3167,7 @@
         <v>25310.69</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>89</v>
       </c>
@@ -3228,36 +3178,36 @@
         <v>38162.33</v>
       </c>
       <c r="D85">
-        <v>36705.919999999998</v>
+        <v>36705.92</v>
       </c>
       <c r="E85">
-        <v>38019.129999999997</v>
+        <v>38019.13</v>
       </c>
       <c r="F85">
-        <v>20752.599999999999</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.45">
+        <v>20752.6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
         <v>90</v>
       </c>
       <c r="B86">
-        <v>38251.129999999997</v>
+        <v>38251.13</v>
       </c>
       <c r="C86">
-        <v>38898.400000000001</v>
+        <v>38898.4</v>
       </c>
       <c r="D86">
         <v>37915.32</v>
       </c>
       <c r="E86">
-        <v>38204.400000000001</v>
+        <v>38204.4</v>
       </c>
       <c r="F86">
         <v>26555.51</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
         <v>91</v>
       </c>
@@ -3265,19 +3215,19 @@
         <v>37742.93</v>
       </c>
       <c r="C87">
-        <v>38002.019999999997</v>
+        <v>38002.02</v>
       </c>
       <c r="D87">
         <v>37344.43</v>
       </c>
       <c r="E87">
-        <v>37621.019999999997</v>
+        <v>37621.02</v>
       </c>
       <c r="F87">
         <v>28581.72</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
         <v>92</v>
       </c>
@@ -3285,67 +3235,67 @@
         <v>37156.76</v>
       </c>
       <c r="C88">
-        <v>37439.120000000003</v>
+        <v>37439.12</v>
       </c>
       <c r="D88">
         <v>36874.25</v>
       </c>
       <c r="E88">
-        <v>37293.370000000003</v>
+        <v>37293.37</v>
       </c>
       <c r="F88">
         <v>22281.81</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>93</v>
       </c>
       <c r="B89">
-        <v>36964.639999999999</v>
+        <v>36964.64</v>
       </c>
       <c r="C89">
         <v>37399.29</v>
       </c>
       <c r="D89">
-        <v>36120.300000000003</v>
+        <v>36120.3</v>
       </c>
       <c r="E89">
-        <v>36247.879999999997</v>
+        <v>36247.88</v>
       </c>
       <c r="F89">
-        <v>18563.330000000002</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.45">
+        <v>18563.33</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>94</v>
       </c>
       <c r="B90">
-        <v>36399.040000000001</v>
+        <v>36399.04</v>
       </c>
       <c r="C90">
         <v>37201.26</v>
       </c>
       <c r="D90">
-        <v>35717.980000000003</v>
+        <v>35717.98</v>
       </c>
       <c r="E90">
-        <v>36019.160000000003</v>
+        <v>36019.16</v>
       </c>
       <c r="F90">
         <v>25382.95</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>95</v>
       </c>
       <c r="B91">
-        <v>35960.239999999998</v>
+        <v>35960.24</v>
       </c>
       <c r="C91">
-        <v>36462.449999999997</v>
+        <v>36462.45</v>
       </c>
       <c r="D91">
         <v>35616.03</v>
@@ -3354,10 +3304,10 @@
         <v>35693.96</v>
       </c>
       <c r="F91">
-        <v>33582.730000000003</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.45">
+        <v>33582.73</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>96</v>
       </c>
@@ -3368,24 +3318,24 @@
         <v>36028.19</v>
       </c>
       <c r="D92">
-        <v>35144.160000000003</v>
+        <v>35144.16</v>
       </c>
       <c r="E92">
         <v>35301</v>
       </c>
       <c r="F92">
-        <v>17542.509999999998</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.45">
+        <v>17542.51</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
         <v>97</v>
       </c>
       <c r="B93">
-        <v>35267.160000000003</v>
+        <v>35267.16</v>
       </c>
       <c r="C93">
-        <v>35972.269999999997</v>
+        <v>35972.27</v>
       </c>
       <c r="D93">
         <v>34806.71</v>
@@ -3394,15 +3344,15 @@
         <v>35417.79</v>
       </c>
       <c r="F93">
-        <v>29968.720000000001</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.45">
+        <v>29968.72</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
         <v>98</v>
       </c>
       <c r="B94">
-        <v>36125.279999999999</v>
+        <v>36125.28</v>
       </c>
       <c r="C94">
         <v>36439.24</v>
@@ -3417,7 +3367,7 @@
         <v>28933.47</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
         <v>99</v>
       </c>
@@ -3431,13 +3381,13 @@
         <v>36077.68</v>
       </c>
       <c r="E95">
-        <v>36555.519999999997</v>
+        <v>36555.52</v>
       </c>
       <c r="F95">
-        <v>36088.639999999999</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.45">
+        <v>36088.64</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
         <v>100</v>
       </c>
@@ -3457,18 +3407,18 @@
         <v>46453.81</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
         <v>101</v>
       </c>
       <c r="B97">
-        <v>36831.919999999998</v>
+        <v>36831.92</v>
       </c>
       <c r="C97">
         <v>37045.75</v>
       </c>
       <c r="D97">
-        <v>36250.129999999997</v>
+        <v>36250.13</v>
       </c>
       <c r="E97">
         <v>36868.97</v>
@@ -3477,7 +3427,7 @@
         <v>31077.08</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
         <v>102</v>
       </c>
@@ -3488,7 +3438,7 @@
         <v>36905.57</v>
       </c>
       <c r="D98">
-        <v>36327.339999999997</v>
+        <v>36327.34</v>
       </c>
       <c r="E98">
         <v>36539.03</v>
@@ -3497,7 +3447,7 @@
         <v>12190.82</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
         <v>103</v>
       </c>
@@ -3514,15 +3464,15 @@
         <v>36350.61</v>
       </c>
       <c r="F99">
-        <v>39817.949999999997</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.45">
+        <v>39817.95</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
         <v>104</v>
       </c>
       <c r="B100">
-        <v>36129.050000000003</v>
+        <v>36129.05</v>
       </c>
       <c r="C100">
         <v>36536.22</v>
@@ -3537,7 +3487,7 @@
         <v>30969.41</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
         <v>105</v>
       </c>
@@ -3548,16 +3498,16 @@
         <v>37353.56</v>
       </c>
       <c r="D101">
-        <v>36415.910000000003</v>
+        <v>36415.91</v>
       </c>
       <c r="E101">
-        <v>37159.339999999997</v>
+        <v>37159.34</v>
       </c>
       <c r="F101">
-        <v>27480.240000000002</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.45">
+        <v>27480.24</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
         <v>106</v>
       </c>
@@ -3568,7 +3518,7 @@
         <v>37345.58</v>
       </c>
       <c r="D102">
-        <v>36705.839999999997</v>
+        <v>36705.84</v>
       </c>
       <c r="E102">
         <v>36711.82</v>
@@ -3577,7 +3527,7 @@
         <v>26353.55</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
         <v>107</v>
       </c>
@@ -3588,7 +3538,7 @@
         <v>37505.67</v>
       </c>
       <c r="D103">
-        <v>36872.449999999997</v>
+        <v>36872.45</v>
       </c>
       <c r="E103">
         <v>36959.51</v>
@@ -3597,15 +3547,15 @@
         <v>32263.73</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
         <v>108</v>
       </c>
       <c r="B104">
-        <v>36606.800000000003</v>
+        <v>36606.8</v>
       </c>
       <c r="C104">
-        <v>37011.599999999999</v>
+        <v>37011.6</v>
       </c>
       <c r="D104">
         <v>36127.42</v>
@@ -3617,7 +3567,7 @@
         <v>19679.07</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
         <v>109</v>
       </c>
@@ -3628,24 +3578,24 @@
         <v>37260.49</v>
       </c>
       <c r="D105">
-        <v>36731.199999999997</v>
+        <v>36731.2</v>
       </c>
       <c r="E105">
         <v>36929.42</v>
       </c>
       <c r="F105">
-        <v>18416.919999999998</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.45">
+        <v>18416.92</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
         <v>110</v>
       </c>
       <c r="B106">
-        <v>37397.410000000003</v>
+        <v>37397.41</v>
       </c>
       <c r="C106">
-        <v>37920.370000000003</v>
+        <v>37920.37</v>
       </c>
       <c r="D106">
         <v>36678.33</v>
@@ -3657,7 +3607,7 @@
         <v>20191.71</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
         <v>111</v>
       </c>
@@ -3668,7 +3618,7 @@
         <v>38239.51</v>
       </c>
       <c r="D107">
-        <v>37766.239999999998</v>
+        <v>37766.24</v>
       </c>
       <c r="E107">
         <v>38096.43</v>
@@ -3677,7 +3627,7 @@
         <v>14383.28</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:6">
       <c r="A108" t="s">
         <v>112</v>
       </c>
@@ -3691,13 +3641,13 @@
         <v>37671.93</v>
       </c>
       <c r="E108">
-        <v>37979.919999999998</v>
+        <v>37979.92</v>
       </c>
       <c r="F108">
         <v>22880.19</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:6">
       <c r="A109" t="s">
         <v>113</v>
       </c>
@@ -3711,13 +3661,13 @@
         <v>37454.58</v>
       </c>
       <c r="E109">
-        <v>37945.910000000003</v>
+        <v>37945.91</v>
       </c>
       <c r="F109">
         <v>42570.33</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:6">
       <c r="A110" t="s">
         <v>114</v>
       </c>
@@ -3734,10 +3684,10 @@
         <v>37867.79</v>
       </c>
       <c r="F110">
-        <v>18097.310000000001</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.45">
+        <v>18097.31</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
       <c r="A111" t="s">
         <v>115</v>
       </c>
@@ -3748,16 +3698,16 @@
         <v>39130.69</v>
       </c>
       <c r="D111">
-        <v>38044.120000000003</v>
+        <v>38044.12</v>
       </c>
       <c r="E111">
-        <v>38837.230000000003</v>
+        <v>38837.23</v>
       </c>
       <c r="F111">
         <v>19037.18</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:6">
       <c r="A112" t="s">
         <v>116</v>
       </c>
@@ -3765,24 +3715,24 @@
         <v>38572.22</v>
       </c>
       <c r="C112">
-        <v>39097.730000000003</v>
+        <v>39097.73</v>
       </c>
       <c r="D112">
         <v>38311.21</v>
       </c>
       <c r="E112">
-        <v>38670.980000000003</v>
+        <v>38670.98</v>
       </c>
       <c r="F112">
         <v>27264.69</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>117</v>
       </c>
       <c r="B113">
-        <v>38377.879999999997</v>
+        <v>38377.88</v>
       </c>
       <c r="C113">
         <v>38637.93</v>
@@ -3797,52 +3747,52 @@
         <v>29774.67</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>118</v>
       </c>
       <c r="B114">
-        <v>38142.980000000003</v>
+        <v>38142.98</v>
       </c>
       <c r="C114">
-        <v>38521.519999999997</v>
+        <v>38521.52</v>
       </c>
       <c r="D114">
-        <v>37833.379999999997</v>
+        <v>37833.38</v>
       </c>
       <c r="E114">
-        <v>37975.949999999997</v>
+        <v>37975.95</v>
       </c>
       <c r="F114">
         <v>27796.87</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
         <v>119</v>
       </c>
       <c r="B115">
-        <v>37975.699999999997</v>
+        <v>37975.7</v>
       </c>
       <c r="C115">
         <v>38063.57</v>
       </c>
       <c r="D115">
-        <v>37762.800000000003</v>
+        <v>37762.8</v>
       </c>
       <c r="E115">
-        <v>37795.519999999997</v>
+        <v>37795.52</v>
       </c>
       <c r="F115">
         <v>14751.53</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
         <v>120</v>
       </c>
       <c r="B116">
-        <v>38155.360000000001</v>
+        <v>38155.36</v>
       </c>
       <c r="C116">
         <v>38668.14</v>
@@ -3851,21 +3801,21 @@
         <v>37711.5</v>
       </c>
       <c r="E116">
-        <v>38365.410000000003</v>
+        <v>38365.41</v>
       </c>
       <c r="F116">
         <v>8735.48</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
         <v>121</v>
       </c>
       <c r="B117">
-        <v>38362.800000000003</v>
+        <v>38362.8</v>
       </c>
       <c r="C117">
-        <v>38735.019999999997</v>
+        <v>38735.02</v>
       </c>
       <c r="D117">
         <v>37924.03</v>
@@ -3877,32 +3827,32 @@
         <v>31459.8</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
         <v>122</v>
       </c>
       <c r="B118">
-        <v>38507.269999999997</v>
+        <v>38507.27</v>
       </c>
       <c r="C118">
-        <v>38749.160000000003</v>
+        <v>38749.16</v>
       </c>
       <c r="D118">
-        <v>37948.300000000003</v>
+        <v>37948.3</v>
       </c>
       <c r="E118">
         <v>38395.9</v>
       </c>
       <c r="F118">
-        <v>40580.910000000003</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.45">
+        <v>40580.91</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
         <v>123</v>
       </c>
       <c r="B119">
-        <v>38338.160000000003</v>
+        <v>38338.16</v>
       </c>
       <c r="C119">
         <v>38908.1</v>
@@ -3911,13 +3861,13 @@
         <v>38290.46</v>
       </c>
       <c r="E119">
-        <v>38595.480000000003</v>
+        <v>38595.48</v>
       </c>
       <c r="F119">
-        <v>19354.919999999998</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.45">
+        <v>19354.92</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
         <v>124</v>
       </c>
@@ -3925,19 +3875,19 @@
         <v>38775.47</v>
       </c>
       <c r="C120">
-        <v>38985.879999999997</v>
+        <v>38985.88</v>
       </c>
       <c r="D120">
-        <v>38365.910000000003</v>
+        <v>38365.91</v>
       </c>
       <c r="E120">
         <v>38819.53</v>
       </c>
       <c r="F120">
-        <v>34347.199999999997</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.45">
+        <v>34347.2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
         <v>125</v>
       </c>
@@ -3945,19 +3895,19 @@
         <v>38651.61</v>
       </c>
       <c r="C121">
-        <v>39197.449999999997</v>
+        <v>39197.45</v>
       </c>
       <c r="D121">
         <v>38281.43</v>
       </c>
       <c r="E121">
-        <v>38353.589999999997</v>
+        <v>38353.59</v>
       </c>
       <c r="F121">
         <v>28031.46</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:6">
       <c r="A122" t="s">
         <v>126</v>
       </c>
@@ -3965,19 +3915,19 @@
         <v>37724.15</v>
       </c>
       <c r="C122">
-        <v>38362.300000000003</v>
+        <v>38362.3</v>
       </c>
       <c r="D122">
-        <v>37189.379999999997</v>
+        <v>37189.38</v>
       </c>
       <c r="E122">
-        <v>37617.360000000001</v>
+        <v>37617.36</v>
       </c>
       <c r="F122">
         <v>26078.92</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
         <v>127</v>
       </c>
@@ -3991,13 +3941,13 @@
         <v>36796.83</v>
       </c>
       <c r="E123">
-        <v>37602.269999999997</v>
+        <v>37602.27</v>
       </c>
       <c r="F123">
         <v>16118.51</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
         <v>128</v>
       </c>
@@ -4008,7 +3958,7 @@
         <v>37702.82</v>
       </c>
       <c r="D124">
-        <v>36925.980000000003</v>
+        <v>36925.98</v>
       </c>
       <c r="E124">
         <v>37056.35</v>
@@ -4017,7 +3967,7 @@
         <v>22857.58</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>129</v>
       </c>
@@ -4031,13 +3981,13 @@
         <v>36920.51</v>
       </c>
       <c r="E125">
-        <v>36972.019999999997</v>
+        <v>36972.02</v>
       </c>
       <c r="F125">
         <v>25693.21</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
         <v>130</v>
       </c>
@@ -4057,7 +4007,7 @@
         <v>29697.26</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
         <v>131</v>
       </c>
@@ -4071,13 +4021,13 @@
         <v>36899.64</v>
       </c>
       <c r="E127">
-        <v>37190.800000000003</v>
+        <v>37190.8</v>
       </c>
       <c r="F127">
         <v>28183.51</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
         <v>132</v>
       </c>
@@ -4085,7 +4035,7 @@
         <v>37373.43</v>
       </c>
       <c r="C128">
-        <v>37630.370000000003</v>
+        <v>37630.37</v>
       </c>
       <c r="D128">
         <v>37041.5</v>
@@ -4097,12 +4047,12 @@
         <v>33184.43</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:6">
       <c r="A129" t="s">
         <v>133</v>
       </c>
       <c r="B129">
-        <v>36982.199999999997</v>
+        <v>36982.2</v>
       </c>
       <c r="C129">
         <v>37312.75</v>
@@ -4117,7 +4067,7 @@
         <v>26696.79</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:6">
       <c r="A130" t="s">
         <v>134</v>
       </c>
@@ -4128,7 +4078,7 @@
         <v>37713.51</v>
       </c>
       <c r="D130">
-        <v>36791.730000000003</v>
+        <v>36791.73</v>
       </c>
       <c r="E130">
         <v>37482.93</v>
@@ -4137,7 +4087,7 @@
         <v>28560.04</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:6">
       <c r="A131" t="s">
         <v>135</v>
       </c>
@@ -4151,21 +4101,21 @@
         <v>37258.71</v>
       </c>
       <c r="E131">
-        <v>37386.199999999997</v>
+        <v>37386.2</v>
       </c>
       <c r="F131">
-        <v>30030.240000000002</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.45">
+        <v>30030.24</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
       <c r="A132" t="s">
         <v>136</v>
       </c>
       <c r="B132">
-        <v>37841.120000000003</v>
+        <v>37841.12</v>
       </c>
       <c r="C132">
-        <v>38093.839999999997</v>
+        <v>38093.84</v>
       </c>
       <c r="D132">
         <v>37109.86</v>
@@ -4177,27 +4127,27 @@
         <v>21763.74</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:6">
       <c r="A133" t="s">
         <v>137</v>
       </c>
       <c r="B133">
-        <v>36825.199999999997</v>
+        <v>36825.2</v>
       </c>
       <c r="C133">
         <v>37156.85</v>
       </c>
       <c r="D133">
-        <v>36347.879999999997</v>
+        <v>36347.88</v>
       </c>
       <c r="E133">
-        <v>36406.120000000003</v>
+        <v>36406.12</v>
       </c>
       <c r="F133">
         <v>25246.82</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:6">
       <c r="A134" t="s">
         <v>138</v>
       </c>
@@ -4208,16 +4158,16 @@
         <v>36733.53</v>
       </c>
       <c r="D134">
-        <v>36130.379999999997</v>
+        <v>36130.38</v>
       </c>
       <c r="E134">
-        <v>36150.449999999997</v>
+        <v>36150.45</v>
       </c>
       <c r="F134">
         <v>28869.8</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:6">
       <c r="A135" t="s">
         <v>139</v>
       </c>
@@ -4225,19 +4175,19 @@
         <v>35944.44</v>
       </c>
       <c r="C135">
-        <v>36093.870000000003</v>
+        <v>36093.87</v>
       </c>
       <c r="D135">
         <v>35545.25</v>
       </c>
       <c r="E135">
-        <v>36060.379999999997</v>
+        <v>36060.38</v>
       </c>
       <c r="F135">
-        <v>32214.560000000001</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.45">
+        <v>32214.56</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
       <c r="A136" t="s">
         <v>140</v>
       </c>
@@ -4245,7 +4195,7 @@
         <v>36347.53</v>
       </c>
       <c r="C136">
-        <v>36814.660000000003</v>
+        <v>36814.66</v>
       </c>
       <c r="D136">
         <v>35691.97</v>
@@ -4257,7 +4207,7 @@
         <v>24031.26</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:6">
       <c r="A137" t="s">
         <v>141</v>
       </c>
@@ -4265,7 +4215,7 @@
         <v>35842.29</v>
       </c>
       <c r="C137">
-        <v>36339.339999999997</v>
+        <v>36339.34</v>
       </c>
       <c r="D137">
         <v>35791.83</v>
@@ -4277,12 +4227,12 @@
         <v>19140.7</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:6">
       <c r="A138" t="s">
         <v>142</v>
       </c>
       <c r="B138">
-        <v>36124.660000000003</v>
+        <v>36124.66</v>
       </c>
       <c r="C138">
         <v>36473.97</v>
@@ -4291,13 +4241,13 @@
         <v>35937.39</v>
       </c>
       <c r="E138">
-        <v>36095.919999999998</v>
+        <v>36095.92</v>
       </c>
       <c r="F138">
         <v>34495.9</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:6">
       <c r="A139" t="s">
         <v>143</v>
       </c>
@@ -4305,19 +4255,19 @@
         <v>35996.35</v>
       </c>
       <c r="C139">
-        <v>36479.620000000003</v>
+        <v>36479.62</v>
       </c>
       <c r="D139">
         <v>35667.67</v>
       </c>
       <c r="E139">
-        <v>35687.410000000003</v>
+        <v>35687.41</v>
       </c>
       <c r="F139">
         <v>42507.12</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:6">
       <c r="A140" t="s">
         <v>144</v>
       </c>
@@ -4328,16 +4278,16 @@
         <v>36213.72</v>
       </c>
       <c r="D140">
-        <v>35730.639999999999</v>
+        <v>35730.64</v>
       </c>
       <c r="E140">
-        <v>36021.089999999997</v>
+        <v>36021.09</v>
       </c>
       <c r="F140">
-        <v>35051.879999999997</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.45">
+        <v>35051.88</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
       <c r="A141" t="s">
         <v>145</v>
       </c>
@@ -4351,33 +4301,33 @@
         <v>35655.42</v>
       </c>
       <c r="E141">
-        <v>35802.629999999997</v>
+        <v>35802.63</v>
       </c>
       <c r="F141">
         <v>25586.35</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:6">
       <c r="A142" t="s">
         <v>146</v>
       </c>
       <c r="B142">
-        <v>35790.699999999997</v>
+        <v>35790.7</v>
       </c>
       <c r="C142">
-        <v>36163.379999999997</v>
+        <v>36163.38</v>
       </c>
       <c r="D142">
-        <v>35699.550000000003</v>
+        <v>35699.55</v>
       </c>
       <c r="E142">
-        <v>36001.870000000003</v>
+        <v>36001.87</v>
       </c>
       <c r="F142">
-        <v>17110.830000000002</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.45">
+        <v>17110.83</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="A143" t="s">
         <v>147</v>
       </c>
@@ -4388,7 +4338,7 @@
         <v>36747.43</v>
       </c>
       <c r="D143">
-        <v>36142.980000000003</v>
+        <v>36142.98</v>
       </c>
       <c r="E143">
         <v>36184.5</v>
@@ -4397,7 +4347,7 @@
         <v>25332.5</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:6">
       <c r="A144" t="s">
         <v>148</v>
       </c>
@@ -4405,10 +4355,10 @@
         <v>35778.97</v>
       </c>
       <c r="C144">
-        <v>36222.239999999998</v>
+        <v>36222.24</v>
       </c>
       <c r="D144">
-        <v>34919.550000000003</v>
+        <v>34919.55</v>
       </c>
       <c r="E144">
         <v>35865.94</v>
@@ -4417,7 +4367,7 @@
         <v>16796.84</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:6">
       <c r="A145" t="s">
         <v>149</v>
       </c>
@@ -4425,7 +4375,7 @@
         <v>36031.32</v>
       </c>
       <c r="C145">
-        <v>36771.129999999997</v>
+        <v>36771.13</v>
       </c>
       <c r="D145">
         <v>35534.46</v>
@@ -4437,7 +4387,7 @@
         <v>16866.38</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:6">
       <c r="A146" t="s">
         <v>150</v>
       </c>
@@ -4451,13 +4401,13 @@
         <v>35819.29</v>
       </c>
       <c r="E146">
-        <v>36746.879999999997</v>
+        <v>36746.88</v>
       </c>
       <c r="F146">
         <v>24771.79</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:6">
       <c r="A147" t="s">
         <v>151</v>
       </c>
@@ -4468,7 +4418,7 @@
         <v>37395.57</v>
       </c>
       <c r="D147">
-        <v>36577.519999999997</v>
+        <v>36577.52</v>
       </c>
       <c r="E147">
         <v>36835</v>
@@ -4477,7 +4427,7 @@
         <v>23735.31</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:6">
       <c r="A148" t="s">
         <v>152</v>
       </c>
@@ -4488,16 +4438,16 @@
         <v>37228.25</v>
       </c>
       <c r="D148">
-        <v>36413.279999999999</v>
+        <v>36413.28</v>
       </c>
       <c r="E148">
-        <v>36417.050000000003</v>
+        <v>36417.05</v>
       </c>
       <c r="F148">
         <v>31231.85</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:6">
       <c r="A149" t="s">
         <v>153</v>
       </c>
@@ -4511,13 +4461,13 @@
         <v>36016.26</v>
       </c>
       <c r="E149">
-        <v>36794.660000000003</v>
+        <v>36794.66</v>
       </c>
       <c r="F149">
         <v>28401.5</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:6">
       <c r="A150" t="s">
         <v>154</v>
       </c>
@@ -4525,7 +4475,7 @@
         <v>36840.86</v>
       </c>
       <c r="C150">
-        <v>37296.559999999998</v>
+        <v>37296.56</v>
       </c>
       <c r="D150">
         <v>36519.06</v>
@@ -4537,12 +4487,12 @@
         <v>28934.91</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:6">
       <c r="A151" t="s">
         <v>155</v>
       </c>
       <c r="B151">
-        <v>36611.480000000003</v>
+        <v>36611.48</v>
       </c>
       <c r="C151">
         <v>37189.19</v>
@@ -4557,7 +4507,7 @@
         <v>32281.1</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:6">
       <c r="A152" t="s">
         <v>156</v>
       </c>
@@ -4565,7 +4515,7 @@
         <v>37271.17</v>
       </c>
       <c r="C152">
-        <v>37645.089999999997</v>
+        <v>37645.09</v>
       </c>
       <c r="D152">
         <v>36989.75</v>
@@ -4577,7 +4527,7 @@
         <v>32187.72</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:6">
       <c r="A153" t="s">
         <v>157</v>
       </c>
@@ -4597,7 +4547,7 @@
         <v>31965.5</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:6">
       <c r="A154" t="s">
         <v>158</v>
       </c>
@@ -4605,10 +4555,10 @@
         <v>36976.32</v>
       </c>
       <c r="C154">
-        <v>37153.949999999997</v>
+        <v>37153.95</v>
       </c>
       <c r="D154">
-        <v>36708.339999999997</v>
+        <v>36708.34</v>
       </c>
       <c r="E154">
         <v>37090.94</v>
@@ -4617,15 +4567,15 @@
         <v>21699.79</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:6">
       <c r="A155" t="s">
         <v>159</v>
       </c>
       <c r="B155">
-        <v>37065.800000000003</v>
+        <v>37065.8</v>
       </c>
       <c r="C155">
-        <v>37809.730000000003</v>
+        <v>37809.73</v>
       </c>
       <c r="D155">
         <v>36905.18</v>
@@ -4637,7 +4587,7 @@
         <v>23148.48</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:6">
       <c r="A156" t="s">
         <v>160</v>
       </c>
@@ -4651,38 +4601,38 @@
         <v>36762.86</v>
       </c>
       <c r="E156">
-        <v>36884.239999999998</v>
+        <v>36884.24</v>
       </c>
       <c r="F156">
         <v>31925.9</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:6">
       <c r="A157" t="s">
         <v>161</v>
       </c>
       <c r="B157">
-        <v>36723.660000000003</v>
+        <v>36723.66</v>
       </c>
       <c r="C157">
         <v>37145.29</v>
       </c>
       <c r="D157">
-        <v>36453.089999999997</v>
+        <v>36453.09</v>
       </c>
       <c r="E157">
-        <v>36753.589999999997</v>
+        <v>36753.59</v>
       </c>
       <c r="F157">
         <v>20756.71</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:6">
       <c r="A158" t="s">
         <v>162</v>
       </c>
       <c r="B158">
-        <v>37173.910000000003</v>
+        <v>37173.91</v>
       </c>
       <c r="C158">
         <v>37822.68</v>
@@ -4691,13 +4641,13 @@
         <v>36994.97</v>
       </c>
       <c r="E158">
-        <v>37215.730000000003</v>
+        <v>37215.73</v>
       </c>
       <c r="F158">
         <v>27134.57</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:6">
       <c r="A159" t="s">
         <v>163</v>
       </c>
@@ -4708,21 +4658,21 @@
         <v>37581.22</v>
       </c>
       <c r="D159">
-        <v>36653.160000000003</v>
+        <v>36653.16</v>
       </c>
       <c r="E159">
         <v>37208.5</v>
       </c>
       <c r="F159">
-        <v>30049.439999999999</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.45">
+        <v>30049.44</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
       <c r="A160" t="s">
         <v>164</v>
       </c>
       <c r="B160">
-        <v>37462.160000000003</v>
+        <v>37462.16</v>
       </c>
       <c r="C160">
         <v>37546.25</v>
@@ -4731,18 +4681,18 @@
         <v>37291.08</v>
       </c>
       <c r="E160">
-        <v>37473.550000000003</v>
+        <v>37473.55</v>
       </c>
       <c r="F160">
         <v>22944.89</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:6">
       <c r="A161" t="s">
         <v>165</v>
       </c>
       <c r="B161">
-        <v>37729.519999999997</v>
+        <v>37729.52</v>
       </c>
       <c r="C161">
         <v>38143.26</v>
@@ -4757,7 +4707,7 @@
         <v>21681.45</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:6">
       <c r="A162" t="s">
         <v>166</v>
       </c>
@@ -4765,7 +4715,7 @@
         <v>37897.11</v>
       </c>
       <c r="C162">
-        <v>38332.629999999997</v>
+        <v>38332.63</v>
       </c>
       <c r="D162">
         <v>37471.81</v>
@@ -4774,10 +4724,10 @@
         <v>38184.04</v>
       </c>
       <c r="F162">
-        <v>33248.339999999997</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.45">
+        <v>33248.34</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
       <c r="A163" t="s">
         <v>167</v>
       </c>
@@ -4791,21 +4741,21 @@
         <v>37560.78</v>
       </c>
       <c r="E163">
-        <v>37764.720000000001</v>
+        <v>37764.72</v>
       </c>
       <c r="F163">
         <v>31030.47</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:6">
       <c r="A164" t="s">
         <v>168</v>
       </c>
       <c r="B164">
-        <v>38395.230000000003</v>
+        <v>38395.23</v>
       </c>
       <c r="C164">
-        <v>38448.080000000002</v>
+        <v>38448.08</v>
       </c>
       <c r="D164">
         <v>37657.24</v>
@@ -4814,10 +4764,10 @@
         <v>38446.46</v>
       </c>
       <c r="F164">
-        <v>20682.810000000001</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.45">
+        <v>20682.81</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
       <c r="A165" t="s">
         <v>169</v>
       </c>
@@ -4837,7 +4787,7 @@
         <v>29262.1</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:6">
       <c r="A166" t="s">
         <v>170</v>
       </c>
@@ -4845,10 +4795,10 @@
         <v>38440.29</v>
       </c>
       <c r="C166">
-        <v>38827.120000000003</v>
+        <v>38827.12</v>
       </c>
       <c r="D166">
-        <v>38134.379999999997</v>
+        <v>38134.38</v>
       </c>
       <c r="E166">
         <v>38208.57</v>
@@ -4857,15 +4807,15 @@
         <v>28871.14</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:6">
       <c r="A167" t="s">
         <v>171</v>
       </c>
       <c r="B167">
-        <v>38009.730000000003</v>
+        <v>38009.73</v>
       </c>
       <c r="C167">
-        <v>38284.980000000003</v>
+        <v>38284.98</v>
       </c>
       <c r="D167">
         <v>37478.07</v>
@@ -4877,12 +4827,12 @@
         <v>12691.34</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:6">
       <c r="A168" t="s">
         <v>172</v>
       </c>
       <c r="B168">
-        <v>37826.480000000003</v>
+        <v>37826.48</v>
       </c>
       <c r="C168">
         <v>38327.57</v>
@@ -4897,7 +4847,7 @@
         <v>26439.52</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:6">
       <c r="A169" t="s">
         <v>173</v>
       </c>
@@ -4905,7 +4855,7 @@
         <v>37950.33</v>
       </c>
       <c r="C169">
-        <v>38170.879999999997</v>
+        <v>38170.88</v>
       </c>
       <c r="D169">
         <v>37563.24</v>
@@ -4917,7 +4867,7 @@
         <v>13660.85</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:6">
       <c r="A170" t="s">
         <v>174</v>
       </c>
@@ -4934,10 +4884,10 @@
         <v>38421.61</v>
       </c>
       <c r="F170">
-        <v>9191.31</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.45">
+        <v>9191.309999999999</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
       <c r="A171" t="s">
         <v>175</v>
       </c>
@@ -4951,13 +4901,13 @@
         <v>37959.18</v>
       </c>
       <c r="E171">
-        <v>38697.040000000001</v>
+        <v>38697.04</v>
       </c>
       <c r="F171">
         <v>34390.17</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:6">
       <c r="A172" t="s">
         <v>176</v>
       </c>
@@ -4965,7 +4915,7 @@
         <v>38828.5</v>
       </c>
       <c r="C172">
-        <v>39093.379999999997</v>
+        <v>39093.38</v>
       </c>
       <c r="D172">
         <v>38727.49</v>
@@ -4974,15 +4924,15 @@
         <v>38789.46</v>
       </c>
       <c r="F172">
-        <v>41425.839999999997</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.45">
+        <v>41425.84</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
       <c r="A173" t="s">
         <v>177</v>
       </c>
       <c r="B173">
-        <v>39140.230000000003</v>
+        <v>39140.23</v>
       </c>
       <c r="C173">
         <v>39535.42</v>
@@ -4991,18 +4941,18 @@
         <v>38800.46</v>
       </c>
       <c r="E173">
-        <v>39462.519999999997</v>
+        <v>39462.52</v>
       </c>
       <c r="F173">
         <v>17444.93</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:6">
       <c r="A174" t="s">
         <v>178</v>
       </c>
       <c r="B174">
-        <v>39649.410000000003</v>
+        <v>39649.41</v>
       </c>
       <c r="C174">
         <v>39832.06</v>
@@ -5011,13 +4961,13 @@
         <v>39071.94</v>
       </c>
       <c r="E174">
-        <v>39311.599999999999</v>
+        <v>39311.6</v>
       </c>
       <c r="F174">
         <v>14176.43</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:6">
       <c r="A175" t="s">
         <v>179</v>
       </c>
@@ -5025,10 +4975,10 @@
         <v>39464.47</v>
       </c>
       <c r="C175">
-        <v>39792.199999999997</v>
+        <v>39792.2</v>
       </c>
       <c r="D175">
-        <v>38863.279999999999</v>
+        <v>38863.28</v>
       </c>
       <c r="E175">
         <v>39782.65</v>
@@ -5037,7 +4987,7 @@
         <v>27565.46</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:6">
       <c r="A176" t="s">
         <v>180</v>
       </c>
@@ -5057,15 +5007,15 @@
         <v>14185.1</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:6">
       <c r="A177" t="s">
         <v>181</v>
       </c>
       <c r="B177">
-        <v>40062.120000000003</v>
+        <v>40062.12</v>
       </c>
       <c r="C177">
-        <v>40392.870000000003</v>
+        <v>40392.87</v>
       </c>
       <c r="D177">
         <v>39353.65</v>
@@ -5074,10 +5024,10 @@
         <v>40320.54</v>
       </c>
       <c r="F177">
-        <v>24597.040000000001</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.45">
+        <v>24597.04</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
       <c r="A178" t="s">
         <v>182</v>
       </c>
@@ -5085,10 +5035,10 @@
         <v>40462.89</v>
       </c>
       <c r="C178">
-        <v>40981.660000000003</v>
+        <v>40981.66</v>
       </c>
       <c r="D178">
-        <v>40092.239999999998</v>
+        <v>40092.24</v>
       </c>
       <c r="E178">
         <v>40286.49</v>
@@ -5097,7 +5047,7 @@
         <v>25051.16</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:6">
       <c r="A179" t="s">
         <v>183</v>
       </c>
@@ -5108,7 +5058,7 @@
         <v>40334.11</v>
       </c>
       <c r="D179">
-        <v>40036.199999999997</v>
+        <v>40036.2</v>
       </c>
       <c r="E179">
         <v>40176.01</v>
@@ -5117,7 +5067,7 @@
         <v>27992.39</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:6">
       <c r="A180" t="s">
         <v>184</v>
       </c>
@@ -5137,7 +5087,7 @@
         <v>17173.36</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:6">
       <c r="A181" t="s">
         <v>185</v>
       </c>
@@ -5151,13 +5101,13 @@
         <v>41057.79</v>
       </c>
       <c r="E181">
-        <v>41335.760000000002</v>
+        <v>41335.76</v>
       </c>
       <c r="F181">
         <v>26651.25</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:6">
       <c r="A182" t="s">
         <v>186</v>
       </c>
@@ -5168,21 +5118,21 @@
         <v>41856.47</v>
       </c>
       <c r="D182">
-        <v>41013.019999999997</v>
+        <v>41013.02</v>
       </c>
       <c r="E182">
         <v>41664.49</v>
       </c>
       <c r="F182">
-        <v>24286.639999999999</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.45">
+        <v>24286.64</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
       <c r="A183" t="s">
         <v>187</v>
       </c>
       <c r="B183">
-        <v>41317.019999999997</v>
+        <v>41317.02</v>
       </c>
       <c r="C183">
         <v>41696.67</v>
@@ -5197,7 +5147,7 @@
         <v>32721.21</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:6">
       <c r="A184" t="s">
         <v>188</v>
       </c>
@@ -5211,13 +5161,13 @@
         <v>40700.14</v>
       </c>
       <c r="E184">
-        <v>40741.089999999997</v>
+        <v>40741.09</v>
       </c>
       <c r="F184">
-        <v>20199.689999999999</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.45">
+        <v>20199.69</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
       <c r="A185" t="s">
         <v>189</v>
       </c>
@@ -5228,7 +5178,7 @@
         <v>41007.71</v>
       </c>
       <c r="D185">
-        <v>40550.620000000003</v>
+        <v>40550.62</v>
       </c>
       <c r="E185">
         <v>40921.57</v>
@@ -5237,15 +5187,15 @@
         <v>12851.98</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:6">
       <c r="A186" t="s">
         <v>190</v>
       </c>
       <c r="B186">
-        <v>40867.949999999997</v>
+        <v>40867.95</v>
       </c>
       <c r="C186">
-        <v>41187.050000000003</v>
+        <v>41187.05</v>
       </c>
       <c r="D186">
         <v>40399.68</v>
@@ -5257,27 +5207,27 @@
         <v>30368.03</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:6">
       <c r="A187" t="s">
         <v>191</v>
       </c>
       <c r="B187">
-        <v>40322.620000000003</v>
+        <v>40322.62</v>
       </c>
       <c r="C187">
         <v>40866.35</v>
       </c>
       <c r="D187">
-        <v>40280.910000000003</v>
+        <v>40280.91</v>
       </c>
       <c r="E187">
         <v>40345.67</v>
       </c>
       <c r="F187">
-        <v>37089.910000000003</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.45">
+        <v>37089.91</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
       <c r="A188" t="s">
         <v>192</v>
       </c>
@@ -5297,7 +5247,7 @@
         <v>26558.32</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:6">
       <c r="A189" t="s">
         <v>193</v>
       </c>
@@ -5305,7 +5255,7 @@
         <v>40058.99</v>
       </c>
       <c r="C189">
-        <v>40495.440000000002</v>
+        <v>40495.44</v>
       </c>
       <c r="D189">
         <v>39494.51</v>
@@ -5317,7 +5267,7 @@
         <v>27256.86</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:6">
       <c r="A190" t="s">
         <v>194</v>
       </c>
@@ -5325,19 +5275,19 @@
         <v>40223.75</v>
       </c>
       <c r="C190">
-        <v>40664.629999999997</v>
+        <v>40664.63</v>
       </c>
       <c r="D190">
-        <v>39837.230000000003</v>
+        <v>39837.23</v>
       </c>
       <c r="E190">
-        <v>39969.360000000001</v>
+        <v>39969.36</v>
       </c>
       <c r="F190">
         <v>35669.51</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:6">
       <c r="A191" t="s">
         <v>195</v>
       </c>
@@ -5345,10 +5295,10 @@
         <v>40291.56</v>
       </c>
       <c r="C191">
-        <v>40545.160000000003</v>
+        <v>40545.16</v>
       </c>
       <c r="D191">
-        <v>39564.959999999999</v>
+        <v>39564.96</v>
       </c>
       <c r="E191">
         <v>40468.53</v>
@@ -5357,27 +5307,27 @@
         <v>12940.58</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:6">
       <c r="A192" t="s">
         <v>196</v>
       </c>
       <c r="B192">
-        <v>40676.959999999999</v>
+        <v>40676.96</v>
       </c>
       <c r="C192">
-        <v>40710.199999999997</v>
+        <v>40710.2</v>
       </c>
       <c r="D192">
-        <v>40433.699999999997</v>
+        <v>40433.7</v>
       </c>
       <c r="E192">
-        <v>40547.129999999997</v>
+        <v>40547.13</v>
       </c>
       <c r="F192">
         <v>29427.38</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:6">
       <c r="A193" t="s">
         <v>197</v>
       </c>
@@ -5385,10 +5335,10 @@
         <v>40480.68</v>
       </c>
       <c r="C193">
-        <v>40976.480000000003</v>
+        <v>40976.48</v>
       </c>
       <c r="D193">
-        <v>40002.800000000003</v>
+        <v>40002.8</v>
       </c>
       <c r="E193">
         <v>40408.35</v>
@@ -5397,7 +5347,7 @@
         <v>22045.48</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:6">
       <c r="A194" t="s">
         <v>198</v>
       </c>
@@ -5411,18 +5361,18 @@
         <v>40131.9</v>
       </c>
       <c r="E194">
-        <v>40575.879999999997</v>
+        <v>40575.88</v>
       </c>
       <c r="F194">
         <v>28741.38</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:6">
       <c r="A195" t="s">
         <v>199</v>
       </c>
       <c r="B195">
-        <v>40072.519999999997</v>
+        <v>40072.52</v>
       </c>
       <c r="C195">
         <v>40519.47</v>
@@ -5431,24 +5381,24 @@
         <v>39922.46</v>
       </c>
       <c r="E195">
-        <v>40027.629999999997</v>
+        <v>40027.63</v>
       </c>
       <c r="F195">
         <v>15773.57</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:6">
       <c r="A196" t="s">
         <v>200</v>
       </c>
       <c r="B196">
-        <v>40236.239999999998</v>
+        <v>40236.24</v>
       </c>
       <c r="C196">
         <v>40599.24</v>
       </c>
       <c r="D196">
-        <v>39963.760000000002</v>
+        <v>39963.76</v>
       </c>
       <c r="E196">
         <v>40315.08</v>
@@ -5457,7 +5407,7 @@
         <v>24900.11</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:6">
       <c r="A197" t="s">
         <v>201</v>
       </c>
@@ -5471,13 +5421,13 @@
         <v>39622.9</v>
       </c>
       <c r="E197">
-        <v>39905.410000000003</v>
+        <v>39905.41</v>
       </c>
       <c r="F197">
         <v>29363.41</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:6">
       <c r="A198" t="s">
         <v>202</v>
       </c>
@@ -5485,7 +5435,7 @@
         <v>39751.85</v>
       </c>
       <c r="C198">
-        <v>40250.879999999997</v>
+        <v>40250.88</v>
       </c>
       <c r="D198">
         <v>39702.21</v>
@@ -5497,7 +5447,7 @@
         <v>25335.87</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:6">
       <c r="A199" t="s">
         <v>203</v>
       </c>
@@ -5511,13 +5461,13 @@
         <v>39449.29</v>
       </c>
       <c r="E199">
-        <v>40143.589999999997</v>
+        <v>40143.59</v>
       </c>
       <c r="F199">
         <v>25967.68</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:6">
       <c r="A200" t="s">
         <v>204</v>
       </c>
@@ -5525,10 +5475,10 @@
         <v>40323.9</v>
       </c>
       <c r="C200">
-        <v>41022.769999999997</v>
+        <v>41022.77</v>
       </c>
       <c r="D200">
-        <v>39890.120000000003</v>
+        <v>39890.12</v>
       </c>
       <c r="E200">
         <v>39962.17</v>
@@ -5537,7 +5487,7 @@
         <v>28930.63</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:6">
       <c r="A201" t="s">
         <v>205</v>
       </c>
@@ -5545,7 +5495,7 @@
         <v>40652.28</v>
       </c>
       <c r="C201">
-        <v>40858.199999999997</v>
+        <v>40858.2</v>
       </c>
       <c r="D201">
         <v>40591.82</v>
@@ -5557,12 +5507,12 @@
         <v>22224.3</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:6">
       <c r="A202" t="s">
         <v>206</v>
       </c>
       <c r="B202">
-        <v>40502.949999999997</v>
+        <v>40502.95</v>
       </c>
       <c r="C202">
         <v>41159.17</v>
@@ -5571,13 +5521,13 @@
         <v>40109.58</v>
       </c>
       <c r="E202">
-        <v>40444.839999999997</v>
+        <v>40444.84</v>
       </c>
       <c r="F202">
         <v>24915.93</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:6">
       <c r="A203" t="s">
         <v>207</v>
       </c>
@@ -5588,7 +5538,7 @@
         <v>41251.46</v>
       </c>
       <c r="D203">
-        <v>40382.019999999997</v>
+        <v>40382.02</v>
       </c>
       <c r="E203">
         <v>40746.22</v>
@@ -5597,7 +5547,7 @@
         <v>16107.39</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:6">
       <c r="A204" t="s">
         <v>208</v>
       </c>
@@ -5617,7 +5567,7 @@
         <v>21287.9</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:6">
       <c r="A205" t="s">
         <v>209</v>
       </c>
@@ -5637,27 +5587,27 @@
         <v>11358.37</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:6">
       <c r="A206" t="s">
         <v>210</v>
       </c>
       <c r="B206">
-        <v>40725.160000000003</v>
+        <v>40725.16</v>
       </c>
       <c r="C206">
         <v>41331.74</v>
       </c>
       <c r="D206">
-        <v>40028.720000000001</v>
+        <v>40028.72</v>
       </c>
       <c r="E206">
-        <v>40778.199999999997</v>
+        <v>40778.2</v>
       </c>
       <c r="F206">
         <v>24312.1</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:6">
       <c r="A207" t="s">
         <v>211</v>
       </c>
@@ -5677,12 +5627,12 @@
         <v>24662.49</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:6">
       <c r="A208" t="s">
         <v>212</v>
       </c>
       <c r="B208">
-        <v>41807.230000000003</v>
+        <v>41807.23</v>
       </c>
       <c r="C208">
         <v>42059.22</v>
@@ -5691,21 +5641,21 @@
         <v>41225.78</v>
       </c>
       <c r="E208">
-        <v>41761.279999999999</v>
+        <v>41761.28</v>
       </c>
       <c r="F208">
         <v>23956.55</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:6">
       <c r="A209" t="s">
         <v>213</v>
       </c>
       <c r="B209">
-        <v>41191.629999999997</v>
+        <v>41191.63</v>
       </c>
       <c r="C209">
-        <v>41831.919999999998</v>
+        <v>41831.92</v>
       </c>
       <c r="D209">
         <v>40864.86</v>
@@ -5714,10 +5664,10 @@
         <v>41170.07</v>
       </c>
       <c r="F209">
-        <v>18662.689999999999</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.45">
+        <v>18662.69</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
       <c r="A210" t="s">
         <v>214</v>
       </c>
@@ -5731,13 +5681,13 @@
         <v>40546.01</v>
       </c>
       <c r="E210">
-        <v>41151.480000000003</v>
+        <v>41151.48</v>
       </c>
       <c r="F210">
         <v>21278.79</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:6">
       <c r="A211" t="s">
         <v>215</v>
       </c>
@@ -5748,21 +5698,21 @@
         <v>41329.58</v>
       </c>
       <c r="D211">
-        <v>41042.800000000003</v>
+        <v>41042.8</v>
       </c>
       <c r="E211">
-        <v>41293.120000000003</v>
+        <v>41293.12</v>
       </c>
       <c r="F211">
         <v>14523.5</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:6">
       <c r="A212" t="s">
         <v>216</v>
       </c>
       <c r="B212">
-        <v>41078.910000000003</v>
+        <v>41078.91</v>
       </c>
       <c r="C212">
         <v>41492.9</v>
@@ -5777,7 +5727,7 @@
         <v>20074.43</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:6">
       <c r="A213" t="s">
         <v>217</v>
       </c>
@@ -5794,15 +5744,15 @@
         <v>41498.74</v>
       </c>
       <c r="F213">
-        <v>57536.800000000003</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.45">
+        <v>57536.8</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
       <c r="A214" t="s">
         <v>218</v>
       </c>
       <c r="B214">
-        <v>41573.279999999999</v>
+        <v>41573.28</v>
       </c>
       <c r="C214">
         <v>41780.82</v>
@@ -5811,13 +5761,13 @@
         <v>40967.78</v>
       </c>
       <c r="E214">
-        <v>41505.370000000003</v>
+        <v>41505.37</v>
       </c>
       <c r="F214">
         <v>27260.3</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:6">
       <c r="A215" t="s">
         <v>219</v>
       </c>
@@ -5831,13 +5781,13 @@
         <v>41143.64</v>
       </c>
       <c r="E215">
-        <v>41695.120000000003</v>
+        <v>41695.12</v>
       </c>
       <c r="F215">
-        <v>19972.509999999998</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.45">
+        <v>19972.51</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
       <c r="A216" t="s">
         <v>220</v>
       </c>
@@ -5854,21 +5804,21 @@
         <v>41799.33</v>
       </c>
       <c r="F216">
-        <v>34072.620000000003</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.45">
+        <v>34072.62</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
       <c r="A217" t="s">
         <v>221</v>
       </c>
       <c r="B217">
-        <v>41822.720000000001</v>
+        <v>41822.72</v>
       </c>
       <c r="C217">
         <v>42194.32</v>
       </c>
       <c r="D217">
-        <v>41347.760000000002</v>
+        <v>41347.76</v>
       </c>
       <c r="E217">
         <v>41781.42</v>
@@ -5877,7 +5827,7 @@
         <v>30854.97</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:6">
       <c r="A218" t="s">
         <v>222</v>
       </c>
@@ -5897,7 +5847,7 @@
         <v>25639.64</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:6">
       <c r="A219" t="s">
         <v>223</v>
       </c>
@@ -5917,7 +5867,7 @@
         <v>23925.77</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:6">
       <c r="A220" t="s">
         <v>224</v>
       </c>
@@ -5937,7 +5887,7 @@
         <v>21820.42</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:6">
       <c r="A221" t="s">
         <v>225</v>
       </c>
@@ -5948,7 +5898,7 @@
         <v>42661.61</v>
       </c>
       <c r="D221">
-        <v>42318.879999999997</v>
+        <v>42318.88</v>
       </c>
       <c r="E221">
         <v>42323.23</v>
@@ -5957,12 +5907,12 @@
         <v>16933.78</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:6">
       <c r="A222" t="s">
         <v>226</v>
       </c>
       <c r="B222">
-        <v>41604.589999999997</v>
+        <v>41604.59</v>
       </c>
       <c r="C222">
         <v>41763.9</v>
@@ -5971,13 +5921,13 @@
         <v>41336.65</v>
       </c>
       <c r="E222">
-        <v>41349.730000000003</v>
+        <v>41349.73</v>
       </c>
       <c r="F222">
         <v>22039</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:6">
       <c r="A223" t="s">
         <v>227</v>
       </c>
@@ -5994,10 +5944,10 @@
         <v>42170.97</v>
       </c>
       <c r="F223">
-        <v>37157.879999999997</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.45">
+        <v>37157.88</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
       <c r="A224" t="s">
         <v>228</v>
       </c>
@@ -6017,7 +5967,7 @@
         <v>14741.85</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:6">
       <c r="A225" t="s">
         <v>229</v>
       </c>
@@ -6037,12 +5987,12 @@
         <v>24463.86</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:6">
       <c r="A226" t="s">
         <v>230</v>
       </c>
       <c r="B226">
-        <v>41758.449999999997</v>
+        <v>41758.45</v>
       </c>
       <c r="C226">
         <v>42105.24</v>
@@ -6057,18 +6007,18 @@
         <v>27935.58</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:6">
       <c r="A227" t="s">
         <v>231</v>
       </c>
       <c r="B227">
-        <v>41608.050000000003</v>
+        <v>41608.05</v>
       </c>
       <c r="C227">
-        <v>41744.019999999997</v>
+        <v>41744.02</v>
       </c>
       <c r="D227">
-        <v>40955.339999999997</v>
+        <v>40955.34</v>
       </c>
       <c r="E227">
         <v>40985.32</v>
@@ -6077,7 +6027,7 @@
         <v>25520.81</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:6">
       <c r="A228" t="s">
         <v>232</v>
       </c>
@@ -6088,7 +6038,7 @@
         <v>41556.94</v>
       </c>
       <c r="D228">
-        <v>40865.839999999997</v>
+        <v>40865.84</v>
       </c>
       <c r="E228">
         <v>40973.54</v>
@@ -6097,12 +6047,12 @@
         <v>17824.5</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:6">
       <c r="A229" t="s">
         <v>233</v>
       </c>
       <c r="B229">
-        <v>41011.589999999997</v>
+        <v>41011.59</v>
       </c>
       <c r="C229">
         <v>41226.26</v>
@@ -6111,18 +6061,18 @@
         <v>40798.07</v>
       </c>
       <c r="E229">
-        <v>41065.379999999997</v>
+        <v>41065.38</v>
       </c>
       <c r="F229">
         <v>7305.98</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:6">
       <c r="A230" t="s">
         <v>234</v>
       </c>
       <c r="B230">
-        <v>41397.360000000001</v>
+        <v>41397.36</v>
       </c>
       <c r="C230">
         <v>42056.38</v>
@@ -6131,53 +6081,53 @@
         <v>40898.43</v>
       </c>
       <c r="E230">
-        <v>41173.980000000003</v>
+        <v>41173.98</v>
       </c>
       <c r="F230">
         <v>28675.78</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:6">
       <c r="A231" t="s">
         <v>235</v>
       </c>
       <c r="B231">
-        <v>40956.089999999997</v>
+        <v>40956.09</v>
       </c>
       <c r="C231">
         <v>41125.97</v>
       </c>
       <c r="D231">
-        <v>40361.120000000003</v>
+        <v>40361.12</v>
       </c>
       <c r="E231">
-        <v>40421.980000000003</v>
+        <v>40421.98</v>
       </c>
       <c r="F231">
         <v>11859.56</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:6">
       <c r="A232" t="s">
         <v>236</v>
       </c>
       <c r="B232">
-        <v>40421.760000000002</v>
+        <v>40421.76</v>
       </c>
       <c r="C232">
-        <v>41014.879999999997</v>
+        <v>41014.88</v>
       </c>
       <c r="D232">
-        <v>40279.279999999999</v>
+        <v>40279.28</v>
       </c>
       <c r="E232">
-        <v>40305.800000000003</v>
+        <v>40305.8</v>
       </c>
       <c r="F232">
         <v>29341.13</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:6">
       <c r="A233" t="s">
         <v>237</v>
       </c>
@@ -6188,7 +6138,7 @@
         <v>41328.57</v>
       </c>
       <c r="D233">
-        <v>40253.379999999997</v>
+        <v>40253.38</v>
       </c>
       <c r="E233">
         <v>40950.14</v>
@@ -6197,7 +6147,7 @@
         <v>24336.06</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:6">
       <c r="A234" t="s">
         <v>238</v>
       </c>
@@ -6208,7 +6158,7 @@
         <v>41518.97</v>
       </c>
       <c r="D234">
-        <v>41047.879999999997</v>
+        <v>41047.88</v>
       </c>
       <c r="E234">
         <v>41148.44</v>
@@ -6217,7 +6167,7 @@
         <v>21952.21</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:6">
       <c r="A235" t="s">
         <v>239</v>
       </c>
@@ -6228,16 +6178,16 @@
         <v>41596.82</v>
       </c>
       <c r="D235">
-        <v>40533.120000000003</v>
+        <v>40533.12</v>
       </c>
       <c r="E235">
-        <v>40538.480000000003</v>
+        <v>40538.48</v>
       </c>
       <c r="F235">
         <v>30390.21</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:6">
       <c r="A236" t="s">
         <v>240</v>
       </c>
@@ -6245,19 +6195,19 @@
         <v>40702.28</v>
       </c>
       <c r="C236">
-        <v>40886.800000000003</v>
+        <v>40886.8</v>
       </c>
       <c r="D236">
-        <v>40127.129999999997</v>
+        <v>40127.13</v>
       </c>
       <c r="E236">
-        <v>40598.449999999997</v>
+        <v>40598.45</v>
       </c>
       <c r="F236">
         <v>36493.58</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:6">
       <c r="A237" t="s">
         <v>241</v>
       </c>
@@ -6277,15 +6227,15 @@
         <v>27943.62</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:6">
       <c r="A238" t="s">
         <v>242</v>
       </c>
       <c r="B238">
-        <v>40426.769999999997</v>
+        <v>40426.77</v>
       </c>
       <c r="C238">
-        <v>40878.370000000003</v>
+        <v>40878.37</v>
       </c>
       <c r="D238">
         <v>39702.01</v>
@@ -6297,7 +6247,7 @@
         <v>33202.44</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:6">
       <c r="A239" t="s">
         <v>243</v>
       </c>
@@ -6308,16 +6258,16 @@
         <v>40827.83</v>
       </c>
       <c r="D239">
-        <v>39541.410000000003</v>
+        <v>39541.41</v>
       </c>
       <c r="E239">
         <v>40419.06</v>
       </c>
       <c r="F239">
-        <v>30874.080000000002</v>
-      </c>
-    </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.45">
+        <v>30874.08</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
       <c r="A240" t="s">
         <v>244</v>
       </c>
@@ -6325,24 +6275,24 @@
         <v>40608.86</v>
       </c>
       <c r="C240">
-        <v>41119.230000000003</v>
+        <v>41119.23</v>
       </c>
       <c r="D240">
         <v>40031</v>
       </c>
       <c r="E240">
-        <v>40393.620000000003</v>
+        <v>40393.62</v>
       </c>
       <c r="F240">
-        <v>18435.080000000002</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.45">
+        <v>18435.08</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
       <c r="A241" t="s">
         <v>245</v>
       </c>
       <c r="B241">
-        <v>40554.519999999997</v>
+        <v>40554.52</v>
       </c>
       <c r="C241">
         <v>40930.76</v>
@@ -6351,18 +6301,18 @@
         <v>40258.28</v>
       </c>
       <c r="E241">
-        <v>40750.410000000003</v>
+        <v>40750.41</v>
       </c>
       <c r="F241">
         <v>17896.78</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:6">
       <c r="A242" t="s">
         <v>246</v>
       </c>
       <c r="B242">
-        <v>40460.400000000001</v>
+        <v>40460.4</v>
       </c>
       <c r="C242">
         <v>40825.74</v>
@@ -6377,7 +6327,7 @@
         <v>19638.47</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:6">
       <c r="A243" t="s">
         <v>247</v>
       </c>
@@ -6388,7 +6338,7 @@
         <v>40955.17</v>
       </c>
       <c r="D243">
-        <v>40216.839999999997</v>
+        <v>40216.84</v>
       </c>
       <c r="E243">
         <v>40261.72</v>
@@ -6397,7 +6347,7 @@
         <v>15058.28</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:6">
       <c r="A244" t="s">
         <v>248</v>
       </c>
@@ -6417,7 +6367,7 @@
         <v>15030.54</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:6">
       <c r="A245" t="s">
         <v>249</v>
       </c>
@@ -6425,19 +6375,19 @@
         <v>39549.39</v>
       </c>
       <c r="C245">
-        <v>39783.129999999997</v>
+        <v>39783.13</v>
       </c>
       <c r="D245">
         <v>39185.82</v>
       </c>
       <c r="E245">
-        <v>39320.300000000003</v>
+        <v>39320.3</v>
       </c>
       <c r="F245">
         <v>22813.03</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:6">
       <c r="A246" t="s">
         <v>250</v>
       </c>
@@ -6451,13 +6401,13 @@
         <v>38893.19</v>
       </c>
       <c r="E246">
-        <v>39253.360000000001</v>
+        <v>39253.36</v>
       </c>
       <c r="F246">
         <v>14584.97</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:6">
       <c r="A247" t="s">
         <v>251</v>
       </c>
@@ -6465,30 +6415,30 @@
         <v>39411.03</v>
       </c>
       <c r="C247">
-        <v>40255.089999999997</v>
+        <v>40255.09</v>
       </c>
       <c r="D247">
-        <v>38949.300000000003</v>
+        <v>38949.3</v>
       </c>
       <c r="E247">
         <v>39101.18</v>
       </c>
       <c r="F247">
-        <v>41579.449999999997</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.45">
+        <v>41579.45</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
       <c r="A248" t="s">
         <v>252</v>
       </c>
       <c r="B248">
-        <v>38664.449999999997</v>
+        <v>38664.45</v>
       </c>
       <c r="C248">
         <v>39350.67</v>
       </c>
       <c r="D248">
-        <v>38298.400000000001</v>
+        <v>38298.4</v>
       </c>
       <c r="E248">
         <v>38359.9</v>
@@ -6497,27 +6447,27 @@
         <v>30614.51</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:6">
       <c r="A249" t="s">
         <v>253</v>
       </c>
       <c r="B249">
-        <v>38138.629999999997</v>
+        <v>38138.63</v>
       </c>
       <c r="C249">
-        <v>38661.050000000003</v>
+        <v>38661.05</v>
       </c>
       <c r="D249">
         <v>37587.58</v>
       </c>
       <c r="E249">
-        <v>38529.089999999997</v>
+        <v>38529.09</v>
       </c>
       <c r="F249">
         <v>31245.72</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:6">
       <c r="A250" t="s">
         <v>254</v>
       </c>
@@ -6528,16 +6478,16 @@
         <v>38814.21</v>
       </c>
       <c r="D250">
-        <v>38093.620000000003</v>
+        <v>38093.62</v>
       </c>
       <c r="E250">
         <v>38696.25</v>
       </c>
       <c r="F250">
-        <v>24131.040000000001</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.45">
+        <v>24131.04</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
       <c r="A251" t="s">
         <v>255</v>
       </c>
@@ -6545,10 +6495,10 @@
         <v>39203.03</v>
       </c>
       <c r="C251">
-        <v>39765.660000000003</v>
+        <v>39765.66</v>
       </c>
       <c r="D251">
-        <v>38986.699999999997</v>
+        <v>38986.7</v>
       </c>
       <c r="E251">
         <v>39328.49</v>
@@ -6557,35 +6507,35 @@
         <v>21201.3</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:6">
       <c r="A252" t="s">
         <v>256</v>
       </c>
       <c r="B252">
-        <v>39131.699999999997</v>
+        <v>39131.7</v>
       </c>
       <c r="C252">
-        <v>39638.589999999997</v>
+        <v>39638.59</v>
       </c>
       <c r="D252">
-        <v>38806.550000000003</v>
+        <v>38806.55</v>
       </c>
       <c r="E252">
-        <v>39508.800000000003</v>
+        <v>39508.8</v>
       </c>
       <c r="F252">
-        <v>34232.730000000003</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.45">
+        <v>34232.73</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
       <c r="A253" t="s">
         <v>257</v>
       </c>
       <c r="B253">
-        <v>39581.230000000003</v>
+        <v>39581.23</v>
       </c>
       <c r="C253">
-        <v>39774.160000000003</v>
+        <v>39774.16</v>
       </c>
       <c r="D253">
         <v>39131.75</v>
@@ -6597,12 +6547,12 @@
         <v>15932.92</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:6">
       <c r="A254" t="s">
         <v>258</v>
       </c>
       <c r="B254">
-        <v>39435.910000000003</v>
+        <v>39435.91</v>
       </c>
       <c r="C254">
         <v>40046.97</v>
@@ -6611,13 +6561,13 @@
         <v>39044.01</v>
       </c>
       <c r="E254">
-        <v>39995.480000000003</v>
+        <v>39995.48</v>
       </c>
       <c r="F254">
         <v>18023.88</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:6">
       <c r="A255" t="s">
         <v>259</v>
       </c>
@@ -6628,7 +6578,7 @@
         <v>40513.4</v>
       </c>
       <c r="D255">
-        <v>40090.269999999997</v>
+        <v>40090.27</v>
       </c>
       <c r="E255">
         <v>40127.07</v>
@@ -6637,7 +6587,7 @@
         <v>19325.89</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:6">
       <c r="A256" t="s">
         <v>260</v>
       </c>
@@ -6648,21 +6598,21 @@
         <v>40445.08</v>
       </c>
       <c r="D256">
-        <v>39263.980000000003</v>
+        <v>39263.98</v>
       </c>
       <c r="E256">
-        <v>39318.080000000002</v>
+        <v>39318.08</v>
       </c>
       <c r="F256">
         <v>13997.6</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:6">
       <c r="A257" t="s">
         <v>261</v>
       </c>
       <c r="B257">
-        <v>39199.589999999997</v>
+        <v>39199.59</v>
       </c>
       <c r="C257">
         <v>39679.93</v>
@@ -6677,15 +6627,15 @@
         <v>34353.15</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:6">
       <c r="A258" t="s">
         <v>262</v>
       </c>
       <c r="B258">
-        <v>38601.129999999997</v>
+        <v>38601.13</v>
       </c>
       <c r="C258">
-        <v>38885.870000000003</v>
+        <v>38885.87</v>
       </c>
       <c r="D258">
         <v>38407.5</v>
@@ -6697,12 +6647,12 @@
         <v>22703.65</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:6">
       <c r="A259" t="s">
         <v>263</v>
       </c>
       <c r="B259">
-        <v>38227.440000000002</v>
+        <v>38227.44</v>
       </c>
       <c r="C259">
         <v>38535.08</v>
@@ -6717,7 +6667,7 @@
         <v>32772.89</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:6">
       <c r="A260" t="s">
         <v>264</v>
       </c>
@@ -6737,12 +6687,12 @@
         <v>21013.89</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:6">
       <c r="A261" t="s">
         <v>265</v>
       </c>
       <c r="B261">
-        <v>38548.629999999997</v>
+        <v>38548.63</v>
       </c>
       <c r="C261">
         <v>38865.06</v>
@@ -6751,13 +6701,13 @@
         <v>38035.24</v>
       </c>
       <c r="E261">
-        <v>38166.639999999999</v>
+        <v>38166.64</v>
       </c>
       <c r="F261">
         <v>17832.82</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:6">
       <c r="A262" t="s">
         <v>266</v>
       </c>
@@ -6765,19 +6715,19 @@
         <v>37672.43</v>
       </c>
       <c r="C262">
-        <v>37821.370000000003</v>
+        <v>37821.37</v>
       </c>
       <c r="D262">
         <v>37314.54</v>
       </c>
       <c r="E262">
-        <v>37443.129999999997</v>
+        <v>37443.13</v>
       </c>
       <c r="F262">
         <v>26936.31</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:6">
       <c r="A263" t="s">
         <v>267</v>
       </c>
@@ -6788,16 +6738,16 @@
         <v>38088.94</v>
       </c>
       <c r="D263">
-        <v>37223.839999999997</v>
+        <v>37223.84</v>
       </c>
       <c r="E263">
         <v>37389.49</v>
       </c>
       <c r="F263">
-        <v>17731.099999999999</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.45">
+        <v>17731.1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
       <c r="A264" t="s">
         <v>268</v>
       </c>
@@ -6817,12 +6767,12 @@
         <v>32548.85</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:6">
       <c r="A265" t="s">
         <v>269</v>
       </c>
       <c r="B265">
-        <v>37916.480000000003</v>
+        <v>37916.48</v>
       </c>
       <c r="C265">
         <v>38517.43</v>
@@ -6831,13 +6781,13 @@
         <v>37560.44</v>
       </c>
       <c r="E265">
-        <v>37990.959999999999</v>
+        <v>37990.96</v>
       </c>
       <c r="F265">
-        <v>37142.239999999998</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.45">
+        <v>37142.24</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
       <c r="A266" t="s">
         <v>270</v>
       </c>
@@ -6848,24 +6798,24 @@
         <v>37893.42</v>
       </c>
       <c r="D266">
-        <v>37263.980000000003</v>
+        <v>37263.98</v>
       </c>
       <c r="E266">
-        <v>37508.449999999997</v>
+        <v>37508.45</v>
       </c>
       <c r="F266">
-        <v>16491.560000000001</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.45">
+        <v>16491.56</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
       <c r="A267" t="s">
         <v>271</v>
       </c>
       <c r="B267">
-        <v>37267.589999999997</v>
+        <v>37267.59</v>
       </c>
       <c r="C267">
-        <v>37738.339999999997</v>
+        <v>37738.34</v>
       </c>
       <c r="D267">
         <v>37052.79</v>
@@ -6877,27 +6827,27 @@
         <v>23652.05</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:6">
       <c r="A268" t="s">
         <v>272</v>
       </c>
       <c r="B268">
-        <v>37285.449999999997</v>
+        <v>37285.45</v>
       </c>
       <c r="C268">
-        <v>37380.870000000003</v>
+        <v>37380.87</v>
       </c>
       <c r="D268">
-        <v>36526.120000000003</v>
+        <v>36526.12</v>
       </c>
       <c r="E268">
-        <v>36639.040000000001</v>
+        <v>36639.04</v>
       </c>
       <c r="F268">
         <v>23016.45</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:6">
       <c r="A269" t="s">
         <v>273</v>
       </c>
@@ -6917,27 +6867,27 @@
         <v>19259.21</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:6">
       <c r="A270" t="s">
         <v>274</v>
       </c>
       <c r="B270">
-        <v>35893.129999999997</v>
+        <v>35893.13</v>
       </c>
       <c r="C270">
         <v>36361.03</v>
       </c>
       <c r="D270">
-        <v>35621.699999999997</v>
+        <v>35621.7</v>
       </c>
       <c r="E270">
-        <v>35845.269999999997</v>
+        <v>35845.27</v>
       </c>
       <c r="F270">
         <v>28986.9</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:6">
       <c r="A271" t="s">
         <v>275</v>
       </c>
@@ -6948,7 +6898,7 @@
         <v>36546.54</v>
       </c>
       <c r="D271">
-        <v>35252.949999999997</v>
+        <v>35252.95</v>
       </c>
       <c r="E271">
         <v>36526.14</v>
@@ -6957,7 +6907,7 @@
         <v>31232.11</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:6">
       <c r="A272" t="s">
         <v>276</v>
       </c>
@@ -6965,7 +6915,7 @@
         <v>37040.03</v>
       </c>
       <c r="C272">
-        <v>37394.370000000003</v>
+        <v>37394.37</v>
       </c>
       <c r="D272">
         <v>36995.67</v>
@@ -6977,18 +6927,18 @@
         <v>25075.33</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:6">
       <c r="A273" t="s">
         <v>277</v>
       </c>
       <c r="B273">
-        <v>37579.730000000003</v>
+        <v>37579.73</v>
       </c>
       <c r="C273">
-        <v>38441.919999999998</v>
+        <v>38441.92</v>
       </c>
       <c r="D273">
-        <v>36944.480000000003</v>
+        <v>36944.48</v>
       </c>
       <c r="E273">
         <v>38013.96</v>
@@ -6997,7 +6947,7 @@
         <v>36243.74</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:6">
       <c r="A274" t="s">
         <v>278</v>
       </c>
@@ -7011,13 +6961,13 @@
         <v>37832.44</v>
       </c>
       <c r="E274">
-        <v>38425.589999999997</v>
+        <v>38425.59</v>
       </c>
       <c r="F274">
         <v>30036.7</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:6">
       <c r="A275" t="s">
         <v>279</v>
       </c>
@@ -7025,44 +6975,44 @@
         <v>38395.21</v>
       </c>
       <c r="C275">
-        <v>38764.769999999997</v>
+        <v>38764.77</v>
       </c>
       <c r="D275">
-        <v>37988.910000000003</v>
+        <v>37988.91</v>
       </c>
       <c r="E275">
-        <v>38662.129999999997</v>
+        <v>38662.13</v>
       </c>
       <c r="F275">
         <v>17914.71</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:6">
       <c r="A276" t="s">
         <v>280</v>
       </c>
       <c r="B276">
-        <v>38740.839999999997</v>
+        <v>38740.84</v>
       </c>
       <c r="C276">
-        <v>38962.370000000003</v>
+        <v>38962.37</v>
       </c>
       <c r="D276">
         <v>38484.19</v>
       </c>
       <c r="E276">
-        <v>38822.120000000003</v>
+        <v>38822.12</v>
       </c>
       <c r="F276">
-        <v>18795.919999999998</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.45">
+        <v>18795.92</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
       <c r="A277" t="s">
         <v>281</v>
       </c>
       <c r="B277">
-        <v>38240.639999999999</v>
+        <v>38240.64</v>
       </c>
       <c r="C277">
         <v>38561.33</v>
@@ -7071,24 +7021,24 @@
         <v>37795.21</v>
       </c>
       <c r="E277">
-        <v>38352.269999999997</v>
+        <v>38352.27</v>
       </c>
       <c r="F277">
         <v>29328.01</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:6">
       <c r="A278" t="s">
         <v>282</v>
       </c>
       <c r="B278">
-        <v>38408.629999999997</v>
+        <v>38408.63</v>
       </c>
       <c r="C278">
         <v>38741.71</v>
       </c>
       <c r="D278">
-        <v>37949.300000000003</v>
+        <v>37949.3</v>
       </c>
       <c r="E278">
         <v>38619.06</v>
@@ -7097,7 +7047,7 @@
         <v>20985.45</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:6">
       <c r="A279" t="s">
         <v>283</v>
       </c>
@@ -7111,21 +7061,21 @@
         <v>37674.82</v>
       </c>
       <c r="E279">
-        <v>38074.589999999997</v>
+        <v>38074.59</v>
       </c>
       <c r="F279">
-        <v>31836.080000000002</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.45">
+        <v>31836.08</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
       <c r="A280" t="s">
         <v>284</v>
       </c>
       <c r="B280">
-        <v>38604.910000000003</v>
+        <v>38604.91</v>
       </c>
       <c r="C280">
-        <v>38976.300000000003</v>
+        <v>38976.3</v>
       </c>
       <c r="D280">
         <v>38274.04</v>
@@ -7134,10 +7084,10 @@
         <v>38622.61</v>
       </c>
       <c r="F280">
-        <v>19486.740000000002</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.45">
+        <v>19486.74</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
       <c r="A281" t="s">
         <v>285</v>
       </c>
@@ -7145,30 +7095,30 @@
         <v>38571.65</v>
       </c>
       <c r="C281">
-        <v>39132.019999999997</v>
+        <v>39132.02</v>
       </c>
       <c r="D281">
         <v>38010.92</v>
       </c>
       <c r="E281">
-        <v>38977.050000000003</v>
+        <v>38977.05</v>
       </c>
       <c r="F281">
         <v>7096.72</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:6">
       <c r="A282" t="s">
         <v>286</v>
       </c>
       <c r="B282">
-        <v>39004.730000000003</v>
+        <v>39004.73</v>
       </c>
       <c r="C282">
         <v>39545.83</v>
       </c>
       <c r="D282">
-        <v>38311.269999999997</v>
+        <v>38311.27</v>
       </c>
       <c r="E282">
         <v>39260.61</v>
@@ -7177,7 +7127,7 @@
         <v>25028.65</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:6">
       <c r="A283" t="s">
         <v>287</v>
       </c>
@@ -7185,39 +7135,39 @@
         <v>38871.15</v>
       </c>
       <c r="C283">
-        <v>39317.440000000002</v>
+        <v>39317.44</v>
       </c>
       <c r="D283">
         <v>38358.44</v>
       </c>
       <c r="E283">
-        <v>39306.639999999999</v>
+        <v>39306.64</v>
       </c>
       <c r="F283">
         <v>14146.42</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:6">
       <c r="A284" t="s">
         <v>288</v>
       </c>
       <c r="B284">
-        <v>39376.370000000003</v>
+        <v>39376.37</v>
       </c>
       <c r="C284">
         <v>39511.93</v>
       </c>
       <c r="D284">
-        <v>38841.019999999997</v>
+        <v>38841.02</v>
       </c>
       <c r="E284">
-        <v>39317.339999999997</v>
+        <v>39317.34</v>
       </c>
       <c r="F284">
         <v>22078.99</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:6">
       <c r="A285" t="s">
         <v>289</v>
       </c>
@@ -7237,7 +7187,7 @@
         <v>13094.36</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:6">
       <c r="A286" t="s">
         <v>290</v>
       </c>
@@ -7245,24 +7195,24 @@
         <v>39770.18</v>
       </c>
       <c r="C286">
-        <v>40055.269999999997</v>
+        <v>40055.27</v>
       </c>
       <c r="D286">
         <v>39385.11</v>
       </c>
       <c r="E286">
-        <v>39756.639999999999</v>
+        <v>39756.64</v>
       </c>
       <c r="F286">
         <v>26826.87</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:6">
       <c r="A287" t="s">
         <v>291</v>
       </c>
       <c r="B287">
-        <v>39220.559999999998</v>
+        <v>39220.56</v>
       </c>
       <c r="C287">
         <v>39508.93</v>
@@ -7277,7 +7227,7 @@
         <v>24623.58</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:6">
       <c r="A288" t="s">
         <v>292</v>
       </c>
@@ -7291,13 +7241,13 @@
         <v>38478.51</v>
       </c>
       <c r="E288">
-        <v>38725.550000000003</v>
+        <v>38725.55</v>
       </c>
       <c r="F288">
         <v>21225.32</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:6">
       <c r="A289" t="s">
         <v>293</v>
       </c>
@@ -7314,10 +7264,10 @@
         <v>39038.15</v>
       </c>
       <c r="F289">
-        <v>38419.230000000003</v>
-      </c>
-    </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.45">
+        <v>38419.23</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
       <c r="A290" t="s">
         <v>294</v>
       </c>
@@ -7334,10 +7284,10 @@
         <v>39029.72</v>
       </c>
       <c r="F290">
-        <v>19302.810000000001</v>
-      </c>
-    </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.45">
+        <v>19302.81</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
       <c r="A291" t="s">
         <v>295</v>
       </c>
@@ -7348,7 +7298,7 @@
         <v>39736</v>
       </c>
       <c r="D291">
-        <v>38819.589999999997</v>
+        <v>38819.59</v>
       </c>
       <c r="E291">
         <v>39582.74</v>
@@ -7357,7 +7307,7 @@
         <v>32951.01</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:6">
       <c r="A292" t="s">
         <v>296</v>
       </c>
@@ -7371,13 +7321,13 @@
         <v>39038.21</v>
       </c>
       <c r="E292">
-        <v>39357.040000000001</v>
+        <v>39357.04</v>
       </c>
       <c r="F292">
         <v>24648.26</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:6">
       <c r="A293" t="s">
         <v>297</v>
       </c>
@@ -7388,7 +7338,7 @@
         <v>39610.68</v>
       </c>
       <c r="D293">
-        <v>39023.589999999997</v>
+        <v>39023.59</v>
       </c>
       <c r="E293">
         <v>39228.75</v>
@@ -7397,7 +7347,7 @@
         <v>14505.53</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:6">
       <c r="A294" t="s">
         <v>298</v>
       </c>
@@ -7414,18 +7364,18 @@
         <v>39375.93</v>
       </c>
       <c r="F294">
-        <v>24302.720000000001</v>
-      </c>
-    </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.45">
+        <v>24302.72</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
       <c r="A295" t="s">
         <v>299</v>
       </c>
       <c r="B295">
-        <v>39388.120000000003</v>
+        <v>39388.12</v>
       </c>
       <c r="C295">
-        <v>39902.089999999997</v>
+        <v>39902.09</v>
       </c>
       <c r="D295">
         <v>38924.36</v>
@@ -7437,12 +7387,12 @@
         <v>10816.47</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:6">
       <c r="A296" t="s">
         <v>300</v>
       </c>
       <c r="B296">
-        <v>39224.480000000003</v>
+        <v>39224.48</v>
       </c>
       <c r="C296">
         <v>39711.31</v>
@@ -7451,13 +7401,13 @@
         <v>39031.31</v>
       </c>
       <c r="E296">
-        <v>39576.519999999997</v>
+        <v>39576.52</v>
       </c>
       <c r="F296">
-        <v>37616.629999999997</v>
-      </c>
-    </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.45">
+        <v>37616.63</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
       <c r="A297" t="s">
         <v>301</v>
       </c>
@@ -7465,30 +7415,30 @@
         <v>39219.78</v>
       </c>
       <c r="C297">
-        <v>39661.910000000003</v>
+        <v>39661.91</v>
       </c>
       <c r="D297">
-        <v>38453.800000000003</v>
+        <v>38453.8</v>
       </c>
       <c r="E297">
-        <v>39207.019999999997</v>
+        <v>39207.02</v>
       </c>
       <c r="F297">
         <v>24221.09</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:6">
       <c r="A298" t="s">
         <v>302</v>
       </c>
       <c r="B298">
-        <v>39085.129999999997</v>
+        <v>39085.13</v>
       </c>
       <c r="C298">
         <v>39762.21</v>
       </c>
       <c r="D298">
-        <v>38852.129999999997</v>
+        <v>38852.13</v>
       </c>
       <c r="E298">
         <v>39072.9</v>
@@ -7497,7 +7447,7 @@
         <v>23792.87</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:6">
       <c r="A299" t="s">
         <v>303</v>
       </c>
@@ -7505,10 +7455,10 @@
         <v>38976.57</v>
       </c>
       <c r="C299">
-        <v>39149.800000000003</v>
+        <v>39149.8</v>
       </c>
       <c r="D299">
-        <v>38609.480000000003</v>
+        <v>38609.48</v>
       </c>
       <c r="E299">
         <v>38900.18</v>
@@ -7517,7 +7467,7 @@
         <v>30062.04</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:6">
       <c r="A300" t="s">
         <v>304</v>
       </c>
@@ -7525,7 +7475,7 @@
         <v>39242.68</v>
       </c>
       <c r="C300">
-        <v>39627.089999999997</v>
+        <v>39627.09</v>
       </c>
       <c r="D300">
         <v>38950.94</v>
@@ -7537,7 +7487,7 @@
         <v>42222.04</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:6">
       <c r="A301" t="s">
         <v>305</v>
       </c>
@@ -7548,7 +7498,7 @@
         <v>39787.78</v>
       </c>
       <c r="D301">
-        <v>38916.300000000003</v>
+        <v>38916.3</v>
       </c>
       <c r="E301">
         <v>39137.51</v>
@@ -7557,27 +7507,27 @@
         <v>31025.42</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:6">
       <c r="A302" t="s">
         <v>306</v>
       </c>
       <c r="B302">
-        <v>39195.300000000003</v>
+        <v>39195.3</v>
       </c>
       <c r="C302">
-        <v>39775.449999999997</v>
+        <v>39775.45</v>
       </c>
       <c r="D302">
-        <v>38750.629999999997</v>
+        <v>38750.63</v>
       </c>
       <c r="E302">
         <v>39358.79</v>
       </c>
       <c r="F302">
-        <v>34123.629999999997</v>
-      </c>
-    </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.45">
+        <v>34123.63</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
       <c r="A303" t="s">
         <v>307</v>
       </c>
@@ -7594,10 +7544,10 @@
         <v>39451.21</v>
       </c>
       <c r="F303">
-        <v>20387.810000000001</v>
-      </c>
-    </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.45">
+        <v>20387.81</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
       <c r="A304" t="s">
         <v>308</v>
       </c>
@@ -7617,18 +7567,18 @@
         <v>19186.11</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:6">
       <c r="A305" t="s">
         <v>309</v>
       </c>
       <c r="B305">
-        <v>39698.269999999997</v>
+        <v>39698.27</v>
       </c>
       <c r="C305">
-        <v>40136.879999999997</v>
+        <v>40136.88</v>
       </c>
       <c r="D305">
-        <v>39250.559999999998</v>
+        <v>39250.56</v>
       </c>
       <c r="E305">
         <v>39334.75</v>
@@ -7637,18 +7587,18 @@
         <v>13669.83</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:6">
       <c r="A306" t="s">
         <v>310</v>
       </c>
       <c r="B306">
-        <v>38939.629999999997</v>
+        <v>38939.63</v>
       </c>
       <c r="C306">
-        <v>39392.519999999997</v>
+        <v>39392.52</v>
       </c>
       <c r="D306">
-        <v>38686.550000000003</v>
+        <v>38686.55</v>
       </c>
       <c r="E306">
         <v>38890.06</v>
@@ -7657,7 +7607,7 @@
         <v>21033.18</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:6">
       <c r="A307" t="s">
         <v>311</v>
       </c>
@@ -7665,19 +7615,19 @@
         <v>38726.81</v>
       </c>
       <c r="C307">
-        <v>39346.449999999997</v>
+        <v>39346.45</v>
       </c>
       <c r="D307">
         <v>38011.35</v>
       </c>
       <c r="E307">
-        <v>38642.199999999997</v>
+        <v>38642.2</v>
       </c>
       <c r="F307">
         <v>21468.75</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:6">
       <c r="A308" t="s">
         <v>312</v>
       </c>
@@ -7697,7 +7647,7 @@
         <v>20989.39</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:6">
       <c r="A309" t="s">
         <v>313</v>
       </c>
@@ -7705,10 +7655,10 @@
         <v>37669.69</v>
       </c>
       <c r="C309">
-        <v>37947.440000000002</v>
+        <v>37947.44</v>
       </c>
       <c r="D309">
-        <v>37215.760000000002</v>
+        <v>37215.76</v>
       </c>
       <c r="E309">
         <v>37733.47</v>
@@ -7717,7 +7667,7 @@
         <v>31477.06</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:6">
       <c r="A310" t="s">
         <v>314</v>
       </c>
@@ -7725,7 +7675,7 @@
         <v>37455.54</v>
       </c>
       <c r="C310">
-        <v>37548.239999999998</v>
+        <v>37548.24</v>
       </c>
       <c r="D310">
         <v>37282.04</v>
@@ -7737,7 +7687,7 @@
         <v>29922.89</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:6">
       <c r="A311" t="s">
         <v>315</v>
       </c>
@@ -7745,24 +7695,24 @@
         <v>37645.07</v>
       </c>
       <c r="C311">
-        <v>38003.370000000003</v>
+        <v>38003.37</v>
       </c>
       <c r="D311">
         <v>37515.42</v>
       </c>
       <c r="E311">
-        <v>37826.550000000003</v>
+        <v>37826.55</v>
       </c>
       <c r="F311">
         <v>14598.25</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:6">
       <c r="A312" t="s">
         <v>316</v>
       </c>
       <c r="B312">
-        <v>37507.449999999997</v>
+        <v>37507.45</v>
       </c>
       <c r="C312">
         <v>37997.96</v>
@@ -7771,13 +7721,13 @@
         <v>36926.68</v>
       </c>
       <c r="E312">
-        <v>37038.410000000003</v>
+        <v>37038.41</v>
       </c>
       <c r="F312">
         <v>43852.76</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:6">
       <c r="A313" t="s">
         <v>317</v>
       </c>
@@ -7788,7 +7738,7 @@
         <v>37004.54</v>
       </c>
       <c r="D313">
-        <v>36130.480000000003</v>
+        <v>36130.48</v>
       </c>
       <c r="E313">
         <v>36279.96</v>
@@ -7797,18 +7747,18 @@
         <v>21403.96</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:6">
       <c r="A314" t="s">
         <v>318</v>
       </c>
       <c r="B314">
-        <v>36052.239999999998</v>
+        <v>36052.24</v>
       </c>
       <c r="C314">
         <v>36425.78</v>
       </c>
       <c r="D314">
-        <v>35561.160000000003</v>
+        <v>35561.16</v>
       </c>
       <c r="E314">
         <v>36225.93</v>
@@ -7817,7 +7767,7 @@
         <v>5736.9</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:6">
       <c r="A315" t="s">
         <v>319</v>
       </c>
@@ -7828,16 +7778,16 @@
         <v>36599.21</v>
       </c>
       <c r="D315">
-        <v>35598.949999999997</v>
+        <v>35598.95</v>
       </c>
       <c r="E315">
-        <v>36558.839999999997</v>
+        <v>36558.84</v>
       </c>
       <c r="F315">
         <v>23482.23</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:6">
       <c r="A316" t="s">
         <v>320</v>
       </c>
@@ -7848,16 +7798,16 @@
         <v>36359.54</v>
       </c>
       <c r="D316">
-        <v>35296.050000000003</v>
+        <v>35296.05</v>
       </c>
       <c r="E316">
-        <v>36033.550000000003</v>
+        <v>36033.55</v>
       </c>
       <c r="F316">
         <v>17878.93</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:6">
       <c r="A317" t="s">
         <v>321</v>
       </c>
@@ -7871,13 +7821,13 @@
         <v>36061.71</v>
       </c>
       <c r="E317">
-        <v>36432.730000000003</v>
+        <v>36432.73</v>
       </c>
       <c r="F317">
         <v>27649.27</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:6">
       <c r="A318" t="s">
         <v>322</v>
       </c>
@@ -7891,24 +7841,24 @@
         <v>35843.61</v>
       </c>
       <c r="E318">
-        <v>36279.980000000003</v>
+        <v>36279.98</v>
       </c>
       <c r="F318">
         <v>16465</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:6">
       <c r="A319" t="s">
         <v>323</v>
       </c>
       <c r="B319">
-        <v>36076.629999999997</v>
+        <v>36076.63</v>
       </c>
       <c r="C319">
-        <v>36311.699999999997</v>
+        <v>36311.7</v>
       </c>
       <c r="D319">
-        <v>35985.040000000001</v>
+        <v>35985.04</v>
       </c>
       <c r="E319">
         <v>36139.54</v>
@@ -7917,7 +7867,7 @@
         <v>20274.41</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:6">
       <c r="A320" t="s">
         <v>324</v>
       </c>
@@ -7925,7 +7875,7 @@
         <v>35859.81</v>
       </c>
       <c r="C320">
-        <v>36016.620000000003</v>
+        <v>36016.62</v>
       </c>
       <c r="D320">
         <v>35767.43</v>
@@ -7937,7 +7887,7 @@
         <v>23441.13</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:6">
       <c r="A321" t="s">
         <v>325</v>
       </c>
@@ -7948,27 +7898,27 @@
         <v>35446</v>
       </c>
       <c r="D321">
-        <v>35155.949999999997</v>
+        <v>35155.95</v>
       </c>
       <c r="E321">
-        <v>35188.269999999997</v>
+        <v>35188.27</v>
       </c>
       <c r="F321">
         <v>24593.26</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:6">
       <c r="A322" t="s">
         <v>326</v>
       </c>
       <c r="B322">
-        <v>35102.480000000003</v>
+        <v>35102.48</v>
       </c>
       <c r="C322">
-        <v>35663.339999999997</v>
+        <v>35663.34</v>
       </c>
       <c r="D322">
-        <v>34761.370000000003</v>
+        <v>34761.37</v>
       </c>
       <c r="E322">
         <v>35486.39</v>
@@ -7977,7 +7927,7 @@
         <v>27472.78</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:6">
       <c r="A323" t="s">
         <v>327</v>
       </c>
@@ -7985,19 +7935,19 @@
         <v>35222.69</v>
       </c>
       <c r="C323">
-        <v>35781.230000000003</v>
+        <v>35781.23</v>
       </c>
       <c r="D323">
         <v>35216.82</v>
       </c>
       <c r="E323">
-        <v>35335.379999999997</v>
+        <v>35335.38</v>
       </c>
       <c r="F323">
-        <v>31394.560000000001</v>
-      </c>
-    </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.45">
+        <v>31394.56</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6">
       <c r="A324" t="s">
         <v>328</v>
       </c>
@@ -8017,12 +7967,12 @@
         <v>31838.67</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:6">
       <c r="A325" t="s">
         <v>329</v>
       </c>
       <c r="B325">
-        <v>35511.370000000003</v>
+        <v>35511.37</v>
       </c>
       <c r="C325">
         <v>35650.21</v>
@@ -8037,12 +7987,12 @@
         <v>26253.08</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:6">
       <c r="A326" t="s">
         <v>330</v>
       </c>
       <c r="B326">
-        <v>35611.879999999997</v>
+        <v>35611.88</v>
       </c>
       <c r="C326">
         <v>36069.96</v>
@@ -8051,13 +8001,13 @@
         <v>35070.75</v>
       </c>
       <c r="E326">
-        <v>35181.050000000003</v>
+        <v>35181.05</v>
       </c>
       <c r="F326">
-        <v>18195.080000000002</v>
-      </c>
-    </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.45">
+        <v>18195.08</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6">
       <c r="A327" t="s">
         <v>331</v>
       </c>
@@ -8065,24 +8015,24 @@
         <v>35587.11</v>
       </c>
       <c r="C327">
-        <v>35677.910000000003</v>
+        <v>35677.91</v>
       </c>
       <c r="D327">
         <v>35184.35</v>
       </c>
       <c r="E327">
-        <v>35431.379999999997</v>
+        <v>35431.38</v>
       </c>
       <c r="F327">
-        <v>36591.339999999997</v>
-      </c>
-    </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.45">
+        <v>36591.34</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6">
       <c r="A328" t="s">
         <v>332</v>
       </c>
       <c r="B328">
-        <v>35263.769999999997</v>
+        <v>35263.77</v>
       </c>
       <c r="C328">
         <v>35555.65</v>
@@ -8097,12 +8047,12 @@
         <v>14427.52</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:6">
       <c r="A329" t="s">
         <v>333</v>
       </c>
       <c r="B329">
-        <v>35725.870000000003</v>
+        <v>35725.87</v>
       </c>
       <c r="C329">
         <v>35793.43</v>
@@ -8111,13 +8061,13 @@
         <v>35452.31</v>
       </c>
       <c r="E329">
-        <v>35738.769999999997</v>
+        <v>35738.77</v>
       </c>
       <c r="F329">
         <v>23792.78</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:6">
       <c r="A330" t="s">
         <v>334</v>
       </c>
@@ -8125,10 +8075,10 @@
         <v>35980.65</v>
       </c>
       <c r="C330">
-        <v>36718.300000000003</v>
+        <v>36718.3</v>
       </c>
       <c r="D330">
-        <v>35650.379999999997</v>
+        <v>35650.38</v>
       </c>
       <c r="E330">
         <v>35992.44</v>
@@ -8137,7 +8087,7 @@
         <v>6181.75</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:6">
       <c r="A331" t="s">
         <v>335</v>
       </c>
@@ -8151,18 +8101,18 @@
         <v>35292.83</v>
       </c>
       <c r="E331">
-        <v>35947.480000000003</v>
+        <v>35947.48</v>
       </c>
       <c r="F331">
         <v>1423.8</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:6">
       <c r="A332" t="s">
         <v>336</v>
       </c>
       <c r="B332">
-        <v>35936.720000000001</v>
+        <v>35936.72</v>
       </c>
       <c r="C332">
         <v>36082.82</v>
@@ -8171,13 +8121,13 @@
         <v>35434.57</v>
       </c>
       <c r="E332">
-        <v>35671.089999999997</v>
+        <v>35671.09</v>
       </c>
       <c r="F332">
         <v>24348.57</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:6">
       <c r="A333" t="s">
         <v>337</v>
       </c>
@@ -8185,7 +8135,7 @@
         <v>35385.14</v>
       </c>
       <c r="C333">
-        <v>35565.870000000003</v>
+        <v>35565.87</v>
       </c>
       <c r="D333">
         <v>34793.06</v>
@@ -8194,10 +8144,10 @@
         <v>35315.06</v>
       </c>
       <c r="F333">
-        <v>17747.810000000001</v>
-      </c>
-    </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.45">
+        <v>17747.81</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6">
       <c r="A334" t="s">
         <v>338</v>
       </c>
@@ -8217,7 +8167,7 @@
         <v>2111.85</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:6">
       <c r="A335" t="s">
         <v>339</v>
       </c>
@@ -8225,7 +8175,7 @@
         <v>34655.08</v>
       </c>
       <c r="C335">
-        <v>34851.589999999997</v>
+        <v>34851.59</v>
       </c>
       <c r="D335">
         <v>33881.21</v>
@@ -8237,12 +8187,12 @@
         <v>21478</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:6">
       <c r="A336" t="s">
         <v>340</v>
       </c>
       <c r="B336">
-        <v>34136.910000000003</v>
+        <v>34136.91</v>
       </c>
       <c r="C336">
         <v>34359.46</v>
@@ -8251,13 +8201,13 @@
         <v>33706.04</v>
       </c>
       <c r="E336">
-        <v>33992.660000000003</v>
+        <v>33992.66</v>
       </c>
       <c r="F336">
         <v>23470.63</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:6">
       <c r="A337" t="s">
         <v>341</v>
       </c>
@@ -8265,19 +8215,19 @@
         <v>33498.07</v>
       </c>
       <c r="C337">
-        <v>33651.599999999999</v>
+        <v>33651.6</v>
       </c>
       <c r="D337">
         <v>33199.58</v>
       </c>
       <c r="E337">
-        <v>33554.620000000003</v>
+        <v>33554.62</v>
       </c>
       <c r="F337">
-        <v>20804.080000000002</v>
-      </c>
-    </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.45">
+        <v>20804.08</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6">
       <c r="A338" t="s">
         <v>342</v>
       </c>
@@ -8285,19 +8235,19 @@
         <v>33608.76</v>
       </c>
       <c r="C338">
-        <v>33943.839999999997</v>
+        <v>33943.84</v>
       </c>
       <c r="D338">
         <v>33086.61</v>
       </c>
       <c r="E338">
-        <v>33723.980000000003</v>
+        <v>33723.98</v>
       </c>
       <c r="F338">
         <v>14110.82</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:6">
       <c r="A339" t="s">
         <v>343</v>
       </c>
@@ -8305,10 +8255,10 @@
         <v>33717.56</v>
       </c>
       <c r="C339">
-        <v>34070.959999999999</v>
+        <v>34070.96</v>
       </c>
       <c r="D339">
-        <v>33348.410000000003</v>
+        <v>33348.41</v>
       </c>
       <c r="E339">
         <v>33831.93</v>
@@ -8317,7 +8267,7 @@
         <v>32733.03</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:6">
       <c r="A340" t="s">
         <v>344</v>
       </c>
@@ -8331,13 +8281,13 @@
         <v>32974.76</v>
       </c>
       <c r="E340">
-        <v>33475.480000000003</v>
+        <v>33475.48</v>
       </c>
       <c r="F340">
         <v>17450.66</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:6">
       <c r="A341" t="s">
         <v>345</v>
       </c>
@@ -8345,24 +8295,24 @@
         <v>33432.79</v>
       </c>
       <c r="C341">
-        <v>33897.980000000003</v>
+        <v>33897.98</v>
       </c>
       <c r="D341">
         <v>33264.1</v>
       </c>
       <c r="E341">
-        <v>33310.629999999997</v>
+        <v>33310.63</v>
       </c>
       <c r="F341">
         <v>29848.11</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:6">
       <c r="A342" t="s">
         <v>346</v>
       </c>
       <c r="B342">
-        <v>33165.339999999997</v>
+        <v>33165.34</v>
       </c>
       <c r="C342">
         <v>33482.17</v>
@@ -8374,10 +8324,10 @@
         <v>32863.79</v>
       </c>
       <c r="F342">
-        <v>27179.200000000001</v>
-      </c>
-    </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.45">
+        <v>27179.2</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6">
       <c r="A343" t="s">
         <v>347</v>
       </c>
@@ -8385,7 +8335,7 @@
         <v>32668.82</v>
       </c>
       <c r="C343">
-        <v>32849.919999999998</v>
+        <v>32849.92</v>
       </c>
       <c r="D343">
         <v>32321.99</v>
@@ -8397,12 +8347,12 @@
         <v>20224.61</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:6">
       <c r="A344" t="s">
         <v>348</v>
       </c>
       <c r="B344">
-        <v>33093.019999999997</v>
+        <v>33093.02</v>
       </c>
       <c r="C344">
         <v>33424.01</v>
@@ -8417,12 +8367,12 @@
         <v>31870.53</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:6">
       <c r="A345" t="s">
         <v>349</v>
       </c>
       <c r="B345">
-        <v>32405.919999999998</v>
+        <v>32405.92</v>
       </c>
       <c r="C345">
         <v>32682.31</v>
@@ -8437,7 +8387,7 @@
         <v>16380.2</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:6">
       <c r="A346" t="s">
         <v>350</v>
       </c>
@@ -8457,12 +8407,12 @@
         <v>22522.44</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:6">
       <c r="A347" t="s">
         <v>351</v>
       </c>
       <c r="B347">
-        <v>32430.799999999999</v>
+        <v>32430.8</v>
       </c>
       <c r="C347">
         <v>32935.33</v>
@@ -8471,13 +8421,13 @@
         <v>32015.84</v>
       </c>
       <c r="E347">
-        <v>32832.949999999997</v>
+        <v>32832.95</v>
       </c>
       <c r="F347">
         <v>22798.52</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:6">
       <c r="A348" t="s">
         <v>352</v>
       </c>
@@ -8491,13 +8441,13 @@
         <v>31955.14</v>
       </c>
       <c r="E348">
-        <v>32753.599999999999</v>
+        <v>32753.6</v>
       </c>
       <c r="F348">
         <v>24003.85</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:6">
       <c r="A349" t="s">
         <v>353</v>
       </c>
@@ -8517,7 +8467,7 @@
         <v>39119.78</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:6">
       <c r="A350" t="s">
         <v>354</v>
       </c>
@@ -8537,7 +8487,7 @@
         <v>34634.01</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:6">
       <c r="A351" t="s">
         <v>355</v>
       </c>
@@ -8557,7 +8507,7 @@
         <v>3221.54</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:6">
       <c r="A352" t="s">
         <v>356</v>
       </c>
@@ -8577,7 +8527,7 @@
         <v>32649.81</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:6">
       <c r="A353" t="s">
         <v>357</v>
       </c>
@@ -8597,7 +8547,7 @@
         <v>35957.89</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:6">
       <c r="A354" t="s">
         <v>358</v>
       </c>
@@ -8617,7 +8567,7 @@
         <v>34456.68</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:6">
       <c r="A355" t="s">
         <v>359</v>
       </c>
@@ -8631,13 +8581,13 @@
         <v>31140.9</v>
       </c>
       <c r="E355">
-        <v>31155.599999999999</v>
+        <v>31155.6</v>
       </c>
       <c r="F355">
         <v>14399.39</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:6">
       <c r="A356" t="s">
         <v>360</v>
       </c>
@@ -8651,13 +8601,13 @@
         <v>30596.06</v>
       </c>
       <c r="E356">
-        <v>31224.880000000001</v>
+        <v>31224.88</v>
       </c>
       <c r="F356">
         <v>24714.28</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:6">
       <c r="A357" t="s">
         <v>361</v>
       </c>
@@ -8677,7 +8627,7 @@
         <v>26756.57</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:6">
       <c r="A358" t="s">
         <v>362</v>
       </c>
@@ -8697,7 +8647,7 @@
         <v>30645.14</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:6">
       <c r="A359" t="s">
         <v>363</v>
       </c>
@@ -8717,7 +8667,7 @@
         <v>37126.71</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:6">
       <c r="A360" t="s">
         <v>364</v>
       </c>
@@ -8737,7 +8687,7 @@
         <v>19926.97</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:6">
       <c r="A361" t="s">
         <v>365</v>
       </c>
@@ -8757,7 +8707,7 @@
         <v>25226.53</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:6">
       <c r="A362" t="s">
         <v>366</v>
       </c>
@@ -8774,10 +8724,10 @@
         <v>29570.35</v>
       </c>
       <c r="F362">
-        <v>9619.2800000000007</v>
-      </c>
-    </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.45">
+        <v>9619.280000000001</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6">
       <c r="A363" t="s">
         <v>367</v>
       </c>
@@ -8797,7 +8747,7 @@
         <v>36418.86</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:6">
       <c r="A364" t="s">
         <v>368</v>
       </c>
@@ -8817,7 +8767,7 @@
         <v>17203.88</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:6">
       <c r="A365" t="s">
         <v>369</v>
       </c>
@@ -8837,7 +8787,7 @@
         <v>17061.73</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:6">
       <c r="A366" t="s">
         <v>370</v>
       </c>
